--- a/holdings.xlsx
+++ b/holdings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\tase-ytm-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{184E01F8-0665-4996-B877-D3D3AF2263E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FDFA9B-003E-405D-B9CE-CE6272EA30EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="110">
   <si>
     <t/>
   </si>
@@ -293,12 +293,6 @@
   </si>
   <si>
     <t>1223452</t>
-  </si>
-  <si>
-    <t>202 פועלים אגח</t>
-  </si>
-  <si>
-    <t>1199850</t>
   </si>
   <si>
     <t>צור אגח י</t>
@@ -750,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:W72"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -777,33 +771,579 @@
     <col min="23" max="23" width="24.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="U5" s="1"/>
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>0</v>
+      </c>
+      <c r="W5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6" t="s">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>0</v>
+      </c>
+      <c r="W6" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C7" s="1"/>
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
+        <v>0</v>
+      </c>
+      <c r="W7" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C8" s="1"/>
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6433</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>-3679.3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-5.41</v>
+      </c>
+      <c r="K8" s="1">
+        <v>6620.52</v>
+      </c>
+      <c r="L8" s="1">
+        <v>6725.05</v>
+      </c>
+      <c r="M8" s="1">
+        <v>-1875.18</v>
+      </c>
+      <c r="N8" s="1">
+        <v>-2.83</v>
+      </c>
+      <c r="O8" s="1">
+        <v>-2920.48</v>
+      </c>
+      <c r="P8" s="1">
+        <v>-4.34</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>64330</v>
+      </c>
+      <c r="R8" s="1">
+        <v>64330</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1">
+        <v>3.31</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0</v>
+      </c>
+      <c r="W8" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>0</v>
@@ -811,55 +1351,51 @@
       <c r="E9" t="s">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>0</v>
+      <c r="F9" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2077</v>
       </c>
       <c r="H9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>0</v>
-      </c>
-      <c r="P9" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>0</v>
-      </c>
-      <c r="R9" t="s">
-        <v>0</v>
-      </c>
-      <c r="S9" t="s">
-        <v>0</v>
-      </c>
-      <c r="T9" t="s">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1">
+        <v>210.42</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1954.92</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2001.82</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1831.18</v>
+      </c>
+      <c r="N9" s="1">
+        <v>6.24</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1127.71</v>
+      </c>
+      <c r="P9" s="1">
+        <v>3.75</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>31155</v>
+      </c>
+      <c r="R9" s="1">
+        <v>31155</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="V9" s="1">
         <v>0</v>
       </c>
       <c r="W9" t="s">
@@ -867,74 +1403,74 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>24</v>
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>9000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>732</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-1440.66</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-2.14</v>
+      </c>
+      <c r="K10" s="1">
+        <v>629.78</v>
+      </c>
+      <c r="L10" s="1">
+        <v>673.72</v>
+      </c>
+      <c r="M10" s="1">
+        <v>9199.61</v>
+      </c>
+      <c r="N10" s="1">
+        <v>16.23</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5245.47</v>
+      </c>
+      <c r="P10" s="1">
+        <v>8.65</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>65880</v>
+      </c>
+      <c r="R10" s="1">
+        <v>65880</v>
+      </c>
+      <c r="S10" s="1">
+        <v>483.32</v>
+      </c>
+      <c r="T10" s="1">
+        <v>483.32</v>
+      </c>
+      <c r="U10" s="1">
+        <v>3.39</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
@@ -942,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>0</v>
@@ -953,55 +1489,51 @@
       <c r="E11" t="s">
         <v>0</v>
       </c>
-      <c r="F11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>0</v>
+      <c r="F11" s="1">
+        <v>85000</v>
+      </c>
+      <c r="G11" s="1">
+        <v>100.4</v>
       </c>
       <c r="H11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>0</v>
-      </c>
-      <c r="P11" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>0</v>
-      </c>
-      <c r="R11" t="s">
-        <v>0</v>
-      </c>
-      <c r="S11" t="s">
-        <v>0</v>
-      </c>
-      <c r="T11" t="s">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>508.99</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="K11" s="1">
+        <v>92.69</v>
+      </c>
+      <c r="L11" s="1">
+        <v>86</v>
+      </c>
+      <c r="M11" s="1">
+        <v>6551.28</v>
+      </c>
+      <c r="N11" s="1">
+        <v>8.31</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12240.77</v>
+      </c>
+      <c r="P11" s="1">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>85340</v>
+      </c>
+      <c r="R11" s="1">
+        <v>85340</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V11" s="1">
         <v>0</v>
       </c>
       <c r="W11" t="s">
@@ -1013,10 +1545,10 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>0</v>
@@ -1024,55 +1556,51 @@
       <c r="E12" t="s">
         <v>0</v>
       </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>0</v>
+      <c r="F12" s="1">
+        <v>172500</v>
+      </c>
+      <c r="G12" s="1">
+        <v>12.9</v>
       </c>
       <c r="H12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-862.18</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-3.73</v>
+      </c>
+      <c r="K12" s="1">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="L12" s="1">
+        <v>18.78</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-10101.42</v>
+      </c>
+      <c r="N12" s="1">
+        <v>-31.22</v>
+      </c>
+      <c r="O12" s="1">
+        <v>-10134.67</v>
+      </c>
+      <c r="P12" s="1">
+        <v>-31.29</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>22252.5</v>
+      </c>
+      <c r="R12" s="1">
+        <v>22252.5</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="V12" s="1">
         <v>0</v>
       </c>
       <c r="W12" t="s">
@@ -1084,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>0</v>
@@ -1095,55 +1623,51 @@
       <c r="E13" t="s">
         <v>0</v>
       </c>
-      <c r="F13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>0</v>
+      <c r="F13" s="1">
+        <v>293</v>
+      </c>
+      <c r="G13" s="1">
+        <v>11120</v>
       </c>
       <c r="H13" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>0</v>
-      </c>
-      <c r="P13" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>0</v>
-      </c>
-      <c r="R13" t="s">
-        <v>0</v>
-      </c>
-      <c r="S13" t="s">
-        <v>0</v>
-      </c>
-      <c r="T13" t="s">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>0</v>
-      </c>
-      <c r="V13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1">
+        <v>673.27</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2.11</v>
+      </c>
+      <c r="K13" s="1">
+        <v>19220.14</v>
+      </c>
+      <c r="L13" s="1">
+        <v>19264.77</v>
+      </c>
+      <c r="M13" s="1">
+        <v>-23733.41</v>
+      </c>
+      <c r="N13" s="1">
+        <v>-42.14</v>
+      </c>
+      <c r="O13" s="1">
+        <v>-23864.16</v>
+      </c>
+      <c r="P13" s="1">
+        <v>-42.27</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>32581.599999999999</v>
+      </c>
+      <c r="R13" s="1">
+        <v>32581.599999999999</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="V13" s="1">
         <v>0</v>
       </c>
       <c r="W13" t="s">
@@ -1155,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
         <v>0</v>
@@ -1166,55 +1690,51 @@
       <c r="E14" t="s">
         <v>0</v>
       </c>
-      <c r="F14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>0</v>
+      <c r="F14" s="1">
+        <v>2200</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1118</v>
       </c>
       <c r="H14" t="s">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>0</v>
-      </c>
-      <c r="M14" t="s">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>0</v>
-      </c>
-      <c r="P14" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>0</v>
-      </c>
-      <c r="R14" t="s">
-        <v>0</v>
-      </c>
-      <c r="S14" t="s">
-        <v>0</v>
-      </c>
-      <c r="T14" t="s">
-        <v>0</v>
-      </c>
-      <c r="U14" t="s">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1">
+        <v>308.45</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1374</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1375.24</v>
+      </c>
+      <c r="M14" s="1">
+        <v>-5632</v>
+      </c>
+      <c r="N14" s="1">
+        <v>-18.63</v>
+      </c>
+      <c r="O14" s="1">
+        <v>-5659.21</v>
+      </c>
+      <c r="P14" s="1">
+        <v>-18.7</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>24596</v>
+      </c>
+      <c r="R14" s="1">
+        <v>24596</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="V14" s="1">
         <v>0</v>
       </c>
       <c r="W14" t="s">
@@ -1226,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
         <v>0</v>
@@ -1238,48 +1758,48 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G15" s="1">
-        <v>6772</v>
+        <v>57.2</v>
       </c>
       <c r="H15" t="s">
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>124.82</v>
+        <v>32.99</v>
       </c>
       <c r="J15" s="1">
-        <v>0.37</v>
+        <v>6.12</v>
       </c>
       <c r="K15" s="1">
-        <v>6688</v>
+        <v>55</v>
       </c>
       <c r="L15" s="1">
-        <v>6694.02</v>
+        <v>55.45</v>
       </c>
       <c r="M15" s="1">
-        <v>419.99</v>
+        <v>22</v>
       </c>
       <c r="N15" s="1">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O15" s="1">
-        <v>389.9</v>
+        <v>17.5</v>
       </c>
       <c r="P15" s="1">
-        <v>1.1599999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" s="1">
-        <v>33860</v>
+        <v>572</v>
       </c>
       <c r="R15" s="1">
-        <v>33860</v>
+        <v>572</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1">
-        <v>1.67</v>
+        <v>0.03</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -1293,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
         <v>0</v>
@@ -1305,52 +1825,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G16" s="1">
-        <v>2029</v>
+        <v>3225</v>
       </c>
       <c r="H16" t="s">
         <v>2</v>
       </c>
       <c r="I16" s="1">
-        <v>405.4</v>
+        <v>2191.2800000000002</v>
       </c>
       <c r="J16" s="1">
-        <v>1.35</v>
+        <v>7.29</v>
       </c>
       <c r="K16" s="1">
-        <v>2000</v>
+        <v>2472</v>
       </c>
       <c r="L16" s="1">
-        <v>2001.82</v>
+        <v>2474.23</v>
       </c>
       <c r="M16" s="1">
-        <v>435</v>
+        <v>7529.99</v>
       </c>
       <c r="N16" s="1">
-        <v>1.45</v>
+        <v>30.46</v>
       </c>
       <c r="O16" s="1">
-        <v>407.71</v>
+        <v>7507.75</v>
       </c>
       <c r="P16" s="1">
-        <v>1.35</v>
+        <v>30.34</v>
       </c>
       <c r="Q16" s="1">
-        <v>30435</v>
+        <v>32250</v>
       </c>
       <c r="R16" s="1">
-        <v>30435</v>
-      </c>
-      <c r="S16" s="1">
-        <v>676.18</v>
-      </c>
-      <c r="T16" s="1">
-        <v>676.18</v>
-      </c>
+        <v>32250</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
       <c r="U16" s="1">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -1364,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
         <v>0</v>
@@ -1376,48 +1892,48 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="G17" s="1">
-        <v>716.8</v>
+        <v>234.8</v>
       </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
       <c r="I17" s="1">
-        <v>648.11</v>
+        <v>-781.23</v>
       </c>
       <c r="J17" s="1">
-        <v>1.53</v>
+        <v>-2.17</v>
       </c>
       <c r="K17" s="1">
-        <v>575.66999999999996</v>
+        <v>317.23</v>
       </c>
       <c r="L17" s="1">
-        <v>641.24</v>
+        <v>318.69</v>
       </c>
       <c r="M17" s="1">
-        <v>8467.61</v>
+        <v>-12364.89</v>
       </c>
       <c r="N17" s="1">
-        <v>24.51</v>
+        <v>-25.98</v>
       </c>
       <c r="O17" s="1">
-        <v>4533.3999999999996</v>
+        <v>-12582.98</v>
       </c>
       <c r="P17" s="1">
-        <v>11.78</v>
+        <v>-26.32</v>
       </c>
       <c r="Q17" s="1">
-        <v>43008</v>
+        <v>35220</v>
       </c>
       <c r="R17" s="1">
-        <v>43008</v>
+        <v>35220</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -1431,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
         <v>0</v>
@@ -1443,48 +1959,48 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>93000</v>
+        <v>1350</v>
       </c>
       <c r="G18" s="1">
-        <v>101.6</v>
+        <v>2231</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>-189.35</v>
+        <v>-298.08</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.2</v>
+        <v>-0.98</v>
       </c>
       <c r="K18" s="1">
-        <v>92.69</v>
+        <v>2575.86</v>
       </c>
       <c r="L18" s="1">
-        <v>89.42</v>
+        <v>2758.41</v>
       </c>
       <c r="M18" s="1">
-        <v>8283.8799999999992</v>
+        <v>-4655.54</v>
       </c>
       <c r="N18" s="1">
-        <v>9.6</v>
+        <v>-13.38</v>
       </c>
       <c r="O18" s="1">
-        <v>11330.2</v>
+        <v>-7119.98</v>
       </c>
       <c r="P18" s="1">
-        <v>13.62</v>
+        <v>-19.11</v>
       </c>
       <c r="Q18" s="1">
-        <v>94488</v>
+        <v>30118.5</v>
       </c>
       <c r="R18" s="1">
-        <v>94488</v>
+        <v>30118.5</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1">
-        <v>4.67</v>
+        <v>1.55</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -1498,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>0</v>
@@ -1510,48 +2026,48 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>172500</v>
+        <v>700</v>
       </c>
       <c r="G19" s="1">
-        <v>15.3</v>
+        <v>4780</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="1">
-        <v>343.84</v>
+        <v>-561.35</v>
       </c>
       <c r="J19" s="1">
-        <v>1.32</v>
+        <v>-1.65</v>
       </c>
       <c r="K19" s="1">
-        <v>18.760000000000002</v>
+        <v>5547.95</v>
       </c>
       <c r="L19" s="1">
-        <v>18.78</v>
+        <v>5657.95</v>
       </c>
       <c r="M19" s="1">
-        <v>-5961.42</v>
+        <v>-5375.68</v>
       </c>
       <c r="N19" s="1">
-        <v>-18.420000000000002</v>
+        <v>-13.84</v>
       </c>
       <c r="O19" s="1">
-        <v>-5994.67</v>
+        <v>-6145.62</v>
       </c>
       <c r="P19" s="1">
-        <v>-18.5</v>
+        <v>-15.51</v>
       </c>
       <c r="Q19" s="1">
-        <v>26392.5</v>
+        <v>33460</v>
       </c>
       <c r="R19" s="1">
-        <v>26392.5</v>
+        <v>33460</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -1565,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>0</v>
@@ -1577,48 +2093,48 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>293</v>
+        <v>2900</v>
       </c>
       <c r="G20" s="1">
-        <v>9874</v>
+        <v>727.2</v>
       </c>
       <c r="H20" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="1">
-        <v>-256.85000000000002</v>
+        <v>-152.94</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.88</v>
+        <v>-0.72</v>
       </c>
       <c r="K20" s="1">
-        <v>19220.14</v>
+        <v>998</v>
       </c>
       <c r="L20" s="1">
-        <v>19264.77</v>
+        <v>998.9</v>
       </c>
       <c r="M20" s="1">
-        <v>-27384.19</v>
+        <v>-7853.2</v>
       </c>
       <c r="N20" s="1">
-        <v>-48.62</v>
+        <v>-27.13</v>
       </c>
       <c r="O20" s="1">
-        <v>-27514.94</v>
+        <v>-7879.25</v>
       </c>
       <c r="P20" s="1">
-        <v>-48.74</v>
+        <v>-27.19</v>
       </c>
       <c r="Q20" s="1">
-        <v>28930.82</v>
+        <v>21088.799999999999</v>
       </c>
       <c r="R20" s="1">
-        <v>28930.82</v>
+        <v>21088.799999999999</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1">
-        <v>1.43</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -1632,10 +2148,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>0</v>
@@ -1644,48 +2160,48 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>2200</v>
+        <v>106391</v>
       </c>
       <c r="G21" s="1">
-        <v>1190</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <v>-20.96</v>
+        <v>3191.44</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.08</v>
+        <v>11.11</v>
       </c>
       <c r="K21" s="1">
-        <v>1374</v>
+        <v>39.97</v>
       </c>
       <c r="L21" s="1">
-        <v>1375.24</v>
+        <v>40.01</v>
       </c>
       <c r="M21" s="1">
-        <v>-4048</v>
+        <v>-10601.86</v>
       </c>
       <c r="N21" s="1">
-        <v>-13.39</v>
+        <v>-24.93</v>
       </c>
       <c r="O21" s="1">
-        <v>-4075.21</v>
+        <v>-69497.63</v>
       </c>
       <c r="P21" s="1">
-        <v>-13.46</v>
+        <v>-25</v>
       </c>
       <c r="Q21" s="1">
-        <v>26180</v>
+        <v>31917.3</v>
       </c>
       <c r="R21" s="1">
-        <v>26180</v>
+        <v>31917.3</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -1699,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
         <v>0</v>
@@ -1711,48 +2227,48 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="G22" s="1">
-        <v>57.7</v>
+        <v>94.8</v>
       </c>
       <c r="H22" t="s">
         <v>2</v>
       </c>
       <c r="I22" s="1">
-        <v>44.02</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>8.26</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>55</v>
+        <v>109.9</v>
       </c>
       <c r="L22" s="1">
-        <v>55.45</v>
+        <v>110</v>
       </c>
       <c r="M22" s="1">
-        <v>26.99</v>
+        <v>-3020</v>
       </c>
       <c r="N22" s="1">
-        <v>4.9000000000000004</v>
+        <v>-13.73</v>
       </c>
       <c r="O22" s="1">
-        <v>22.5</v>
+        <v>-3039.78</v>
       </c>
       <c r="P22" s="1">
-        <v>4.05</v>
+        <v>-13.81</v>
       </c>
       <c r="Q22" s="1">
-        <v>577</v>
+        <v>18960</v>
       </c>
       <c r="R22" s="1">
-        <v>577</v>
+        <v>18960</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1">
-        <v>0.03</v>
+        <v>0.98</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -1766,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
         <v>0</v>
@@ -1778,48 +2294,48 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G23" s="1">
-        <v>3119</v>
+        <v>4012</v>
       </c>
       <c r="H23" t="s">
         <v>2</v>
       </c>
       <c r="I23" s="1">
-        <v>-191.43</v>
+        <v>-64.400000000000006</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.61</v>
+        <v>-0.32</v>
       </c>
       <c r="K23" s="1">
-        <v>2472</v>
+        <v>4481.99</v>
       </c>
       <c r="L23" s="1">
-        <v>2474.23</v>
+        <v>4486.0200000000004</v>
       </c>
       <c r="M23" s="1">
-        <v>6469.99</v>
+        <v>-2349.9299999999998</v>
       </c>
       <c r="N23" s="1">
-        <v>26.17</v>
+        <v>-10.48</v>
       </c>
       <c r="O23" s="1">
-        <v>6447.75</v>
+        <v>-2370.09</v>
       </c>
       <c r="P23" s="1">
-        <v>26.05</v>
+        <v>-10.56</v>
       </c>
       <c r="Q23" s="1">
-        <v>31190</v>
+        <v>20060</v>
       </c>
       <c r="R23" s="1">
-        <v>31190</v>
+        <v>20060</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -1833,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
         <v>0</v>
@@ -1844,51 +2360,55 @@
       <c r="E24" t="s">
         <v>0</v>
       </c>
-      <c r="F24" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G24" s="1">
-        <v>267.3</v>
+      <c r="F24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" s="1">
-        <v>2039.76</v>
-      </c>
-      <c r="J24" s="1">
-        <v>5.36</v>
-      </c>
-      <c r="K24" s="1">
-        <v>317.23</v>
-      </c>
-      <c r="L24" s="1">
-        <v>318.69</v>
-      </c>
-      <c r="M24" s="1">
-        <v>-7489.89</v>
-      </c>
-      <c r="N24" s="1">
-        <v>-15.74</v>
-      </c>
-      <c r="O24" s="1">
-        <v>-7707.98</v>
-      </c>
-      <c r="P24" s="1">
-        <v>-16.12</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>40095</v>
-      </c>
-      <c r="R24" s="1">
-        <v>40095</v>
-      </c>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1">
-        <v>1.98</v>
-      </c>
-      <c r="V24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>0</v>
+      </c>
+      <c r="L24" t="s">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>0</v>
+      </c>
+      <c r="P24" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>0</v>
+      </c>
+      <c r="S24" t="s">
+        <v>0</v>
+      </c>
+      <c r="T24" t="s">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>0</v>
+      </c>
+      <c r="V24" t="s">
         <v>0</v>
       </c>
       <c r="W24" t="s">
@@ -1900,10 +2420,10 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
         <v>0</v>
@@ -1911,51 +2431,55 @@
       <c r="E25" t="s">
         <v>0</v>
       </c>
-      <c r="F25" s="1">
-        <v>1350</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2440</v>
+      <c r="F25" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>2</v>
-      </c>
-      <c r="I25" s="1">
-        <v>-215.51</v>
-      </c>
-      <c r="J25" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="K25" s="1">
-        <v>2575.86</v>
-      </c>
-      <c r="L25" s="1">
-        <v>2758.41</v>
-      </c>
-      <c r="M25" s="1">
-        <v>-1834.03</v>
-      </c>
-      <c r="N25" s="1">
-        <v>-5.27</v>
-      </c>
-      <c r="O25" s="1">
-        <v>-4298.4799999999996</v>
-      </c>
-      <c r="P25" s="1">
-        <v>-11.54</v>
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>0</v>
+      </c>
+      <c r="P25" t="s">
+        <v>0</v>
       </c>
       <c r="Q25" s="1">
-        <v>32940</v>
-      </c>
-      <c r="R25" s="1">
-        <v>32940</v>
-      </c>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="V25" s="1">
+        <v>549781.69999999995</v>
+      </c>
+      <c r="R25" t="s">
+        <v>0</v>
+      </c>
+      <c r="S25" t="s">
+        <v>0</v>
+      </c>
+      <c r="T25" t="s">
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>0</v>
+      </c>
+      <c r="V25" t="s">
         <v>0</v>
       </c>
       <c r="W25" t="s">
@@ -1967,10 +2491,10 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
         <v>0</v>
@@ -1978,51 +2502,55 @@
       <c r="E26" t="s">
         <v>0</v>
       </c>
-      <c r="F26" s="1">
-        <v>700</v>
-      </c>
-      <c r="G26" s="1">
-        <v>4673</v>
+      <c r="F26" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" s="1">
-        <v>-474.55</v>
-      </c>
-      <c r="J26" s="1">
-        <v>-1.43</v>
-      </c>
-      <c r="K26" s="1">
-        <v>5547.95</v>
-      </c>
-      <c r="L26" s="1">
-        <v>5657.95</v>
-      </c>
-      <c r="M26" s="1">
-        <v>-6124.68</v>
-      </c>
-      <c r="N26" s="1">
-        <v>-15.77</v>
-      </c>
-      <c r="O26" s="1">
-        <v>-6894.62</v>
-      </c>
-      <c r="P26" s="1">
-        <v>-17.399999999999999</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>32711</v>
-      </c>
-      <c r="R26" s="1">
-        <v>32711</v>
-      </c>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="V26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>0</v>
+      </c>
+      <c r="P26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>0</v>
+      </c>
+      <c r="R26" t="s">
+        <v>0</v>
+      </c>
+      <c r="S26" t="s">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
+        <v>0</v>
+      </c>
+      <c r="U26" t="s">
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
         <v>0</v>
       </c>
       <c r="W26" t="s">
@@ -2034,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D27" t="s">
         <v>0</v>
@@ -2045,51 +2573,55 @@
       <c r="E27" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="1">
-        <v>2900</v>
-      </c>
-      <c r="G27" s="1">
-        <v>755.6</v>
+      <c r="F27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" s="1">
-        <v>-203.47</v>
-      </c>
-      <c r="J27" s="1">
-        <v>-0.92</v>
-      </c>
-      <c r="K27" s="1">
-        <v>998</v>
-      </c>
-      <c r="L27" s="1">
-        <v>998.9</v>
-      </c>
-      <c r="M27" s="1">
-        <v>-7029.6</v>
-      </c>
-      <c r="N27" s="1">
-        <v>-24.28</v>
-      </c>
-      <c r="O27" s="1">
-        <v>-7055.65</v>
-      </c>
-      <c r="P27" s="1">
-        <v>-24.35</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>21912.400000000001</v>
-      </c>
-      <c r="R27" s="1">
-        <v>21912.400000000001</v>
-      </c>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="V27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>0</v>
+      </c>
+      <c r="P27" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
+        <v>0</v>
+      </c>
+      <c r="S27" t="s">
+        <v>0</v>
+      </c>
+      <c r="T27" t="s">
+        <v>0</v>
+      </c>
+      <c r="U27" t="s">
+        <v>0</v>
+      </c>
+      <c r="V27" t="s">
         <v>0</v>
       </c>
       <c r="W27" t="s">
@@ -2101,10 +2633,10 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
         <v>0</v>
@@ -2113,48 +2645,48 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>252849</v>
+        <v>30000</v>
       </c>
       <c r="G28" s="1">
-        <v>32</v>
+        <v>121.84</v>
       </c>
       <c r="H28" t="s">
         <v>2</v>
       </c>
       <c r="I28" s="1">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="K28" s="1">
-        <v>40</v>
+        <v>120.64</v>
       </c>
       <c r="L28" s="1">
-        <v>40.04</v>
+        <v>120.76</v>
       </c>
       <c r="M28" s="1">
-        <v>-20217.8</v>
+        <v>360.11</v>
       </c>
       <c r="N28" s="1">
-        <v>-19.989999999999998</v>
+        <v>0.99</v>
       </c>
       <c r="O28" s="1">
-        <v>-20315.07</v>
+        <v>323.23</v>
       </c>
       <c r="P28" s="1">
-        <v>-20.059999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q28" s="1">
-        <v>80911.679999999993</v>
+        <v>36552</v>
       </c>
       <c r="R28" s="1">
-        <v>80911.679999999993</v>
+        <v>36552</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1">
-        <v>4</v>
+        <v>1.88</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
@@ -2168,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
         <v>0</v>
@@ -2180,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>20000</v>
+        <v>75688.77</v>
       </c>
       <c r="G29" s="1">
-        <v>94.8</v>
+        <v>88.7</v>
       </c>
       <c r="H29" t="s">
         <v>2</v>
@@ -2195,33 +2727,33 @@
         <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>109.9</v>
+        <v>74.53</v>
       </c>
       <c r="L29" s="1">
-        <v>110</v>
+        <v>81.37</v>
       </c>
       <c r="M29" s="1">
-        <v>-3020</v>
+        <v>10729.03</v>
       </c>
       <c r="N29" s="1">
-        <v>-13.73</v>
+        <v>19.02</v>
       </c>
       <c r="O29" s="1">
-        <v>-3039.78</v>
+        <v>5548.02</v>
       </c>
       <c r="P29" s="1">
-        <v>-13.81</v>
+        <v>9</v>
       </c>
       <c r="Q29" s="1">
-        <v>18960</v>
+        <v>67135.94</v>
       </c>
       <c r="R29" s="1">
-        <v>18960</v>
+        <v>67135.94</v>
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1">
-        <v>0.94</v>
+        <v>3.46</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
@@ -2235,10 +2767,10 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -2247,48 +2779,48 @@
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <v>500</v>
+        <v>50000</v>
       </c>
       <c r="G30" s="1">
-        <v>4167</v>
+        <v>103.28</v>
       </c>
       <c r="H30" t="s">
         <v>2</v>
       </c>
       <c r="I30" s="1">
-        <v>-651.03</v>
+        <v>-463.72</v>
       </c>
       <c r="J30" s="1">
-        <v>-3.03</v>
+        <v>-0.89</v>
       </c>
       <c r="K30" s="1">
-        <v>4481.99</v>
+        <v>99.28</v>
       </c>
       <c r="L30" s="1">
-        <v>4486.0200000000004</v>
+        <v>102.54</v>
       </c>
       <c r="M30" s="1">
-        <v>-1574.93</v>
+        <v>1998.69</v>
       </c>
       <c r="N30" s="1">
-        <v>-7.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="O30" s="1">
-        <v>-1595.09</v>
+        <v>371.4</v>
       </c>
       <c r="P30" s="1">
-        <v>-7.11</v>
+        <v>0.72</v>
       </c>
       <c r="Q30" s="1">
-        <v>20835</v>
+        <v>51640</v>
       </c>
       <c r="R30" s="1">
-        <v>20835</v>
+        <v>51640</v>
       </c>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -2302,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
         <v>0</v>
@@ -2313,55 +2845,51 @@
       <c r="E31" t="s">
         <v>0</v>
       </c>
-      <c r="F31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>0</v>
+      <c r="F31" s="1">
+        <v>25000</v>
+      </c>
+      <c r="G31" s="1">
+        <v>97.93</v>
       </c>
       <c r="H31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I31" t="s">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>0</v>
-      </c>
-      <c r="L31" t="s">
-        <v>0</v>
-      </c>
-      <c r="M31" t="s">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>0</v>
-      </c>
-      <c r="P31" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>0</v>
-      </c>
-      <c r="R31" t="s">
-        <v>0</v>
-      </c>
-      <c r="S31" t="s">
-        <v>0</v>
-      </c>
-      <c r="T31" t="s">
-        <v>0</v>
-      </c>
-      <c r="U31" t="s">
-        <v>0</v>
-      </c>
-      <c r="V31" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1">
+        <v>-108.2</v>
+      </c>
+      <c r="J31" s="1">
+        <v>-0.44</v>
+      </c>
+      <c r="K31" s="1">
+        <v>97.53</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100.91</v>
+      </c>
+      <c r="M31" s="1">
+        <v>100.97</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="O31" s="1">
+        <v>-745.47</v>
+      </c>
+      <c r="P31" s="1">
+        <v>-2.95</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>24482.5</v>
+      </c>
+      <c r="R31" s="1">
+        <v>24482.5</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="V31" s="1">
         <v>0</v>
       </c>
       <c r="W31" t="s">
@@ -2373,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
         <v>0</v>
@@ -2384,55 +2912,51 @@
       <c r="E32" t="s">
         <v>0</v>
       </c>
-      <c r="F32" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>0</v>
+      <c r="F32" s="1">
+        <v>80257.09</v>
+      </c>
+      <c r="G32" s="1">
+        <v>112.84</v>
       </c>
       <c r="H32" t="s">
-        <v>0</v>
-      </c>
-      <c r="I32" t="s">
-        <v>0</v>
-      </c>
-      <c r="J32" t="s">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
-        <v>0</v>
-      </c>
-      <c r="L32" t="s">
-        <v>0</v>
-      </c>
-      <c r="M32" t="s">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>0</v>
-      </c>
-      <c r="P32" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-18.12</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.02</v>
+      </c>
+      <c r="K32" s="1">
+        <v>94.06</v>
+      </c>
+      <c r="L32" s="1">
+        <v>99.76</v>
+      </c>
+      <c r="M32" s="1">
+        <v>15069.31</v>
+      </c>
+      <c r="N32" s="1">
+        <v>19.96</v>
+      </c>
+      <c r="O32" s="1">
+        <v>10500.75</v>
+      </c>
+      <c r="P32" s="1">
+        <v>13.11</v>
       </c>
       <c r="Q32" s="1">
-        <v>563426.4</v>
-      </c>
-      <c r="R32" t="s">
-        <v>0</v>
-      </c>
-      <c r="S32" t="s">
-        <v>0</v>
-      </c>
-      <c r="T32" t="s">
-        <v>0</v>
-      </c>
-      <c r="U32" t="s">
-        <v>0</v>
-      </c>
-      <c r="V32" t="s">
+        <v>90562.1</v>
+      </c>
+      <c r="R32" s="1">
+        <v>90562.1</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1">
+        <v>4.67</v>
+      </c>
+      <c r="V32" s="1">
         <v>0</v>
       </c>
       <c r="W32" t="s">
@@ -2444,10 +2968,10 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>0</v>
@@ -2455,55 +2979,51 @@
       <c r="E33" t="s">
         <v>0</v>
       </c>
-      <c r="F33" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>0</v>
+      <c r="F33" s="1">
+        <v>23000</v>
+      </c>
+      <c r="G33" s="1">
+        <v>121.62</v>
       </c>
       <c r="H33" t="s">
-        <v>0</v>
-      </c>
-      <c r="I33" t="s">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
-        <v>0</v>
-      </c>
-      <c r="L33" t="s">
-        <v>0</v>
-      </c>
-      <c r="M33" t="s">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>0</v>
-      </c>
-      <c r="P33" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>0</v>
-      </c>
-      <c r="R33" t="s">
-        <v>0</v>
-      </c>
-      <c r="S33" t="s">
-        <v>0</v>
-      </c>
-      <c r="T33" t="s">
-        <v>0</v>
-      </c>
-      <c r="U33" t="s">
-        <v>0</v>
-      </c>
-      <c r="V33" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>-2.8</v>
+      </c>
+      <c r="J33" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="K33" s="1">
+        <v>120.19</v>
+      </c>
+      <c r="L33" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="M33" s="1">
+        <v>328.89</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="O33" s="1">
+        <v>304.02</v>
+      </c>
+      <c r="P33" s="1">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>27972.6</v>
+      </c>
+      <c r="R33" s="1">
+        <v>27972.6</v>
+      </c>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="V33" s="1">
         <v>0</v>
       </c>
       <c r="W33" t="s">
@@ -2515,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
         <v>0</v>
@@ -2526,55 +3046,51 @@
       <c r="E34" t="s">
         <v>0</v>
       </c>
-      <c r="F34" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>0</v>
+      <c r="F34" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G34" s="1">
+        <v>91.32</v>
       </c>
       <c r="H34" t="s">
-        <v>0</v>
-      </c>
-      <c r="I34" t="s">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
-        <v>0</v>
-      </c>
-      <c r="L34" t="s">
-        <v>0</v>
-      </c>
-      <c r="M34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>0</v>
-      </c>
-      <c r="P34" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>0</v>
-      </c>
-      <c r="R34" t="s">
-        <v>0</v>
-      </c>
-      <c r="S34" t="s">
-        <v>0</v>
-      </c>
-      <c r="T34" t="s">
-        <v>0</v>
-      </c>
-      <c r="U34" t="s">
-        <v>0</v>
-      </c>
-      <c r="V34" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" s="1">
+        <v>-128.03</v>
+      </c>
+      <c r="J34" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="K34" s="1">
+        <v>74.83</v>
+      </c>
+      <c r="L34" s="1">
+        <v>82.14</v>
+      </c>
+      <c r="M34" s="1">
+        <v>16492.490000000002</v>
+      </c>
+      <c r="N34" s="1">
+        <v>22.04</v>
+      </c>
+      <c r="O34" s="1">
+        <v>9177.93</v>
+      </c>
+      <c r="P34" s="1">
+        <v>11.17</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>91320</v>
+      </c>
+      <c r="R34" s="1">
+        <v>91320</v>
+      </c>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="V34" s="1">
         <v>0</v>
       </c>
       <c r="W34" t="s">
@@ -2586,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
         <v>0</v>
@@ -2598,48 +3114,48 @@
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="G35" s="1">
-        <v>121.73</v>
+        <v>100.17</v>
       </c>
       <c r="H35" t="s">
         <v>2</v>
       </c>
       <c r="I35" s="1">
-        <v>25.55</v>
+        <v>-299.48</v>
       </c>
       <c r="J35" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>-0.66</v>
       </c>
       <c r="K35" s="1">
-        <v>120.64</v>
+        <v>102.23</v>
       </c>
       <c r="L35" s="1">
-        <v>120.76</v>
+        <v>102.33</v>
       </c>
       <c r="M35" s="1">
-        <v>327.11</v>
+        <v>-928.48</v>
       </c>
       <c r="N35" s="1">
-        <v>0.9</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="O35" s="1">
-        <v>290.23</v>
+        <v>-969.9</v>
       </c>
       <c r="P35" s="1">
-        <v>0.8</v>
+        <v>-2.1</v>
       </c>
       <c r="Q35" s="1">
-        <v>36519</v>
+        <v>45076.5</v>
       </c>
       <c r="R35" s="1">
-        <v>36519</v>
+        <v>45076.5</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1">
-        <v>1.8</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -2653,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>0</v>
@@ -2665,48 +3181,48 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>75688.77</v>
+        <v>30000</v>
       </c>
       <c r="G36" s="1">
-        <v>89.74</v>
+        <v>99.8</v>
       </c>
       <c r="H36" t="s">
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>74.53</v>
+        <v>99</v>
       </c>
       <c r="L36" s="1">
-        <v>81.37</v>
+        <v>99.09</v>
       </c>
       <c r="M36" s="1">
-        <v>11516.19</v>
+        <v>239.99</v>
       </c>
       <c r="N36" s="1">
-        <v>20.41</v>
+        <v>0.8</v>
       </c>
       <c r="O36" s="1">
-        <v>6335.18</v>
+        <v>213.27</v>
       </c>
       <c r="P36" s="1">
-        <v>10.28</v>
+        <v>0.71</v>
       </c>
       <c r="Q36" s="1">
-        <v>67923.100000000006</v>
+        <v>29940</v>
       </c>
       <c r="R36" s="1">
-        <v>67923.100000000006</v>
+        <v>29940</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1">
-        <v>3.36</v>
+        <v>1.54</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -2720,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
         <v>0</v>
@@ -2732,48 +3248,48 @@
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>50000</v>
+        <v>25133</v>
       </c>
       <c r="G37" s="1">
-        <v>104.89</v>
+        <v>100.42</v>
       </c>
       <c r="H37" t="s">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>94.23</v>
+        <v>-91.19</v>
       </c>
       <c r="J37" s="1">
-        <v>0.18</v>
+        <v>-0.36</v>
       </c>
       <c r="K37" s="1">
-        <v>99.28</v>
+        <v>97.53</v>
       </c>
       <c r="L37" s="1">
-        <v>102.54</v>
+        <v>99.56</v>
       </c>
       <c r="M37" s="1">
-        <v>2803.69</v>
+        <v>726.79</v>
       </c>
       <c r="N37" s="1">
-        <v>5.64</v>
+        <v>2.96</v>
       </c>
       <c r="O37" s="1">
-        <v>1176.4000000000001</v>
+        <v>216.26</v>
       </c>
       <c r="P37" s="1">
-        <v>2.29</v>
+        <v>0.86</v>
       </c>
       <c r="Q37" s="1">
-        <v>52445</v>
+        <v>25238.560000000001</v>
       </c>
       <c r="R37" s="1">
-        <v>52445</v>
+        <v>25238.560000000001</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1">
-        <v>2.59</v>
+        <v>1.3</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
@@ -2787,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>0</v>
@@ -2799,48 +3315,48 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="G38" s="1">
-        <v>98.75</v>
+        <v>98.1</v>
       </c>
       <c r="H38" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="1">
-        <v>0</v>
+        <v>78.319999999999993</v>
       </c>
       <c r="J38" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K38" s="1">
-        <v>97.53</v>
+        <v>84.49</v>
       </c>
       <c r="L38" s="1">
-        <v>100.91</v>
+        <v>94.72</v>
       </c>
       <c r="M38" s="1">
-        <v>305.97000000000003</v>
+        <v>5443.63</v>
       </c>
       <c r="N38" s="1">
-        <v>1.25</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="O38" s="1">
-        <v>-540.47</v>
+        <v>1352.16</v>
       </c>
       <c r="P38" s="1">
-        <v>-2.14</v>
+        <v>3.56</v>
       </c>
       <c r="Q38" s="1">
-        <v>24687.5</v>
+        <v>39240</v>
       </c>
       <c r="R38" s="1">
-        <v>24687.5</v>
+        <v>39240</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -2854,10 +3370,10 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
         <v>0</v>
@@ -2866,48 +3382,48 @@
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>80257.09</v>
+        <v>41667.919999999998</v>
       </c>
       <c r="G39" s="1">
-        <v>112.82</v>
+        <v>110.16</v>
       </c>
       <c r="H39" t="s">
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>117.56</v>
+        <v>13.77</v>
       </c>
       <c r="J39" s="1">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="K39" s="1">
-        <v>94.06</v>
+        <v>107.93</v>
       </c>
       <c r="L39" s="1">
-        <v>99.76</v>
+        <v>108.14</v>
       </c>
       <c r="M39" s="1">
-        <v>15053.26</v>
+        <v>931.02</v>
       </c>
       <c r="N39" s="1">
-        <v>19.93</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="O39" s="1">
-        <v>10484.700000000001</v>
+        <v>842.84</v>
       </c>
       <c r="P39" s="1">
-        <v>13.09</v>
+        <v>1.87</v>
       </c>
       <c r="Q39" s="1">
-        <v>90546.05</v>
+        <v>45901.38</v>
       </c>
       <c r="R39" s="1">
-        <v>90546.05</v>
+        <v>45901.38</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <v>4.47</v>
+        <v>2.36</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -2921,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
         <v>0</v>
@@ -2933,48 +3449,48 @@
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>23000</v>
+        <v>61602</v>
       </c>
       <c r="G40" s="1">
-        <v>121.42</v>
+        <v>95.42</v>
       </c>
       <c r="H40" t="s">
         <v>2</v>
       </c>
       <c r="I40" s="1">
-        <v>16.75</v>
+        <v>70.45</v>
       </c>
       <c r="J40" s="1">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="K40" s="1">
-        <v>120.19</v>
+        <v>86.1</v>
       </c>
       <c r="L40" s="1">
-        <v>120.3</v>
+        <v>88.3</v>
       </c>
       <c r="M40" s="1">
-        <v>282.89</v>
+        <v>5740.25</v>
       </c>
       <c r="N40" s="1">
-        <v>1.02</v>
+        <v>10.82</v>
       </c>
       <c r="O40" s="1">
-        <v>258.02</v>
+        <v>4383.8599999999997</v>
       </c>
       <c r="P40" s="1">
-        <v>0.93</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="Q40" s="1">
-        <v>27926.6</v>
+        <v>58780.63</v>
       </c>
       <c r="R40" s="1">
-        <v>27926.6</v>
+        <v>58780.63</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1">
-        <v>1.38</v>
+        <v>3.03</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
@@ -2988,10 +3504,10 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
         <v>0</v>
@@ -3000,48 +3516,48 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>100000</v>
+        <v>57435.9</v>
       </c>
       <c r="G41" s="1">
-        <v>92.41</v>
+        <v>119.63</v>
       </c>
       <c r="H41" t="s">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>-9.24</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>74.83</v>
+        <v>106.92</v>
       </c>
       <c r="L41" s="1">
-        <v>82.14</v>
+        <v>110.63</v>
       </c>
       <c r="M41" s="1">
-        <v>17582.490000000002</v>
+        <v>7299.81</v>
       </c>
       <c r="N41" s="1">
-        <v>23.49</v>
+        <v>11.88</v>
       </c>
       <c r="O41" s="1">
-        <v>10267.93</v>
+        <v>5166.88</v>
       </c>
       <c r="P41" s="1">
-        <v>12.5</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="Q41" s="1">
-        <v>92410</v>
+        <v>68710.570000000007</v>
       </c>
       <c r="R41" s="1">
-        <v>92410</v>
+        <v>68710.570000000007</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1">
-        <v>4.57</v>
+        <v>3.54</v>
       </c>
       <c r="V41" s="1">
         <v>0</v>
@@ -3055,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
         <v>0</v>
@@ -3070,45 +3586,45 @@
         <v>45000</v>
       </c>
       <c r="G42" s="1">
-        <v>100.5</v>
+        <v>103.67</v>
       </c>
       <c r="H42" t="s">
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <v>500.91</v>
+        <v>-46.7</v>
       </c>
       <c r="J42" s="1">
-        <v>1.1200000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="K42" s="1">
-        <v>102.23</v>
+        <v>101.08</v>
       </c>
       <c r="L42" s="1">
-        <v>102.33</v>
+        <v>106.6</v>
       </c>
       <c r="M42" s="1">
-        <v>-779.98</v>
+        <v>1166.48</v>
       </c>
       <c r="N42" s="1">
-        <v>-1.69</v>
+        <v>2.56</v>
       </c>
       <c r="O42" s="1">
-        <v>-821.4</v>
+        <v>-1316.62</v>
       </c>
       <c r="P42" s="1">
-        <v>-1.78</v>
+        <v>-2.74</v>
       </c>
       <c r="Q42" s="1">
-        <v>45225</v>
+        <v>46651.5</v>
       </c>
       <c r="R42" s="1">
-        <v>45225</v>
+        <v>46651.5</v>
       </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -3122,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
         <v>0</v>
@@ -3134,48 +3650,48 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="G43" s="1">
-        <v>100.4</v>
+        <v>121.85</v>
       </c>
       <c r="H43" t="s">
         <v>2</v>
       </c>
       <c r="I43" s="1">
-        <v>0</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="J43" s="1">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="K43" s="1">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="L43" s="1">
-        <v>99.09</v>
+        <v>121.13</v>
       </c>
       <c r="M43" s="1">
-        <v>419.99</v>
+        <v>203.99</v>
       </c>
       <c r="N43" s="1">
-        <v>1.41</v>
+        <v>0.7</v>
       </c>
       <c r="O43" s="1">
-        <v>393.27</v>
+        <v>173.41</v>
       </c>
       <c r="P43" s="1">
-        <v>1.32</v>
+        <v>0.59</v>
       </c>
       <c r="Q43" s="1">
-        <v>30120</v>
+        <v>29244</v>
       </c>
       <c r="R43" s="1">
-        <v>30120</v>
+        <v>29244</v>
       </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -3189,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D44" t="s">
         <v>0</v>
@@ -3200,51 +3716,55 @@
       <c r="E44" t="s">
         <v>0</v>
       </c>
-      <c r="F44" s="1">
-        <v>25133</v>
-      </c>
-      <c r="G44" s="1">
-        <v>100.92</v>
+      <c r="F44" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>2</v>
-      </c>
-      <c r="I44" s="1">
-        <v>35.46</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K44" s="1">
-        <v>97.53</v>
-      </c>
-      <c r="L44" s="1">
-        <v>99.56</v>
-      </c>
-      <c r="M44" s="1">
-        <v>852.46</v>
-      </c>
-      <c r="N44" s="1">
-        <v>3.47</v>
-      </c>
-      <c r="O44" s="1">
-        <v>341.92</v>
-      </c>
-      <c r="P44" s="1">
-        <v>1.36</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>25364.22</v>
-      </c>
-      <c r="R44" s="1">
-        <v>25364.22</v>
-      </c>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1">
-        <v>1.25</v>
-      </c>
-      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>0</v>
+      </c>
+      <c r="L44" t="s">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>0</v>
+      </c>
+      <c r="P44" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>0</v>
+      </c>
+      <c r="R44" t="s">
+        <v>0</v>
+      </c>
+      <c r="S44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
         <v>0</v>
       </c>
       <c r="W44" t="s">
@@ -3256,10 +3776,10 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D45" t="s">
         <v>0</v>
@@ -3267,51 +3787,55 @@
       <c r="E45" t="s">
         <v>0</v>
       </c>
-      <c r="F45" s="1">
-        <v>40000</v>
-      </c>
-      <c r="G45" s="1">
-        <v>96.6</v>
+      <c r="F45" t="s">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>2</v>
-      </c>
-      <c r="I45" s="1">
-        <v>161.61000000000001</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="K45" s="1">
-        <v>84.49</v>
-      </c>
-      <c r="L45" s="1">
-        <v>94.72</v>
-      </c>
-      <c r="M45" s="1">
-        <v>4843.63</v>
-      </c>
-      <c r="N45" s="1">
-        <v>14.33</v>
-      </c>
-      <c r="O45" s="1">
-        <v>752.16</v>
-      </c>
-      <c r="P45" s="1">
-        <v>1.98</v>
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>0</v>
+      </c>
+      <c r="P45" t="s">
+        <v>0</v>
       </c>
       <c r="Q45" s="1">
-        <v>38640</v>
-      </c>
-      <c r="R45" s="1">
-        <v>38640</v>
-      </c>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1">
-        <v>1.91</v>
-      </c>
-      <c r="V45" s="1">
+        <v>778448.28</v>
+      </c>
+      <c r="R45" t="s">
+        <v>0</v>
+      </c>
+      <c r="S45" t="s">
+        <v>0</v>
+      </c>
+      <c r="T45" t="s">
+        <v>0</v>
+      </c>
+      <c r="U45" t="s">
+        <v>0</v>
+      </c>
+      <c r="V45" t="s">
         <v>0</v>
       </c>
       <c r="W45" t="s">
@@ -3323,10 +3847,10 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="D46" t="s">
         <v>0</v>
@@ -3334,51 +3858,55 @@
       <c r="E46" t="s">
         <v>0</v>
       </c>
-      <c r="F46" s="1">
-        <v>41667.919999999998</v>
-      </c>
-      <c r="G46" s="1">
-        <v>110.2</v>
+      <c r="F46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I46" s="1">
-        <v>4.59</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="K46" s="1">
-        <v>107.93</v>
-      </c>
-      <c r="L46" s="1">
-        <v>108.14</v>
-      </c>
-      <c r="M46" s="1">
-        <v>947.69</v>
-      </c>
-      <c r="N46" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="O46" s="1">
-        <v>859.51</v>
-      </c>
-      <c r="P46" s="1">
-        <v>1.9</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>45918.05</v>
-      </c>
-      <c r="R46" s="1">
-        <v>45918.05</v>
-      </c>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1">
-        <v>2.27</v>
-      </c>
-      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>0</v>
+      </c>
+      <c r="P46" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>0</v>
+      </c>
+      <c r="R46" t="s">
+        <v>0</v>
+      </c>
+      <c r="S46" t="s">
+        <v>0</v>
+      </c>
+      <c r="T46" t="s">
+        <v>0</v>
+      </c>
+      <c r="U46" t="s">
+        <v>0</v>
+      </c>
+      <c r="V46" t="s">
         <v>0</v>
       </c>
       <c r="W46" t="s">
@@ -3390,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="D47" t="s">
         <v>0</v>
@@ -3401,51 +3929,55 @@
       <c r="E47" t="s">
         <v>0</v>
       </c>
-      <c r="F47" s="1">
-        <v>61602</v>
-      </c>
-      <c r="G47" s="1">
-        <v>96.6</v>
+      <c r="F47" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>2</v>
-      </c>
-      <c r="I47" s="1">
-        <v>-137.18</v>
-      </c>
-      <c r="J47" s="1">
-        <v>-0.23</v>
-      </c>
-      <c r="K47" s="1">
-        <v>86.1</v>
-      </c>
-      <c r="L47" s="1">
-        <v>88.3</v>
-      </c>
-      <c r="M47" s="1">
-        <v>6467.16</v>
-      </c>
-      <c r="N47" s="1">
-        <v>12.19</v>
-      </c>
-      <c r="O47" s="1">
-        <v>5110.76</v>
-      </c>
-      <c r="P47" s="1">
-        <v>9.39</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>59507.53</v>
-      </c>
-      <c r="R47" s="1">
-        <v>59507.53</v>
-      </c>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1">
-        <v>2.94</v>
-      </c>
-      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>0</v>
+      </c>
+      <c r="P47" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>0</v>
+      </c>
+      <c r="R47" t="s">
+        <v>0</v>
+      </c>
+      <c r="S47" t="s">
+        <v>0</v>
+      </c>
+      <c r="T47" t="s">
+        <v>0</v>
+      </c>
+      <c r="U47" t="s">
+        <v>0</v>
+      </c>
+      <c r="V47" t="s">
         <v>0</v>
       </c>
       <c r="W47" t="s">
@@ -3457,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
         <v>0</v>
@@ -3469,48 +4001,48 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>57435.9</v>
+        <v>41000</v>
       </c>
       <c r="G48" s="1">
-        <v>119.55</v>
+        <v>127.55</v>
       </c>
       <c r="H48" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" s="1">
-        <v>-6.87</v>
+        <v>12.44</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="K48" s="1">
-        <v>106.92</v>
+        <v>120.19</v>
       </c>
       <c r="L48" s="1">
-        <v>110.63</v>
+        <v>125.17</v>
       </c>
       <c r="M48" s="1">
-        <v>7253.86</v>
+        <v>9206.16</v>
       </c>
       <c r="N48" s="1">
-        <v>11.81</v>
+        <v>6.12</v>
       </c>
       <c r="O48" s="1">
-        <v>5120.93</v>
+        <v>2973.08</v>
       </c>
       <c r="P48" s="1">
-        <v>8.0500000000000007</v>
+        <v>1.9</v>
       </c>
       <c r="Q48" s="1">
-        <v>68664.62</v>
+        <v>159448.98000000001</v>
       </c>
       <c r="R48" s="1">
-        <v>68664.62</v>
+        <v>52295.5</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1">
-        <v>3.39</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
@@ -3524,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
         <v>0</v>
@@ -3536,48 +4068,48 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>45000</v>
+        <v>144000</v>
       </c>
       <c r="G49" s="1">
-        <v>104.46</v>
+        <v>106.33</v>
       </c>
       <c r="H49" t="s">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>4.7</v>
+        <v>14.39</v>
       </c>
       <c r="J49" s="1">
         <v>0.01</v>
       </c>
       <c r="K49" s="1">
-        <v>101.08</v>
+        <v>105.16</v>
       </c>
       <c r="L49" s="1">
-        <v>106.6</v>
+        <v>105.53</v>
       </c>
       <c r="M49" s="1">
-        <v>1521.98</v>
+        <v>1678.6</v>
       </c>
       <c r="N49" s="1">
-        <v>3.34</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O49" s="1">
-        <v>-961.12</v>
+        <v>1152</v>
       </c>
       <c r="P49" s="1">
-        <v>-2</v>
+        <v>0.75</v>
       </c>
       <c r="Q49" s="1">
-        <v>47007</v>
+        <v>153115.20000000001</v>
       </c>
       <c r="R49" s="1">
-        <v>47007</v>
+        <v>153115.20000000001</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1">
-        <v>2.3199999999999998</v>
+        <v>7.89</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -3591,10 +4123,10 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
         <v>0</v>
@@ -3603,48 +4135,48 @@
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="G50" s="1">
-        <v>119.2</v>
+        <v>108.45</v>
       </c>
       <c r="H50" t="s">
         <v>2</v>
       </c>
       <c r="I50" s="1">
-        <v>-14.31</v>
+        <v>3.59</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K50" s="1">
-        <v>109.11</v>
+        <v>108.45</v>
       </c>
       <c r="L50" s="1">
-        <v>111.45</v>
+        <v>108.45</v>
       </c>
       <c r="M50" s="1">
-        <v>4037.39</v>
+        <v>0</v>
       </c>
       <c r="N50" s="1">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
-        <v>3101.07</v>
+        <v>0</v>
       </c>
       <c r="P50" s="1">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="1">
-        <v>47680</v>
+        <v>19521</v>
       </c>
       <c r="R50" s="1">
-        <v>47680</v>
+        <v>19521</v>
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
@@ -3658,10 +4190,10 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D51" t="s">
         <v>0</v>
@@ -3669,51 +4201,55 @@
       <c r="E51" t="s">
         <v>0</v>
       </c>
-      <c r="F51" s="1">
-        <v>24000</v>
-      </c>
-      <c r="G51" s="1">
-        <v>121.8</v>
+      <c r="F51" t="s">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>2</v>
-      </c>
-      <c r="I51" s="1">
-        <v>23.37</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="K51" s="1">
-        <v>121</v>
-      </c>
-      <c r="L51" s="1">
-        <v>121.13</v>
-      </c>
-      <c r="M51" s="1">
-        <v>191.99</v>
-      </c>
-      <c r="N51" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="O51" s="1">
-        <v>161.41</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>29232</v>
-      </c>
-      <c r="R51" s="1">
-        <v>29232</v>
-      </c>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" t="s">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>0</v>
+      </c>
+      <c r="P51" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>0</v>
+      </c>
+      <c r="R51" t="s">
+        <v>0</v>
+      </c>
+      <c r="S51" t="s">
+        <v>0</v>
+      </c>
+      <c r="T51" t="s">
+        <v>0</v>
+      </c>
+      <c r="U51" t="s">
+        <v>0</v>
+      </c>
+      <c r="V51" t="s">
         <v>0</v>
       </c>
       <c r="W51" t="s">
@@ -3725,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -3769,8 +4305,8 @@
       <c r="P52" t="s">
         <v>0</v>
       </c>
-      <c r="Q52" t="s">
-        <v>0</v>
+      <c r="Q52" s="1">
+        <v>332085.18</v>
       </c>
       <c r="R52" t="s">
         <v>0</v>
@@ -3796,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
@@ -3840,8 +4376,8 @@
       <c r="P53" t="s">
         <v>0</v>
       </c>
-      <c r="Q53" s="1">
-        <v>829815.67</v>
+      <c r="Q53" t="s">
+        <v>0</v>
       </c>
       <c r="R53" t="s">
         <v>0</v>
@@ -3867,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
         <v>0</v>
@@ -3938,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C55" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
         <v>0</v>
@@ -3949,55 +4485,51 @@
       <c r="E55" t="s">
         <v>0</v>
       </c>
-      <c r="F55" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" t="s">
-        <v>0</v>
+      <c r="F55" s="1">
+        <v>703</v>
+      </c>
+      <c r="G55" s="1">
+        <v>39850</v>
       </c>
       <c r="H55" t="s">
-        <v>0</v>
-      </c>
-      <c r="I55" t="s">
-        <v>0</v>
-      </c>
-      <c r="J55" t="s">
-        <v>0</v>
-      </c>
-      <c r="K55" t="s">
-        <v>0</v>
-      </c>
-      <c r="L55" t="s">
-        <v>0</v>
-      </c>
-      <c r="M55" t="s">
-        <v>0</v>
-      </c>
-      <c r="N55" t="s">
-        <v>0</v>
-      </c>
-      <c r="O55" t="s">
-        <v>0</v>
-      </c>
-      <c r="P55" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>0</v>
-      </c>
-      <c r="R55" t="s">
-        <v>0</v>
-      </c>
-      <c r="S55" t="s">
-        <v>0</v>
-      </c>
-      <c r="T55" t="s">
-        <v>0</v>
-      </c>
-      <c r="U55" t="s">
-        <v>0</v>
-      </c>
-      <c r="V55" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1">
+        <v>-2316.19</v>
+      </c>
+      <c r="J55" s="1">
+        <v>-0.82</v>
+      </c>
+      <c r="K55" s="1">
+        <v>34092.879999999997</v>
+      </c>
+      <c r="L55" s="1">
+        <v>34168.11</v>
+      </c>
+      <c r="M55" s="1">
+        <v>40472.550000000003</v>
+      </c>
+      <c r="N55" s="1">
+        <v>16.88</v>
+      </c>
+      <c r="O55" s="1">
+        <v>39943.71</v>
+      </c>
+      <c r="P55" s="1">
+        <v>16.62</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>280145.5</v>
+      </c>
+      <c r="R55" s="1">
+        <v>280145.5</v>
+      </c>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1">
+        <v>14.43</v>
+      </c>
+      <c r="V55" s="1">
         <v>0</v>
       </c>
       <c r="W55" t="s">
@@ -4009,10 +4541,10 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C56" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -4020,51 +4552,55 @@
       <c r="E56" t="s">
         <v>0</v>
       </c>
-      <c r="F56" s="1">
-        <v>41000</v>
-      </c>
-      <c r="G56" s="1">
-        <v>127.46</v>
+      <c r="F56" t="s">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>3</v>
-      </c>
-      <c r="I56" s="1">
-        <v>24.49</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K56" s="1">
-        <v>120.19</v>
-      </c>
-      <c r="L56" s="1">
-        <v>125.17</v>
-      </c>
-      <c r="M56" s="1">
-        <v>8962.42</v>
-      </c>
-      <c r="N56" s="1">
-        <v>6.05</v>
-      </c>
-      <c r="O56" s="1">
-        <v>2819.29</v>
-      </c>
-      <c r="P56" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>157037.09</v>
-      </c>
-      <c r="R56" s="1">
-        <v>52258.6</v>
-      </c>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1">
-        <v>7.76</v>
-      </c>
-      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>0</v>
+      </c>
+      <c r="P56" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>0</v>
+      </c>
+      <c r="R56" t="s">
+        <v>0</v>
+      </c>
+      <c r="S56" t="s">
+        <v>0</v>
+      </c>
+      <c r="T56" t="s">
+        <v>0</v>
+      </c>
+      <c r="U56" t="s">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
         <v>0</v>
       </c>
       <c r="W56" t="s">
@@ -4076,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D57" t="s">
         <v>0</v>
@@ -4087,51 +4623,55 @@
       <c r="E57" t="s">
         <v>0</v>
       </c>
-      <c r="F57" s="1">
-        <v>144000</v>
-      </c>
-      <c r="G57" s="1">
-        <v>106.24</v>
+      <c r="F57" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>2</v>
-      </c>
-      <c r="I57" s="1">
-        <v>14.38</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="K57" s="1">
-        <v>105.16</v>
-      </c>
-      <c r="L57" s="1">
-        <v>105.53</v>
-      </c>
-      <c r="M57" s="1">
-        <v>1549</v>
-      </c>
-      <c r="N57" s="1">
-        <v>1.02</v>
-      </c>
-      <c r="O57" s="1">
-        <v>1022.4</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0.67</v>
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>0</v>
+      </c>
+      <c r="K57" t="s">
+        <v>0</v>
+      </c>
+      <c r="L57" t="s">
+        <v>0</v>
+      </c>
+      <c r="M57" t="s">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>0</v>
+      </c>
+      <c r="P57" t="s">
+        <v>0</v>
       </c>
       <c r="Q57" s="1">
-        <v>152985.60000000001</v>
-      </c>
-      <c r="R57" s="1">
-        <v>152985.60000000001</v>
-      </c>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1">
-        <v>7.56</v>
-      </c>
-      <c r="V57" s="1">
+        <v>280145.5</v>
+      </c>
+      <c r="R57" t="s">
+        <v>0</v>
+      </c>
+      <c r="S57" t="s">
+        <v>0</v>
+      </c>
+      <c r="T57" t="s">
+        <v>0</v>
+      </c>
+      <c r="U57" t="s">
+        <v>0</v>
+      </c>
+      <c r="V57" t="s">
         <v>0</v>
       </c>
       <c r="W57" t="s">
@@ -4143,10 +4683,10 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D58" t="s">
         <v>0</v>
@@ -4154,51 +4694,55 @@
       <c r="E58" t="s">
         <v>0</v>
       </c>
-      <c r="F58" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G58" s="1">
-        <v>108.37</v>
+      <c r="F58" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>2</v>
-      </c>
-      <c r="I58" s="1">
-        <v>5.98</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K58" s="1">
-        <v>108.37</v>
-      </c>
-      <c r="L58" s="1">
-        <v>108.37</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>32511</v>
-      </c>
-      <c r="R58" s="1">
-        <v>32511</v>
-      </c>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" t="s">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
+        <v>0</v>
+      </c>
+      <c r="M58" t="s">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>0</v>
+      </c>
+      <c r="P58" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>0</v>
+      </c>
+      <c r="R58" t="s">
+        <v>0</v>
+      </c>
+      <c r="S58" t="s">
+        <v>0</v>
+      </c>
+      <c r="T58" t="s">
+        <v>0</v>
+      </c>
+      <c r="U58" t="s">
+        <v>0</v>
+      </c>
+      <c r="V58" t="s">
         <v>0</v>
       </c>
       <c r="W58" t="s">
@@ -4210,7 +4754,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
         <v>0</v>
@@ -4281,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
@@ -4325,8 +4869,8 @@
       <c r="P60" t="s">
         <v>0</v>
       </c>
-      <c r="Q60" s="1">
-        <v>342533.69</v>
+      <c r="Q60" t="s">
+        <v>0</v>
       </c>
       <c r="R60" t="s">
         <v>0</v>
@@ -4352,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C61" t="s">
         <v>0</v>
@@ -4423,66 +4967,62 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="D62" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s">
         <v>0</v>
       </c>
-      <c r="F62" t="s">
-        <v>0</v>
-      </c>
-      <c r="G62" t="s">
-        <v>0</v>
+      <c r="F62" s="1">
+        <v>700</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.3</v>
       </c>
       <c r="H62" t="s">
-        <v>0</v>
-      </c>
-      <c r="I62" t="s">
-        <v>0</v>
-      </c>
-      <c r="J62" t="s">
-        <v>0</v>
-      </c>
-      <c r="K62" t="s">
-        <v>0</v>
-      </c>
-      <c r="L62" t="s">
-        <v>0</v>
-      </c>
-      <c r="M62" t="s">
-        <v>0</v>
-      </c>
-      <c r="N62" t="s">
-        <v>0</v>
-      </c>
-      <c r="O62" t="s">
-        <v>0</v>
-      </c>
-      <c r="P62" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>0</v>
-      </c>
-      <c r="R62" t="s">
-        <v>0</v>
-      </c>
-      <c r="S62" t="s">
-        <v>0</v>
-      </c>
-      <c r="T62" t="s">
-        <v>0</v>
-      </c>
-      <c r="U62" t="s">
-        <v>0</v>
-      </c>
-      <c r="V62" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="1">
+        <v>-17.5</v>
+      </c>
+      <c r="J62" s="1">
+        <v>-2.7</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="M62" s="1">
+        <v>-627.69000000000005</v>
+      </c>
+      <c r="N62" s="1">
+        <v>-49.84</v>
+      </c>
+      <c r="O62" s="1">
+        <v>-636.23</v>
+      </c>
+      <c r="P62" s="1">
+        <v>-50.18</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>631.54</v>
+      </c>
+      <c r="R62" s="1">
+        <v>207.13</v>
+      </c>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="V62" s="1">
         <v>0</v>
       </c>
       <c r="W62" t="s">
@@ -4494,10 +5034,10 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D63" t="s">
         <v>0</v>
@@ -4505,51 +5045,55 @@
       <c r="E63" t="s">
         <v>0</v>
       </c>
-      <c r="F63" s="1">
-        <v>703</v>
-      </c>
-      <c r="G63" s="1">
-        <v>40860</v>
+      <c r="F63" t="s">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>2</v>
-      </c>
-      <c r="I63" s="1">
-        <v>2251.46</v>
-      </c>
-      <c r="J63" s="1">
-        <v>0.79</v>
-      </c>
-      <c r="K63" s="1">
-        <v>34092.879999999997</v>
-      </c>
-      <c r="L63" s="1">
-        <v>34168.11</v>
-      </c>
-      <c r="M63" s="1">
-        <v>47572.85</v>
-      </c>
-      <c r="N63" s="1">
-        <v>19.84</v>
-      </c>
-      <c r="O63" s="1">
-        <v>47044.01</v>
-      </c>
-      <c r="P63" s="1">
-        <v>19.579999999999998</v>
-      </c>
-      <c r="Q63" s="1">
-        <v>287245.8</v>
-      </c>
-      <c r="R63" s="1">
-        <v>287245.8</v>
-      </c>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="1">
-        <v>14.19</v>
-      </c>
-      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>0</v>
+      </c>
+      <c r="J63" t="s">
+        <v>0</v>
+      </c>
+      <c r="K63" t="s">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>0</v>
+      </c>
+      <c r="M63" t="s">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>0</v>
+      </c>
+      <c r="O63" t="s">
+        <v>0</v>
+      </c>
+      <c r="P63" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>0</v>
+      </c>
+      <c r="R63" t="s">
+        <v>0</v>
+      </c>
+      <c r="S63" t="s">
+        <v>0</v>
+      </c>
+      <c r="T63" t="s">
+        <v>0</v>
+      </c>
+      <c r="U63" t="s">
+        <v>0</v>
+      </c>
+      <c r="V63" t="s">
         <v>0</v>
       </c>
       <c r="W63" t="s">
@@ -4561,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
         <v>0</v>
@@ -4605,8 +5149,8 @@
       <c r="P64" t="s">
         <v>0</v>
       </c>
-      <c r="Q64" t="s">
-        <v>0</v>
+      <c r="Q64" s="1">
+        <v>631.54</v>
       </c>
       <c r="R64" t="s">
         <v>0</v>
@@ -4632,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
         <v>0</v>
@@ -4774,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C67" t="s">
         <v>0</v>
@@ -4987,13 +5531,13 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" t="s">
         <v>109</v>
-      </c>
-      <c r="C70" t="s">
-        <v>110</v>
-      </c>
-      <c r="D70" t="s">
-        <v>111</v>
       </c>
       <c r="E70" t="s">
         <v>0</v>

--- a/holdings.xlsx
+++ b/holdings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\tase-ytm-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FDFA9B-003E-405D-B9CE-CE6272EA30EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB6845A-EE1E-4F3C-A46A-13344A0ADCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="110">
   <si>
     <t/>
   </si>
@@ -744,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -5171,570 +5171,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C65" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" t="s">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
-        <v>0</v>
-      </c>
-      <c r="F65" t="s">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
-        <v>0</v>
-      </c>
-      <c r="H65" t="s">
-        <v>0</v>
-      </c>
-      <c r="I65" t="s">
-        <v>0</v>
-      </c>
-      <c r="J65" t="s">
-        <v>0</v>
-      </c>
-      <c r="K65" t="s">
-        <v>0</v>
-      </c>
-      <c r="L65" t="s">
-        <v>0</v>
-      </c>
-      <c r="M65" t="s">
-        <v>0</v>
-      </c>
-      <c r="N65" t="s">
-        <v>0</v>
-      </c>
-      <c r="O65" t="s">
-        <v>0</v>
-      </c>
-      <c r="P65" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>287245.8</v>
-      </c>
-      <c r="R65" t="s">
-        <v>0</v>
-      </c>
-      <c r="S65" t="s">
-        <v>0</v>
-      </c>
-      <c r="T65" t="s">
-        <v>0</v>
-      </c>
-      <c r="U65" t="s">
-        <v>0</v>
-      </c>
-      <c r="V65" t="s">
-        <v>0</v>
-      </c>
-      <c r="W65" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" t="s">
-        <v>0</v>
-      </c>
-      <c r="C66" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" t="s">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>0</v>
-      </c>
-      <c r="F66" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" t="s">
-        <v>0</v>
-      </c>
-      <c r="H66" t="s">
-        <v>0</v>
-      </c>
-      <c r="I66" t="s">
-        <v>0</v>
-      </c>
-      <c r="J66" t="s">
-        <v>0</v>
-      </c>
-      <c r="K66" t="s">
-        <v>0</v>
-      </c>
-      <c r="L66" t="s">
-        <v>0</v>
-      </c>
-      <c r="M66" t="s">
-        <v>0</v>
-      </c>
-      <c r="N66" t="s">
-        <v>0</v>
-      </c>
-      <c r="O66" t="s">
-        <v>0</v>
-      </c>
-      <c r="P66" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>0</v>
-      </c>
-      <c r="R66" t="s">
-        <v>0</v>
-      </c>
-      <c r="S66" t="s">
-        <v>0</v>
-      </c>
-      <c r="T66" t="s">
-        <v>0</v>
-      </c>
-      <c r="U66" t="s">
-        <v>0</v>
-      </c>
-      <c r="V66" t="s">
-        <v>0</v>
-      </c>
-      <c r="W66" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" t="s">
-        <v>106</v>
-      </c>
-      <c r="C67" t="s">
-        <v>0</v>
-      </c>
-      <c r="D67" t="s">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>0</v>
-      </c>
-      <c r="F67" t="s">
-        <v>0</v>
-      </c>
-      <c r="G67" t="s">
-        <v>0</v>
-      </c>
-      <c r="H67" t="s">
-        <v>0</v>
-      </c>
-      <c r="I67" t="s">
-        <v>0</v>
-      </c>
-      <c r="J67" t="s">
-        <v>0</v>
-      </c>
-      <c r="K67" t="s">
-        <v>0</v>
-      </c>
-      <c r="L67" t="s">
-        <v>0</v>
-      </c>
-      <c r="M67" t="s">
-        <v>0</v>
-      </c>
-      <c r="N67" t="s">
-        <v>0</v>
-      </c>
-      <c r="O67" t="s">
-        <v>0</v>
-      </c>
-      <c r="P67" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>0</v>
-      </c>
-      <c r="R67" t="s">
-        <v>0</v>
-      </c>
-      <c r="S67" t="s">
-        <v>0</v>
-      </c>
-      <c r="T67" t="s">
-        <v>0</v>
-      </c>
-      <c r="U67" t="s">
-        <v>0</v>
-      </c>
-      <c r="V67" t="s">
-        <v>0</v>
-      </c>
-      <c r="W67" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B68" t="s">
-        <v>0</v>
-      </c>
-      <c r="C68" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" t="s">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>0</v>
-      </c>
-      <c r="F68" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>0</v>
-      </c>
-      <c r="I68" t="s">
-        <v>0</v>
-      </c>
-      <c r="J68" t="s">
-        <v>0</v>
-      </c>
-      <c r="K68" t="s">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
-        <v>0</v>
-      </c>
-      <c r="M68" t="s">
-        <v>0</v>
-      </c>
-      <c r="N68" t="s">
-        <v>0</v>
-      </c>
-      <c r="O68" t="s">
-        <v>0</v>
-      </c>
-      <c r="P68" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>0</v>
-      </c>
-      <c r="R68" t="s">
-        <v>0</v>
-      </c>
-      <c r="S68" t="s">
-        <v>0</v>
-      </c>
-      <c r="T68" t="s">
-        <v>0</v>
-      </c>
-      <c r="U68" t="s">
-        <v>0</v>
-      </c>
-      <c r="V68" t="s">
-        <v>0</v>
-      </c>
-      <c r="W68" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B69" t="s">
-        <v>26</v>
-      </c>
-      <c r="C69" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69" t="s">
-        <v>0</v>
-      </c>
-      <c r="E69" t="s">
-        <v>0</v>
-      </c>
-      <c r="F69" t="s">
-        <v>0</v>
-      </c>
-      <c r="G69" t="s">
-        <v>0</v>
-      </c>
-      <c r="H69" t="s">
-        <v>0</v>
-      </c>
-      <c r="I69" t="s">
-        <v>0</v>
-      </c>
-      <c r="J69" t="s">
-        <v>0</v>
-      </c>
-      <c r="K69" t="s">
-        <v>0</v>
-      </c>
-      <c r="L69" t="s">
-        <v>0</v>
-      </c>
-      <c r="M69" t="s">
-        <v>0</v>
-      </c>
-      <c r="N69" t="s">
-        <v>0</v>
-      </c>
-      <c r="O69" t="s">
-        <v>0</v>
-      </c>
-      <c r="P69" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>0</v>
-      </c>
-      <c r="R69" t="s">
-        <v>0</v>
-      </c>
-      <c r="S69" t="s">
-        <v>0</v>
-      </c>
-      <c r="T69" t="s">
-        <v>0</v>
-      </c>
-      <c r="U69" t="s">
-        <v>0</v>
-      </c>
-      <c r="V69" t="s">
-        <v>0</v>
-      </c>
-      <c r="W69" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B70" t="s">
-        <v>107</v>
-      </c>
-      <c r="C70" t="s">
-        <v>108</v>
-      </c>
-      <c r="D70" t="s">
-        <v>109</v>
-      </c>
-      <c r="E70" t="s">
-        <v>0</v>
-      </c>
-      <c r="F70" s="1">
-        <v>700</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="H70" t="s">
-        <v>3</v>
-      </c>
-      <c r="I70" s="1">
-        <v>0</v>
-      </c>
-      <c r="J70" s="1">
-        <v>0</v>
-      </c>
-      <c r="K70" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="L70" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="M70" s="1">
-        <v>-555.74</v>
-      </c>
-      <c r="N70" s="1">
-        <v>-44.77</v>
-      </c>
-      <c r="O70" s="1">
-        <v>-564.15</v>
-      </c>
-      <c r="P70" s="1">
-        <v>-45.15</v>
-      </c>
-      <c r="Q70" s="1">
-        <v>685.32</v>
-      </c>
-      <c r="R70" s="1">
-        <v>228.06</v>
-      </c>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="V70" s="1">
-        <v>0</v>
-      </c>
-      <c r="W70" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H71" t="s">
-        <v>0</v>
-      </c>
-      <c r="I71" t="s">
-        <v>0</v>
-      </c>
-      <c r="J71" t="s">
-        <v>0</v>
-      </c>
-      <c r="K71" t="s">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
-        <v>0</v>
-      </c>
-      <c r="M71" t="s">
-        <v>0</v>
-      </c>
-      <c r="N71" t="s">
-        <v>0</v>
-      </c>
-      <c r="O71" t="s">
-        <v>0</v>
-      </c>
-      <c r="P71" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>0</v>
-      </c>
-      <c r="R71" t="s">
-        <v>0</v>
-      </c>
-      <c r="S71" t="s">
-        <v>0</v>
-      </c>
-      <c r="T71" t="s">
-        <v>0</v>
-      </c>
-      <c r="U71" t="s">
-        <v>0</v>
-      </c>
-      <c r="V71" t="s">
-        <v>0</v>
-      </c>
-      <c r="W71" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" t="s">
-        <v>59</v>
-      </c>
-      <c r="C72" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72" t="s">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
-        <v>0</v>
-      </c>
-      <c r="F72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I72" t="s">
-        <v>0</v>
-      </c>
-      <c r="J72" t="s">
-        <v>0</v>
-      </c>
-      <c r="K72" t="s">
-        <v>0</v>
-      </c>
-      <c r="L72" t="s">
-        <v>0</v>
-      </c>
-      <c r="M72" t="s">
-        <v>0</v>
-      </c>
-      <c r="N72" t="s">
-        <v>0</v>
-      </c>
-      <c r="O72" t="s">
-        <v>0</v>
-      </c>
-      <c r="P72" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="1">
-        <v>685.32</v>
-      </c>
-      <c r="R72" t="s">
-        <v>0</v>
-      </c>
-      <c r="S72" t="s">
-        <v>0</v>
-      </c>
-      <c r="T72" t="s">
-        <v>0</v>
-      </c>
-      <c r="U72" t="s">
-        <v>0</v>
-      </c>
-      <c r="V72" t="s">
-        <v>0</v>
-      </c>
-      <c r="W72" t="s">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/holdings.xlsx
+++ b/holdings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{184E01F8-0665-4996-B877-D3D3AF2263E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB6845A-EE1E-4F3C-A46A-13344A0ADCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="110">
   <si>
     <t/>
   </si>
@@ -293,12 +293,6 @@
   </si>
   <si>
     <t>1223452</t>
-  </si>
-  <si>
-    <t>202 פועלים אגח</t>
-  </si>
-  <si>
-    <t>1199850</t>
   </si>
   <si>
     <t>צור אגח י</t>
@@ -750,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:W72"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -777,33 +771,579 @@
     <col min="23" max="23" width="24.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="U5" s="1"/>
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>0</v>
+      </c>
+      <c r="W5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6" t="s">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>0</v>
+      </c>
+      <c r="W6" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C7" s="1"/>
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
+        <v>0</v>
+      </c>
+      <c r="W7" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C8" s="1"/>
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6433</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>-3679.3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-5.41</v>
+      </c>
+      <c r="K8" s="1">
+        <v>6620.52</v>
+      </c>
+      <c r="L8" s="1">
+        <v>6725.05</v>
+      </c>
+      <c r="M8" s="1">
+        <v>-1875.18</v>
+      </c>
+      <c r="N8" s="1">
+        <v>-2.83</v>
+      </c>
+      <c r="O8" s="1">
+        <v>-2920.48</v>
+      </c>
+      <c r="P8" s="1">
+        <v>-4.34</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>64330</v>
+      </c>
+      <c r="R8" s="1">
+        <v>64330</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1">
+        <v>3.31</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0</v>
+      </c>
+      <c r="W8" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>0</v>
@@ -811,55 +1351,51 @@
       <c r="E9" t="s">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>0</v>
+      <c r="F9" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2077</v>
       </c>
       <c r="H9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>0</v>
-      </c>
-      <c r="P9" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>0</v>
-      </c>
-      <c r="R9" t="s">
-        <v>0</v>
-      </c>
-      <c r="S9" t="s">
-        <v>0</v>
-      </c>
-      <c r="T9" t="s">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1">
+        <v>210.42</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1954.92</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2001.82</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1831.18</v>
+      </c>
+      <c r="N9" s="1">
+        <v>6.24</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1127.71</v>
+      </c>
+      <c r="P9" s="1">
+        <v>3.75</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>31155</v>
+      </c>
+      <c r="R9" s="1">
+        <v>31155</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="V9" s="1">
         <v>0</v>
       </c>
       <c r="W9" t="s">
@@ -867,74 +1403,74 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>24</v>
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>9000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>732</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-1440.66</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-2.14</v>
+      </c>
+      <c r="K10" s="1">
+        <v>629.78</v>
+      </c>
+      <c r="L10" s="1">
+        <v>673.72</v>
+      </c>
+      <c r="M10" s="1">
+        <v>9199.61</v>
+      </c>
+      <c r="N10" s="1">
+        <v>16.23</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5245.47</v>
+      </c>
+      <c r="P10" s="1">
+        <v>8.65</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>65880</v>
+      </c>
+      <c r="R10" s="1">
+        <v>65880</v>
+      </c>
+      <c r="S10" s="1">
+        <v>483.32</v>
+      </c>
+      <c r="T10" s="1">
+        <v>483.32</v>
+      </c>
+      <c r="U10" s="1">
+        <v>3.39</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
@@ -942,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>0</v>
@@ -953,55 +1489,51 @@
       <c r="E11" t="s">
         <v>0</v>
       </c>
-      <c r="F11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>0</v>
+      <c r="F11" s="1">
+        <v>85000</v>
+      </c>
+      <c r="G11" s="1">
+        <v>100.4</v>
       </c>
       <c r="H11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>0</v>
-      </c>
-      <c r="P11" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>0</v>
-      </c>
-      <c r="R11" t="s">
-        <v>0</v>
-      </c>
-      <c r="S11" t="s">
-        <v>0</v>
-      </c>
-      <c r="T11" t="s">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>508.99</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="K11" s="1">
+        <v>92.69</v>
+      </c>
+      <c r="L11" s="1">
+        <v>86</v>
+      </c>
+      <c r="M11" s="1">
+        <v>6551.28</v>
+      </c>
+      <c r="N11" s="1">
+        <v>8.31</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12240.77</v>
+      </c>
+      <c r="P11" s="1">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>85340</v>
+      </c>
+      <c r="R11" s="1">
+        <v>85340</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V11" s="1">
         <v>0</v>
       </c>
       <c r="W11" t="s">
@@ -1013,10 +1545,10 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>0</v>
@@ -1024,55 +1556,51 @@
       <c r="E12" t="s">
         <v>0</v>
       </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>0</v>
+      <c r="F12" s="1">
+        <v>172500</v>
+      </c>
+      <c r="G12" s="1">
+        <v>12.9</v>
       </c>
       <c r="H12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-862.18</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-3.73</v>
+      </c>
+      <c r="K12" s="1">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="L12" s="1">
+        <v>18.78</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-10101.42</v>
+      </c>
+      <c r="N12" s="1">
+        <v>-31.22</v>
+      </c>
+      <c r="O12" s="1">
+        <v>-10134.67</v>
+      </c>
+      <c r="P12" s="1">
+        <v>-31.29</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>22252.5</v>
+      </c>
+      <c r="R12" s="1">
+        <v>22252.5</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="V12" s="1">
         <v>0</v>
       </c>
       <c r="W12" t="s">
@@ -1084,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>0</v>
@@ -1095,55 +1623,51 @@
       <c r="E13" t="s">
         <v>0</v>
       </c>
-      <c r="F13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>0</v>
+      <c r="F13" s="1">
+        <v>293</v>
+      </c>
+      <c r="G13" s="1">
+        <v>11120</v>
       </c>
       <c r="H13" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>0</v>
-      </c>
-      <c r="P13" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>0</v>
-      </c>
-      <c r="R13" t="s">
-        <v>0</v>
-      </c>
-      <c r="S13" t="s">
-        <v>0</v>
-      </c>
-      <c r="T13" t="s">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>0</v>
-      </c>
-      <c r="V13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1">
+        <v>673.27</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2.11</v>
+      </c>
+      <c r="K13" s="1">
+        <v>19220.14</v>
+      </c>
+      <c r="L13" s="1">
+        <v>19264.77</v>
+      </c>
+      <c r="M13" s="1">
+        <v>-23733.41</v>
+      </c>
+      <c r="N13" s="1">
+        <v>-42.14</v>
+      </c>
+      <c r="O13" s="1">
+        <v>-23864.16</v>
+      </c>
+      <c r="P13" s="1">
+        <v>-42.27</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>32581.599999999999</v>
+      </c>
+      <c r="R13" s="1">
+        <v>32581.599999999999</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="V13" s="1">
         <v>0</v>
       </c>
       <c r="W13" t="s">
@@ -1155,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
         <v>0</v>
@@ -1166,55 +1690,51 @@
       <c r="E14" t="s">
         <v>0</v>
       </c>
-      <c r="F14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>0</v>
+      <c r="F14" s="1">
+        <v>2200</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1118</v>
       </c>
       <c r="H14" t="s">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>0</v>
-      </c>
-      <c r="M14" t="s">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>0</v>
-      </c>
-      <c r="P14" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>0</v>
-      </c>
-      <c r="R14" t="s">
-        <v>0</v>
-      </c>
-      <c r="S14" t="s">
-        <v>0</v>
-      </c>
-      <c r="T14" t="s">
-        <v>0</v>
-      </c>
-      <c r="U14" t="s">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1">
+        <v>308.45</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1374</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1375.24</v>
+      </c>
+      <c r="M14" s="1">
+        <v>-5632</v>
+      </c>
+      <c r="N14" s="1">
+        <v>-18.63</v>
+      </c>
+      <c r="O14" s="1">
+        <v>-5659.21</v>
+      </c>
+      <c r="P14" s="1">
+        <v>-18.7</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>24596</v>
+      </c>
+      <c r="R14" s="1">
+        <v>24596</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="V14" s="1">
         <v>0</v>
       </c>
       <c r="W14" t="s">
@@ -1226,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
         <v>0</v>
@@ -1238,48 +1758,48 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G15" s="1">
-        <v>6772</v>
+        <v>57.2</v>
       </c>
       <c r="H15" t="s">
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>124.82</v>
+        <v>32.99</v>
       </c>
       <c r="J15" s="1">
-        <v>0.37</v>
+        <v>6.12</v>
       </c>
       <c r="K15" s="1">
-        <v>6688</v>
+        <v>55</v>
       </c>
       <c r="L15" s="1">
-        <v>6694.02</v>
+        <v>55.45</v>
       </c>
       <c r="M15" s="1">
-        <v>419.99</v>
+        <v>22</v>
       </c>
       <c r="N15" s="1">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O15" s="1">
-        <v>389.9</v>
+        <v>17.5</v>
       </c>
       <c r="P15" s="1">
-        <v>1.1599999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" s="1">
-        <v>33860</v>
+        <v>572</v>
       </c>
       <c r="R15" s="1">
-        <v>33860</v>
+        <v>572</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1">
-        <v>1.67</v>
+        <v>0.03</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -1293,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
         <v>0</v>
@@ -1305,52 +1825,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G16" s="1">
-        <v>2029</v>
+        <v>3225</v>
       </c>
       <c r="H16" t="s">
         <v>2</v>
       </c>
       <c r="I16" s="1">
-        <v>405.4</v>
+        <v>2191.2800000000002</v>
       </c>
       <c r="J16" s="1">
-        <v>1.35</v>
+        <v>7.29</v>
       </c>
       <c r="K16" s="1">
-        <v>2000</v>
+        <v>2472</v>
       </c>
       <c r="L16" s="1">
-        <v>2001.82</v>
+        <v>2474.23</v>
       </c>
       <c r="M16" s="1">
-        <v>435</v>
+        <v>7529.99</v>
       </c>
       <c r="N16" s="1">
-        <v>1.45</v>
+        <v>30.46</v>
       </c>
       <c r="O16" s="1">
-        <v>407.71</v>
+        <v>7507.75</v>
       </c>
       <c r="P16" s="1">
-        <v>1.35</v>
+        <v>30.34</v>
       </c>
       <c r="Q16" s="1">
-        <v>30435</v>
+        <v>32250</v>
       </c>
       <c r="R16" s="1">
-        <v>30435</v>
-      </c>
-      <c r="S16" s="1">
-        <v>676.18</v>
-      </c>
-      <c r="T16" s="1">
-        <v>676.18</v>
-      </c>
+        <v>32250</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
       <c r="U16" s="1">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -1364,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
         <v>0</v>
@@ -1376,48 +1892,48 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="G17" s="1">
-        <v>716.8</v>
+        <v>234.8</v>
       </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
       <c r="I17" s="1">
-        <v>648.11</v>
+        <v>-781.23</v>
       </c>
       <c r="J17" s="1">
-        <v>1.53</v>
+        <v>-2.17</v>
       </c>
       <c r="K17" s="1">
-        <v>575.66999999999996</v>
+        <v>317.23</v>
       </c>
       <c r="L17" s="1">
-        <v>641.24</v>
+        <v>318.69</v>
       </c>
       <c r="M17" s="1">
-        <v>8467.61</v>
+        <v>-12364.89</v>
       </c>
       <c r="N17" s="1">
-        <v>24.51</v>
+        <v>-25.98</v>
       </c>
       <c r="O17" s="1">
-        <v>4533.3999999999996</v>
+        <v>-12582.98</v>
       </c>
       <c r="P17" s="1">
-        <v>11.78</v>
+        <v>-26.32</v>
       </c>
       <c r="Q17" s="1">
-        <v>43008</v>
+        <v>35220</v>
       </c>
       <c r="R17" s="1">
-        <v>43008</v>
+        <v>35220</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -1431,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
         <v>0</v>
@@ -1443,48 +1959,48 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>93000</v>
+        <v>1350</v>
       </c>
       <c r="G18" s="1">
-        <v>101.6</v>
+        <v>2231</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>-189.35</v>
+        <v>-298.08</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.2</v>
+        <v>-0.98</v>
       </c>
       <c r="K18" s="1">
-        <v>92.69</v>
+        <v>2575.86</v>
       </c>
       <c r="L18" s="1">
-        <v>89.42</v>
+        <v>2758.41</v>
       </c>
       <c r="M18" s="1">
-        <v>8283.8799999999992</v>
+        <v>-4655.54</v>
       </c>
       <c r="N18" s="1">
-        <v>9.6</v>
+        <v>-13.38</v>
       </c>
       <c r="O18" s="1">
-        <v>11330.2</v>
+        <v>-7119.98</v>
       </c>
       <c r="P18" s="1">
-        <v>13.62</v>
+        <v>-19.11</v>
       </c>
       <c r="Q18" s="1">
-        <v>94488</v>
+        <v>30118.5</v>
       </c>
       <c r="R18" s="1">
-        <v>94488</v>
+        <v>30118.5</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1">
-        <v>4.67</v>
+        <v>1.55</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -1498,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>0</v>
@@ -1510,48 +2026,48 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>172500</v>
+        <v>700</v>
       </c>
       <c r="G19" s="1">
-        <v>15.3</v>
+        <v>4780</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="1">
-        <v>343.84</v>
+        <v>-561.35</v>
       </c>
       <c r="J19" s="1">
-        <v>1.32</v>
+        <v>-1.65</v>
       </c>
       <c r="K19" s="1">
-        <v>18.760000000000002</v>
+        <v>5547.95</v>
       </c>
       <c r="L19" s="1">
-        <v>18.78</v>
+        <v>5657.95</v>
       </c>
       <c r="M19" s="1">
-        <v>-5961.42</v>
+        <v>-5375.68</v>
       </c>
       <c r="N19" s="1">
-        <v>-18.420000000000002</v>
+        <v>-13.84</v>
       </c>
       <c r="O19" s="1">
-        <v>-5994.67</v>
+        <v>-6145.62</v>
       </c>
       <c r="P19" s="1">
-        <v>-18.5</v>
+        <v>-15.51</v>
       </c>
       <c r="Q19" s="1">
-        <v>26392.5</v>
+        <v>33460</v>
       </c>
       <c r="R19" s="1">
-        <v>26392.5</v>
+        <v>33460</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -1565,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>0</v>
@@ -1577,48 +2093,48 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>293</v>
+        <v>2900</v>
       </c>
       <c r="G20" s="1">
-        <v>9874</v>
+        <v>727.2</v>
       </c>
       <c r="H20" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="1">
-        <v>-256.85000000000002</v>
+        <v>-152.94</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.88</v>
+        <v>-0.72</v>
       </c>
       <c r="K20" s="1">
-        <v>19220.14</v>
+        <v>998</v>
       </c>
       <c r="L20" s="1">
-        <v>19264.77</v>
+        <v>998.9</v>
       </c>
       <c r="M20" s="1">
-        <v>-27384.19</v>
+        <v>-7853.2</v>
       </c>
       <c r="N20" s="1">
-        <v>-48.62</v>
+        <v>-27.13</v>
       </c>
       <c r="O20" s="1">
-        <v>-27514.94</v>
+        <v>-7879.25</v>
       </c>
       <c r="P20" s="1">
-        <v>-48.74</v>
+        <v>-27.19</v>
       </c>
       <c r="Q20" s="1">
-        <v>28930.82</v>
+        <v>21088.799999999999</v>
       </c>
       <c r="R20" s="1">
-        <v>28930.82</v>
+        <v>21088.799999999999</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1">
-        <v>1.43</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -1632,10 +2148,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>0</v>
@@ -1644,48 +2160,48 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>2200</v>
+        <v>106391</v>
       </c>
       <c r="G21" s="1">
-        <v>1190</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <v>-20.96</v>
+        <v>3191.44</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.08</v>
+        <v>11.11</v>
       </c>
       <c r="K21" s="1">
-        <v>1374</v>
+        <v>39.97</v>
       </c>
       <c r="L21" s="1">
-        <v>1375.24</v>
+        <v>40.01</v>
       </c>
       <c r="M21" s="1">
-        <v>-4048</v>
+        <v>-10601.86</v>
       </c>
       <c r="N21" s="1">
-        <v>-13.39</v>
+        <v>-24.93</v>
       </c>
       <c r="O21" s="1">
-        <v>-4075.21</v>
+        <v>-69497.63</v>
       </c>
       <c r="P21" s="1">
-        <v>-13.46</v>
+        <v>-25</v>
       </c>
       <c r="Q21" s="1">
-        <v>26180</v>
+        <v>31917.3</v>
       </c>
       <c r="R21" s="1">
-        <v>26180</v>
+        <v>31917.3</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -1699,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
         <v>0</v>
@@ -1711,48 +2227,48 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="G22" s="1">
-        <v>57.7</v>
+        <v>94.8</v>
       </c>
       <c r="H22" t="s">
         <v>2</v>
       </c>
       <c r="I22" s="1">
-        <v>44.02</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>8.26</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>55</v>
+        <v>109.9</v>
       </c>
       <c r="L22" s="1">
-        <v>55.45</v>
+        <v>110</v>
       </c>
       <c r="M22" s="1">
-        <v>26.99</v>
+        <v>-3020</v>
       </c>
       <c r="N22" s="1">
-        <v>4.9000000000000004</v>
+        <v>-13.73</v>
       </c>
       <c r="O22" s="1">
-        <v>22.5</v>
+        <v>-3039.78</v>
       </c>
       <c r="P22" s="1">
-        <v>4.05</v>
+        <v>-13.81</v>
       </c>
       <c r="Q22" s="1">
-        <v>577</v>
+        <v>18960</v>
       </c>
       <c r="R22" s="1">
-        <v>577</v>
+        <v>18960</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1">
-        <v>0.03</v>
+        <v>0.98</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -1766,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
         <v>0</v>
@@ -1778,48 +2294,48 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G23" s="1">
-        <v>3119</v>
+        <v>4012</v>
       </c>
       <c r="H23" t="s">
         <v>2</v>
       </c>
       <c r="I23" s="1">
-        <v>-191.43</v>
+        <v>-64.400000000000006</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.61</v>
+        <v>-0.32</v>
       </c>
       <c r="K23" s="1">
-        <v>2472</v>
+        <v>4481.99</v>
       </c>
       <c r="L23" s="1">
-        <v>2474.23</v>
+        <v>4486.0200000000004</v>
       </c>
       <c r="M23" s="1">
-        <v>6469.99</v>
+        <v>-2349.9299999999998</v>
       </c>
       <c r="N23" s="1">
-        <v>26.17</v>
+        <v>-10.48</v>
       </c>
       <c r="O23" s="1">
-        <v>6447.75</v>
+        <v>-2370.09</v>
       </c>
       <c r="P23" s="1">
-        <v>26.05</v>
+        <v>-10.56</v>
       </c>
       <c r="Q23" s="1">
-        <v>31190</v>
+        <v>20060</v>
       </c>
       <c r="R23" s="1">
-        <v>31190</v>
+        <v>20060</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -1833,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
         <v>0</v>
@@ -1844,51 +2360,55 @@
       <c r="E24" t="s">
         <v>0</v>
       </c>
-      <c r="F24" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G24" s="1">
-        <v>267.3</v>
+      <c r="F24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" s="1">
-        <v>2039.76</v>
-      </c>
-      <c r="J24" s="1">
-        <v>5.36</v>
-      </c>
-      <c r="K24" s="1">
-        <v>317.23</v>
-      </c>
-      <c r="L24" s="1">
-        <v>318.69</v>
-      </c>
-      <c r="M24" s="1">
-        <v>-7489.89</v>
-      </c>
-      <c r="N24" s="1">
-        <v>-15.74</v>
-      </c>
-      <c r="O24" s="1">
-        <v>-7707.98</v>
-      </c>
-      <c r="P24" s="1">
-        <v>-16.12</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>40095</v>
-      </c>
-      <c r="R24" s="1">
-        <v>40095</v>
-      </c>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1">
-        <v>1.98</v>
-      </c>
-      <c r="V24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>0</v>
+      </c>
+      <c r="L24" t="s">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>0</v>
+      </c>
+      <c r="P24" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>0</v>
+      </c>
+      <c r="S24" t="s">
+        <v>0</v>
+      </c>
+      <c r="T24" t="s">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>0</v>
+      </c>
+      <c r="V24" t="s">
         <v>0</v>
       </c>
       <c r="W24" t="s">
@@ -1900,10 +2420,10 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
         <v>0</v>
@@ -1911,51 +2431,55 @@
       <c r="E25" t="s">
         <v>0</v>
       </c>
-      <c r="F25" s="1">
-        <v>1350</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2440</v>
+      <c r="F25" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>2</v>
-      </c>
-      <c r="I25" s="1">
-        <v>-215.51</v>
-      </c>
-      <c r="J25" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="K25" s="1">
-        <v>2575.86</v>
-      </c>
-      <c r="L25" s="1">
-        <v>2758.41</v>
-      </c>
-      <c r="M25" s="1">
-        <v>-1834.03</v>
-      </c>
-      <c r="N25" s="1">
-        <v>-5.27</v>
-      </c>
-      <c r="O25" s="1">
-        <v>-4298.4799999999996</v>
-      </c>
-      <c r="P25" s="1">
-        <v>-11.54</v>
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>0</v>
+      </c>
+      <c r="P25" t="s">
+        <v>0</v>
       </c>
       <c r="Q25" s="1">
-        <v>32940</v>
-      </c>
-      <c r="R25" s="1">
-        <v>32940</v>
-      </c>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="V25" s="1">
+        <v>549781.69999999995</v>
+      </c>
+      <c r="R25" t="s">
+        <v>0</v>
+      </c>
+      <c r="S25" t="s">
+        <v>0</v>
+      </c>
+      <c r="T25" t="s">
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>0</v>
+      </c>
+      <c r="V25" t="s">
         <v>0</v>
       </c>
       <c r="W25" t="s">
@@ -1967,10 +2491,10 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
         <v>0</v>
@@ -1978,51 +2502,55 @@
       <c r="E26" t="s">
         <v>0</v>
       </c>
-      <c r="F26" s="1">
-        <v>700</v>
-      </c>
-      <c r="G26" s="1">
-        <v>4673</v>
+      <c r="F26" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" s="1">
-        <v>-474.55</v>
-      </c>
-      <c r="J26" s="1">
-        <v>-1.43</v>
-      </c>
-      <c r="K26" s="1">
-        <v>5547.95</v>
-      </c>
-      <c r="L26" s="1">
-        <v>5657.95</v>
-      </c>
-      <c r="M26" s="1">
-        <v>-6124.68</v>
-      </c>
-      <c r="N26" s="1">
-        <v>-15.77</v>
-      </c>
-      <c r="O26" s="1">
-        <v>-6894.62</v>
-      </c>
-      <c r="P26" s="1">
-        <v>-17.399999999999999</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>32711</v>
-      </c>
-      <c r="R26" s="1">
-        <v>32711</v>
-      </c>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="V26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>0</v>
+      </c>
+      <c r="P26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>0</v>
+      </c>
+      <c r="R26" t="s">
+        <v>0</v>
+      </c>
+      <c r="S26" t="s">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
+        <v>0</v>
+      </c>
+      <c r="U26" t="s">
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
         <v>0</v>
       </c>
       <c r="W26" t="s">
@@ -2034,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D27" t="s">
         <v>0</v>
@@ -2045,51 +2573,55 @@
       <c r="E27" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="1">
-        <v>2900</v>
-      </c>
-      <c r="G27" s="1">
-        <v>755.6</v>
+      <c r="F27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" s="1">
-        <v>-203.47</v>
-      </c>
-      <c r="J27" s="1">
-        <v>-0.92</v>
-      </c>
-      <c r="K27" s="1">
-        <v>998</v>
-      </c>
-      <c r="L27" s="1">
-        <v>998.9</v>
-      </c>
-      <c r="M27" s="1">
-        <v>-7029.6</v>
-      </c>
-      <c r="N27" s="1">
-        <v>-24.28</v>
-      </c>
-      <c r="O27" s="1">
-        <v>-7055.65</v>
-      </c>
-      <c r="P27" s="1">
-        <v>-24.35</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>21912.400000000001</v>
-      </c>
-      <c r="R27" s="1">
-        <v>21912.400000000001</v>
-      </c>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="V27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>0</v>
+      </c>
+      <c r="P27" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
+        <v>0</v>
+      </c>
+      <c r="S27" t="s">
+        <v>0</v>
+      </c>
+      <c r="T27" t="s">
+        <v>0</v>
+      </c>
+      <c r="U27" t="s">
+        <v>0</v>
+      </c>
+      <c r="V27" t="s">
         <v>0</v>
       </c>
       <c r="W27" t="s">
@@ -2101,10 +2633,10 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
         <v>0</v>
@@ -2113,48 +2645,48 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>252849</v>
+        <v>30000</v>
       </c>
       <c r="G28" s="1">
-        <v>32</v>
+        <v>121.84</v>
       </c>
       <c r="H28" t="s">
         <v>2</v>
       </c>
       <c r="I28" s="1">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="K28" s="1">
-        <v>40</v>
+        <v>120.64</v>
       </c>
       <c r="L28" s="1">
-        <v>40.04</v>
+        <v>120.76</v>
       </c>
       <c r="M28" s="1">
-        <v>-20217.8</v>
+        <v>360.11</v>
       </c>
       <c r="N28" s="1">
-        <v>-19.989999999999998</v>
+        <v>0.99</v>
       </c>
       <c r="O28" s="1">
-        <v>-20315.07</v>
+        <v>323.23</v>
       </c>
       <c r="P28" s="1">
-        <v>-20.059999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q28" s="1">
-        <v>80911.679999999993</v>
+        <v>36552</v>
       </c>
       <c r="R28" s="1">
-        <v>80911.679999999993</v>
+        <v>36552</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1">
-        <v>4</v>
+        <v>1.88</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
@@ -2168,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
         <v>0</v>
@@ -2180,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>20000</v>
+        <v>75688.77</v>
       </c>
       <c r="G29" s="1">
-        <v>94.8</v>
+        <v>88.7</v>
       </c>
       <c r="H29" t="s">
         <v>2</v>
@@ -2195,33 +2727,33 @@
         <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>109.9</v>
+        <v>74.53</v>
       </c>
       <c r="L29" s="1">
-        <v>110</v>
+        <v>81.37</v>
       </c>
       <c r="M29" s="1">
-        <v>-3020</v>
+        <v>10729.03</v>
       </c>
       <c r="N29" s="1">
-        <v>-13.73</v>
+        <v>19.02</v>
       </c>
       <c r="O29" s="1">
-        <v>-3039.78</v>
+        <v>5548.02</v>
       </c>
       <c r="P29" s="1">
-        <v>-13.81</v>
+        <v>9</v>
       </c>
       <c r="Q29" s="1">
-        <v>18960</v>
+        <v>67135.94</v>
       </c>
       <c r="R29" s="1">
-        <v>18960</v>
+        <v>67135.94</v>
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1">
-        <v>0.94</v>
+        <v>3.46</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
@@ -2235,10 +2767,10 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -2247,48 +2779,48 @@
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <v>500</v>
+        <v>50000</v>
       </c>
       <c r="G30" s="1">
-        <v>4167</v>
+        <v>103.28</v>
       </c>
       <c r="H30" t="s">
         <v>2</v>
       </c>
       <c r="I30" s="1">
-        <v>-651.03</v>
+        <v>-463.72</v>
       </c>
       <c r="J30" s="1">
-        <v>-3.03</v>
+        <v>-0.89</v>
       </c>
       <c r="K30" s="1">
-        <v>4481.99</v>
+        <v>99.28</v>
       </c>
       <c r="L30" s="1">
-        <v>4486.0200000000004</v>
+        <v>102.54</v>
       </c>
       <c r="M30" s="1">
-        <v>-1574.93</v>
+        <v>1998.69</v>
       </c>
       <c r="N30" s="1">
-        <v>-7.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="O30" s="1">
-        <v>-1595.09</v>
+        <v>371.4</v>
       </c>
       <c r="P30" s="1">
-        <v>-7.11</v>
+        <v>0.72</v>
       </c>
       <c r="Q30" s="1">
-        <v>20835</v>
+        <v>51640</v>
       </c>
       <c r="R30" s="1">
-        <v>20835</v>
+        <v>51640</v>
       </c>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -2302,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
         <v>0</v>
@@ -2313,55 +2845,51 @@
       <c r="E31" t="s">
         <v>0</v>
       </c>
-      <c r="F31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>0</v>
+      <c r="F31" s="1">
+        <v>25000</v>
+      </c>
+      <c r="G31" s="1">
+        <v>97.93</v>
       </c>
       <c r="H31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I31" t="s">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>0</v>
-      </c>
-      <c r="L31" t="s">
-        <v>0</v>
-      </c>
-      <c r="M31" t="s">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>0</v>
-      </c>
-      <c r="P31" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>0</v>
-      </c>
-      <c r="R31" t="s">
-        <v>0</v>
-      </c>
-      <c r="S31" t="s">
-        <v>0</v>
-      </c>
-      <c r="T31" t="s">
-        <v>0</v>
-      </c>
-      <c r="U31" t="s">
-        <v>0</v>
-      </c>
-      <c r="V31" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1">
+        <v>-108.2</v>
+      </c>
+      <c r="J31" s="1">
+        <v>-0.44</v>
+      </c>
+      <c r="K31" s="1">
+        <v>97.53</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100.91</v>
+      </c>
+      <c r="M31" s="1">
+        <v>100.97</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="O31" s="1">
+        <v>-745.47</v>
+      </c>
+      <c r="P31" s="1">
+        <v>-2.95</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>24482.5</v>
+      </c>
+      <c r="R31" s="1">
+        <v>24482.5</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="V31" s="1">
         <v>0</v>
       </c>
       <c r="W31" t="s">
@@ -2373,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
         <v>0</v>
@@ -2384,55 +2912,51 @@
       <c r="E32" t="s">
         <v>0</v>
       </c>
-      <c r="F32" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>0</v>
+      <c r="F32" s="1">
+        <v>80257.09</v>
+      </c>
+      <c r="G32" s="1">
+        <v>112.84</v>
       </c>
       <c r="H32" t="s">
-        <v>0</v>
-      </c>
-      <c r="I32" t="s">
-        <v>0</v>
-      </c>
-      <c r="J32" t="s">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
-        <v>0</v>
-      </c>
-      <c r="L32" t="s">
-        <v>0</v>
-      </c>
-      <c r="M32" t="s">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>0</v>
-      </c>
-      <c r="P32" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-18.12</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.02</v>
+      </c>
+      <c r="K32" s="1">
+        <v>94.06</v>
+      </c>
+      <c r="L32" s="1">
+        <v>99.76</v>
+      </c>
+      <c r="M32" s="1">
+        <v>15069.31</v>
+      </c>
+      <c r="N32" s="1">
+        <v>19.96</v>
+      </c>
+      <c r="O32" s="1">
+        <v>10500.75</v>
+      </c>
+      <c r="P32" s="1">
+        <v>13.11</v>
       </c>
       <c r="Q32" s="1">
-        <v>563426.4</v>
-      </c>
-      <c r="R32" t="s">
-        <v>0</v>
-      </c>
-      <c r="S32" t="s">
-        <v>0</v>
-      </c>
-      <c r="T32" t="s">
-        <v>0</v>
-      </c>
-      <c r="U32" t="s">
-        <v>0</v>
-      </c>
-      <c r="V32" t="s">
+        <v>90562.1</v>
+      </c>
+      <c r="R32" s="1">
+        <v>90562.1</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1">
+        <v>4.67</v>
+      </c>
+      <c r="V32" s="1">
         <v>0</v>
       </c>
       <c r="W32" t="s">
@@ -2444,10 +2968,10 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>0</v>
@@ -2455,55 +2979,51 @@
       <c r="E33" t="s">
         <v>0</v>
       </c>
-      <c r="F33" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>0</v>
+      <c r="F33" s="1">
+        <v>23000</v>
+      </c>
+      <c r="G33" s="1">
+        <v>121.62</v>
       </c>
       <c r="H33" t="s">
-        <v>0</v>
-      </c>
-      <c r="I33" t="s">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
-        <v>0</v>
-      </c>
-      <c r="L33" t="s">
-        <v>0</v>
-      </c>
-      <c r="M33" t="s">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>0</v>
-      </c>
-      <c r="P33" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>0</v>
-      </c>
-      <c r="R33" t="s">
-        <v>0</v>
-      </c>
-      <c r="S33" t="s">
-        <v>0</v>
-      </c>
-      <c r="T33" t="s">
-        <v>0</v>
-      </c>
-      <c r="U33" t="s">
-        <v>0</v>
-      </c>
-      <c r="V33" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>-2.8</v>
+      </c>
+      <c r="J33" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="K33" s="1">
+        <v>120.19</v>
+      </c>
+      <c r="L33" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="M33" s="1">
+        <v>328.89</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="O33" s="1">
+        <v>304.02</v>
+      </c>
+      <c r="P33" s="1">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>27972.6</v>
+      </c>
+      <c r="R33" s="1">
+        <v>27972.6</v>
+      </c>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="V33" s="1">
         <v>0</v>
       </c>
       <c r="W33" t="s">
@@ -2515,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
         <v>0</v>
@@ -2526,55 +3046,51 @@
       <c r="E34" t="s">
         <v>0</v>
       </c>
-      <c r="F34" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>0</v>
+      <c r="F34" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G34" s="1">
+        <v>91.32</v>
       </c>
       <c r="H34" t="s">
-        <v>0</v>
-      </c>
-      <c r="I34" t="s">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
-        <v>0</v>
-      </c>
-      <c r="L34" t="s">
-        <v>0</v>
-      </c>
-      <c r="M34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>0</v>
-      </c>
-      <c r="P34" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>0</v>
-      </c>
-      <c r="R34" t="s">
-        <v>0</v>
-      </c>
-      <c r="S34" t="s">
-        <v>0</v>
-      </c>
-      <c r="T34" t="s">
-        <v>0</v>
-      </c>
-      <c r="U34" t="s">
-        <v>0</v>
-      </c>
-      <c r="V34" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" s="1">
+        <v>-128.03</v>
+      </c>
+      <c r="J34" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="K34" s="1">
+        <v>74.83</v>
+      </c>
+      <c r="L34" s="1">
+        <v>82.14</v>
+      </c>
+      <c r="M34" s="1">
+        <v>16492.490000000002</v>
+      </c>
+      <c r="N34" s="1">
+        <v>22.04</v>
+      </c>
+      <c r="O34" s="1">
+        <v>9177.93</v>
+      </c>
+      <c r="P34" s="1">
+        <v>11.17</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>91320</v>
+      </c>
+      <c r="R34" s="1">
+        <v>91320</v>
+      </c>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="V34" s="1">
         <v>0</v>
       </c>
       <c r="W34" t="s">
@@ -2586,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
         <v>0</v>
@@ -2598,48 +3114,48 @@
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="G35" s="1">
-        <v>121.73</v>
+        <v>100.17</v>
       </c>
       <c r="H35" t="s">
         <v>2</v>
       </c>
       <c r="I35" s="1">
-        <v>25.55</v>
+        <v>-299.48</v>
       </c>
       <c r="J35" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>-0.66</v>
       </c>
       <c r="K35" s="1">
-        <v>120.64</v>
+        <v>102.23</v>
       </c>
       <c r="L35" s="1">
-        <v>120.76</v>
+        <v>102.33</v>
       </c>
       <c r="M35" s="1">
-        <v>327.11</v>
+        <v>-928.48</v>
       </c>
       <c r="N35" s="1">
-        <v>0.9</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="O35" s="1">
-        <v>290.23</v>
+        <v>-969.9</v>
       </c>
       <c r="P35" s="1">
-        <v>0.8</v>
+        <v>-2.1</v>
       </c>
       <c r="Q35" s="1">
-        <v>36519</v>
+        <v>45076.5</v>
       </c>
       <c r="R35" s="1">
-        <v>36519</v>
+        <v>45076.5</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1">
-        <v>1.8</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -2653,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>0</v>
@@ -2665,48 +3181,48 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>75688.77</v>
+        <v>30000</v>
       </c>
       <c r="G36" s="1">
-        <v>89.74</v>
+        <v>99.8</v>
       </c>
       <c r="H36" t="s">
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>74.53</v>
+        <v>99</v>
       </c>
       <c r="L36" s="1">
-        <v>81.37</v>
+        <v>99.09</v>
       </c>
       <c r="M36" s="1">
-        <v>11516.19</v>
+        <v>239.99</v>
       </c>
       <c r="N36" s="1">
-        <v>20.41</v>
+        <v>0.8</v>
       </c>
       <c r="O36" s="1">
-        <v>6335.18</v>
+        <v>213.27</v>
       </c>
       <c r="P36" s="1">
-        <v>10.28</v>
+        <v>0.71</v>
       </c>
       <c r="Q36" s="1">
-        <v>67923.100000000006</v>
+        <v>29940</v>
       </c>
       <c r="R36" s="1">
-        <v>67923.100000000006</v>
+        <v>29940</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1">
-        <v>3.36</v>
+        <v>1.54</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -2720,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
         <v>0</v>
@@ -2732,48 +3248,48 @@
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>50000</v>
+        <v>25133</v>
       </c>
       <c r="G37" s="1">
-        <v>104.89</v>
+        <v>100.42</v>
       </c>
       <c r="H37" t="s">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>94.23</v>
+        <v>-91.19</v>
       </c>
       <c r="J37" s="1">
-        <v>0.18</v>
+        <v>-0.36</v>
       </c>
       <c r="K37" s="1">
-        <v>99.28</v>
+        <v>97.53</v>
       </c>
       <c r="L37" s="1">
-        <v>102.54</v>
+        <v>99.56</v>
       </c>
       <c r="M37" s="1">
-        <v>2803.69</v>
+        <v>726.79</v>
       </c>
       <c r="N37" s="1">
-        <v>5.64</v>
+        <v>2.96</v>
       </c>
       <c r="O37" s="1">
-        <v>1176.4000000000001</v>
+        <v>216.26</v>
       </c>
       <c r="P37" s="1">
-        <v>2.29</v>
+        <v>0.86</v>
       </c>
       <c r="Q37" s="1">
-        <v>52445</v>
+        <v>25238.560000000001</v>
       </c>
       <c r="R37" s="1">
-        <v>52445</v>
+        <v>25238.560000000001</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1">
-        <v>2.59</v>
+        <v>1.3</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
@@ -2787,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>0</v>
@@ -2799,48 +3315,48 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="G38" s="1">
-        <v>98.75</v>
+        <v>98.1</v>
       </c>
       <c r="H38" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="1">
-        <v>0</v>
+        <v>78.319999999999993</v>
       </c>
       <c r="J38" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K38" s="1">
-        <v>97.53</v>
+        <v>84.49</v>
       </c>
       <c r="L38" s="1">
-        <v>100.91</v>
+        <v>94.72</v>
       </c>
       <c r="M38" s="1">
-        <v>305.97000000000003</v>
+        <v>5443.63</v>
       </c>
       <c r="N38" s="1">
-        <v>1.25</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="O38" s="1">
-        <v>-540.47</v>
+        <v>1352.16</v>
       </c>
       <c r="P38" s="1">
-        <v>-2.14</v>
+        <v>3.56</v>
       </c>
       <c r="Q38" s="1">
-        <v>24687.5</v>
+        <v>39240</v>
       </c>
       <c r="R38" s="1">
-        <v>24687.5</v>
+        <v>39240</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -2854,10 +3370,10 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
         <v>0</v>
@@ -2866,48 +3382,48 @@
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>80257.09</v>
+        <v>41667.919999999998</v>
       </c>
       <c r="G39" s="1">
-        <v>112.82</v>
+        <v>110.16</v>
       </c>
       <c r="H39" t="s">
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>117.56</v>
+        <v>13.77</v>
       </c>
       <c r="J39" s="1">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="K39" s="1">
-        <v>94.06</v>
+        <v>107.93</v>
       </c>
       <c r="L39" s="1">
-        <v>99.76</v>
+        <v>108.14</v>
       </c>
       <c r="M39" s="1">
-        <v>15053.26</v>
+        <v>931.02</v>
       </c>
       <c r="N39" s="1">
-        <v>19.93</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="O39" s="1">
-        <v>10484.700000000001</v>
+        <v>842.84</v>
       </c>
       <c r="P39" s="1">
-        <v>13.09</v>
+        <v>1.87</v>
       </c>
       <c r="Q39" s="1">
-        <v>90546.05</v>
+        <v>45901.38</v>
       </c>
       <c r="R39" s="1">
-        <v>90546.05</v>
+        <v>45901.38</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <v>4.47</v>
+        <v>2.36</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -2921,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
         <v>0</v>
@@ -2933,48 +3449,48 @@
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>23000</v>
+        <v>61602</v>
       </c>
       <c r="G40" s="1">
-        <v>121.42</v>
+        <v>95.42</v>
       </c>
       <c r="H40" t="s">
         <v>2</v>
       </c>
       <c r="I40" s="1">
-        <v>16.75</v>
+        <v>70.45</v>
       </c>
       <c r="J40" s="1">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="K40" s="1">
-        <v>120.19</v>
+        <v>86.1</v>
       </c>
       <c r="L40" s="1">
-        <v>120.3</v>
+        <v>88.3</v>
       </c>
       <c r="M40" s="1">
-        <v>282.89</v>
+        <v>5740.25</v>
       </c>
       <c r="N40" s="1">
-        <v>1.02</v>
+        <v>10.82</v>
       </c>
       <c r="O40" s="1">
-        <v>258.02</v>
+        <v>4383.8599999999997</v>
       </c>
       <c r="P40" s="1">
-        <v>0.93</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="Q40" s="1">
-        <v>27926.6</v>
+        <v>58780.63</v>
       </c>
       <c r="R40" s="1">
-        <v>27926.6</v>
+        <v>58780.63</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1">
-        <v>1.38</v>
+        <v>3.03</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
@@ -2988,10 +3504,10 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
         <v>0</v>
@@ -3000,48 +3516,48 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>100000</v>
+        <v>57435.9</v>
       </c>
       <c r="G41" s="1">
-        <v>92.41</v>
+        <v>119.63</v>
       </c>
       <c r="H41" t="s">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>-9.24</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>74.83</v>
+        <v>106.92</v>
       </c>
       <c r="L41" s="1">
-        <v>82.14</v>
+        <v>110.63</v>
       </c>
       <c r="M41" s="1">
-        <v>17582.490000000002</v>
+        <v>7299.81</v>
       </c>
       <c r="N41" s="1">
-        <v>23.49</v>
+        <v>11.88</v>
       </c>
       <c r="O41" s="1">
-        <v>10267.93</v>
+        <v>5166.88</v>
       </c>
       <c r="P41" s="1">
-        <v>12.5</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="Q41" s="1">
-        <v>92410</v>
+        <v>68710.570000000007</v>
       </c>
       <c r="R41" s="1">
-        <v>92410</v>
+        <v>68710.570000000007</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1">
-        <v>4.57</v>
+        <v>3.54</v>
       </c>
       <c r="V41" s="1">
         <v>0</v>
@@ -3055,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
         <v>0</v>
@@ -3070,45 +3586,45 @@
         <v>45000</v>
       </c>
       <c r="G42" s="1">
-        <v>100.5</v>
+        <v>103.67</v>
       </c>
       <c r="H42" t="s">
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <v>500.91</v>
+        <v>-46.7</v>
       </c>
       <c r="J42" s="1">
-        <v>1.1200000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="K42" s="1">
-        <v>102.23</v>
+        <v>101.08</v>
       </c>
       <c r="L42" s="1">
-        <v>102.33</v>
+        <v>106.6</v>
       </c>
       <c r="M42" s="1">
-        <v>-779.98</v>
+        <v>1166.48</v>
       </c>
       <c r="N42" s="1">
-        <v>-1.69</v>
+        <v>2.56</v>
       </c>
       <c r="O42" s="1">
-        <v>-821.4</v>
+        <v>-1316.62</v>
       </c>
       <c r="P42" s="1">
-        <v>-1.78</v>
+        <v>-2.74</v>
       </c>
       <c r="Q42" s="1">
-        <v>45225</v>
+        <v>46651.5</v>
       </c>
       <c r="R42" s="1">
-        <v>45225</v>
+        <v>46651.5</v>
       </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -3122,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
         <v>0</v>
@@ -3134,48 +3650,48 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="G43" s="1">
-        <v>100.4</v>
+        <v>121.85</v>
       </c>
       <c r="H43" t="s">
         <v>2</v>
       </c>
       <c r="I43" s="1">
-        <v>0</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="J43" s="1">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="K43" s="1">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="L43" s="1">
-        <v>99.09</v>
+        <v>121.13</v>
       </c>
       <c r="M43" s="1">
-        <v>419.99</v>
+        <v>203.99</v>
       </c>
       <c r="N43" s="1">
-        <v>1.41</v>
+        <v>0.7</v>
       </c>
       <c r="O43" s="1">
-        <v>393.27</v>
+        <v>173.41</v>
       </c>
       <c r="P43" s="1">
-        <v>1.32</v>
+        <v>0.59</v>
       </c>
       <c r="Q43" s="1">
-        <v>30120</v>
+        <v>29244</v>
       </c>
       <c r="R43" s="1">
-        <v>30120</v>
+        <v>29244</v>
       </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -3189,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D44" t="s">
         <v>0</v>
@@ -3200,51 +3716,55 @@
       <c r="E44" t="s">
         <v>0</v>
       </c>
-      <c r="F44" s="1">
-        <v>25133</v>
-      </c>
-      <c r="G44" s="1">
-        <v>100.92</v>
+      <c r="F44" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>2</v>
-      </c>
-      <c r="I44" s="1">
-        <v>35.46</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K44" s="1">
-        <v>97.53</v>
-      </c>
-      <c r="L44" s="1">
-        <v>99.56</v>
-      </c>
-      <c r="M44" s="1">
-        <v>852.46</v>
-      </c>
-      <c r="N44" s="1">
-        <v>3.47</v>
-      </c>
-      <c r="O44" s="1">
-        <v>341.92</v>
-      </c>
-      <c r="P44" s="1">
-        <v>1.36</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>25364.22</v>
-      </c>
-      <c r="R44" s="1">
-        <v>25364.22</v>
-      </c>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1">
-        <v>1.25</v>
-      </c>
-      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>0</v>
+      </c>
+      <c r="L44" t="s">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>0</v>
+      </c>
+      <c r="P44" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>0</v>
+      </c>
+      <c r="R44" t="s">
+        <v>0</v>
+      </c>
+      <c r="S44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
         <v>0</v>
       </c>
       <c r="W44" t="s">
@@ -3256,10 +3776,10 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D45" t="s">
         <v>0</v>
@@ -3267,51 +3787,55 @@
       <c r="E45" t="s">
         <v>0</v>
       </c>
-      <c r="F45" s="1">
-        <v>40000</v>
-      </c>
-      <c r="G45" s="1">
-        <v>96.6</v>
+      <c r="F45" t="s">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>2</v>
-      </c>
-      <c r="I45" s="1">
-        <v>161.61000000000001</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="K45" s="1">
-        <v>84.49</v>
-      </c>
-      <c r="L45" s="1">
-        <v>94.72</v>
-      </c>
-      <c r="M45" s="1">
-        <v>4843.63</v>
-      </c>
-      <c r="N45" s="1">
-        <v>14.33</v>
-      </c>
-      <c r="O45" s="1">
-        <v>752.16</v>
-      </c>
-      <c r="P45" s="1">
-        <v>1.98</v>
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>0</v>
+      </c>
+      <c r="P45" t="s">
+        <v>0</v>
       </c>
       <c r="Q45" s="1">
-        <v>38640</v>
-      </c>
-      <c r="R45" s="1">
-        <v>38640</v>
-      </c>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1">
-        <v>1.91</v>
-      </c>
-      <c r="V45" s="1">
+        <v>778448.28</v>
+      </c>
+      <c r="R45" t="s">
+        <v>0</v>
+      </c>
+      <c r="S45" t="s">
+        <v>0</v>
+      </c>
+      <c r="T45" t="s">
+        <v>0</v>
+      </c>
+      <c r="U45" t="s">
+        <v>0</v>
+      </c>
+      <c r="V45" t="s">
         <v>0</v>
       </c>
       <c r="W45" t="s">
@@ -3323,10 +3847,10 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="D46" t="s">
         <v>0</v>
@@ -3334,51 +3858,55 @@
       <c r="E46" t="s">
         <v>0</v>
       </c>
-      <c r="F46" s="1">
-        <v>41667.919999999998</v>
-      </c>
-      <c r="G46" s="1">
-        <v>110.2</v>
+      <c r="F46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I46" s="1">
-        <v>4.59</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="K46" s="1">
-        <v>107.93</v>
-      </c>
-      <c r="L46" s="1">
-        <v>108.14</v>
-      </c>
-      <c r="M46" s="1">
-        <v>947.69</v>
-      </c>
-      <c r="N46" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="O46" s="1">
-        <v>859.51</v>
-      </c>
-      <c r="P46" s="1">
-        <v>1.9</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>45918.05</v>
-      </c>
-      <c r="R46" s="1">
-        <v>45918.05</v>
-      </c>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1">
-        <v>2.27</v>
-      </c>
-      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>0</v>
+      </c>
+      <c r="P46" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>0</v>
+      </c>
+      <c r="R46" t="s">
+        <v>0</v>
+      </c>
+      <c r="S46" t="s">
+        <v>0</v>
+      </c>
+      <c r="T46" t="s">
+        <v>0</v>
+      </c>
+      <c r="U46" t="s">
+        <v>0</v>
+      </c>
+      <c r="V46" t="s">
         <v>0</v>
       </c>
       <c r="W46" t="s">
@@ -3390,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="D47" t="s">
         <v>0</v>
@@ -3401,51 +3929,55 @@
       <c r="E47" t="s">
         <v>0</v>
       </c>
-      <c r="F47" s="1">
-        <v>61602</v>
-      </c>
-      <c r="G47" s="1">
-        <v>96.6</v>
+      <c r="F47" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>2</v>
-      </c>
-      <c r="I47" s="1">
-        <v>-137.18</v>
-      </c>
-      <c r="J47" s="1">
-        <v>-0.23</v>
-      </c>
-      <c r="K47" s="1">
-        <v>86.1</v>
-      </c>
-      <c r="L47" s="1">
-        <v>88.3</v>
-      </c>
-      <c r="M47" s="1">
-        <v>6467.16</v>
-      </c>
-      <c r="N47" s="1">
-        <v>12.19</v>
-      </c>
-      <c r="O47" s="1">
-        <v>5110.76</v>
-      </c>
-      <c r="P47" s="1">
-        <v>9.39</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>59507.53</v>
-      </c>
-      <c r="R47" s="1">
-        <v>59507.53</v>
-      </c>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1">
-        <v>2.94</v>
-      </c>
-      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>0</v>
+      </c>
+      <c r="P47" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>0</v>
+      </c>
+      <c r="R47" t="s">
+        <v>0</v>
+      </c>
+      <c r="S47" t="s">
+        <v>0</v>
+      </c>
+      <c r="T47" t="s">
+        <v>0</v>
+      </c>
+      <c r="U47" t="s">
+        <v>0</v>
+      </c>
+      <c r="V47" t="s">
         <v>0</v>
       </c>
       <c r="W47" t="s">
@@ -3457,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
         <v>0</v>
@@ -3469,48 +4001,48 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>57435.9</v>
+        <v>41000</v>
       </c>
       <c r="G48" s="1">
-        <v>119.55</v>
+        <v>127.55</v>
       </c>
       <c r="H48" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" s="1">
-        <v>-6.87</v>
+        <v>12.44</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="K48" s="1">
-        <v>106.92</v>
+        <v>120.19</v>
       </c>
       <c r="L48" s="1">
-        <v>110.63</v>
+        <v>125.17</v>
       </c>
       <c r="M48" s="1">
-        <v>7253.86</v>
+        <v>9206.16</v>
       </c>
       <c r="N48" s="1">
-        <v>11.81</v>
+        <v>6.12</v>
       </c>
       <c r="O48" s="1">
-        <v>5120.93</v>
+        <v>2973.08</v>
       </c>
       <c r="P48" s="1">
-        <v>8.0500000000000007</v>
+        <v>1.9</v>
       </c>
       <c r="Q48" s="1">
-        <v>68664.62</v>
+        <v>159448.98000000001</v>
       </c>
       <c r="R48" s="1">
-        <v>68664.62</v>
+        <v>52295.5</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1">
-        <v>3.39</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
@@ -3524,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
         <v>0</v>
@@ -3536,48 +4068,48 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>45000</v>
+        <v>144000</v>
       </c>
       <c r="G49" s="1">
-        <v>104.46</v>
+        <v>106.33</v>
       </c>
       <c r="H49" t="s">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>4.7</v>
+        <v>14.39</v>
       </c>
       <c r="J49" s="1">
         <v>0.01</v>
       </c>
       <c r="K49" s="1">
-        <v>101.08</v>
+        <v>105.16</v>
       </c>
       <c r="L49" s="1">
-        <v>106.6</v>
+        <v>105.53</v>
       </c>
       <c r="M49" s="1">
-        <v>1521.98</v>
+        <v>1678.6</v>
       </c>
       <c r="N49" s="1">
-        <v>3.34</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O49" s="1">
-        <v>-961.12</v>
+        <v>1152</v>
       </c>
       <c r="P49" s="1">
-        <v>-2</v>
+        <v>0.75</v>
       </c>
       <c r="Q49" s="1">
-        <v>47007</v>
+        <v>153115.20000000001</v>
       </c>
       <c r="R49" s="1">
-        <v>47007</v>
+        <v>153115.20000000001</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1">
-        <v>2.3199999999999998</v>
+        <v>7.89</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -3591,10 +4123,10 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
         <v>0</v>
@@ -3603,48 +4135,48 @@
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="G50" s="1">
-        <v>119.2</v>
+        <v>108.45</v>
       </c>
       <c r="H50" t="s">
         <v>2</v>
       </c>
       <c r="I50" s="1">
-        <v>-14.31</v>
+        <v>3.59</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K50" s="1">
-        <v>109.11</v>
+        <v>108.45</v>
       </c>
       <c r="L50" s="1">
-        <v>111.45</v>
+        <v>108.45</v>
       </c>
       <c r="M50" s="1">
-        <v>4037.39</v>
+        <v>0</v>
       </c>
       <c r="N50" s="1">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
-        <v>3101.07</v>
+        <v>0</v>
       </c>
       <c r="P50" s="1">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="1">
-        <v>47680</v>
+        <v>19521</v>
       </c>
       <c r="R50" s="1">
-        <v>47680</v>
+        <v>19521</v>
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
@@ -3658,10 +4190,10 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D51" t="s">
         <v>0</v>
@@ -3669,51 +4201,55 @@
       <c r="E51" t="s">
         <v>0</v>
       </c>
-      <c r="F51" s="1">
-        <v>24000</v>
-      </c>
-      <c r="G51" s="1">
-        <v>121.8</v>
+      <c r="F51" t="s">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>2</v>
-      </c>
-      <c r="I51" s="1">
-        <v>23.37</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="K51" s="1">
-        <v>121</v>
-      </c>
-      <c r="L51" s="1">
-        <v>121.13</v>
-      </c>
-      <c r="M51" s="1">
-        <v>191.99</v>
-      </c>
-      <c r="N51" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="O51" s="1">
-        <v>161.41</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>29232</v>
-      </c>
-      <c r="R51" s="1">
-        <v>29232</v>
-      </c>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" t="s">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>0</v>
+      </c>
+      <c r="P51" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>0</v>
+      </c>
+      <c r="R51" t="s">
+        <v>0</v>
+      </c>
+      <c r="S51" t="s">
+        <v>0</v>
+      </c>
+      <c r="T51" t="s">
+        <v>0</v>
+      </c>
+      <c r="U51" t="s">
+        <v>0</v>
+      </c>
+      <c r="V51" t="s">
         <v>0</v>
       </c>
       <c r="W51" t="s">
@@ -3725,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -3769,8 +4305,8 @@
       <c r="P52" t="s">
         <v>0</v>
       </c>
-      <c r="Q52" t="s">
-        <v>0</v>
+      <c r="Q52" s="1">
+        <v>332085.18</v>
       </c>
       <c r="R52" t="s">
         <v>0</v>
@@ -3796,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
@@ -3840,8 +4376,8 @@
       <c r="P53" t="s">
         <v>0</v>
       </c>
-      <c r="Q53" s="1">
-        <v>829815.67</v>
+      <c r="Q53" t="s">
+        <v>0</v>
       </c>
       <c r="R53" t="s">
         <v>0</v>
@@ -3867,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
         <v>0</v>
@@ -3938,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C55" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
         <v>0</v>
@@ -3949,55 +4485,51 @@
       <c r="E55" t="s">
         <v>0</v>
       </c>
-      <c r="F55" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" t="s">
-        <v>0</v>
+      <c r="F55" s="1">
+        <v>703</v>
+      </c>
+      <c r="G55" s="1">
+        <v>39850</v>
       </c>
       <c r="H55" t="s">
-        <v>0</v>
-      </c>
-      <c r="I55" t="s">
-        <v>0</v>
-      </c>
-      <c r="J55" t="s">
-        <v>0</v>
-      </c>
-      <c r="K55" t="s">
-        <v>0</v>
-      </c>
-      <c r="L55" t="s">
-        <v>0</v>
-      </c>
-      <c r="M55" t="s">
-        <v>0</v>
-      </c>
-      <c r="N55" t="s">
-        <v>0</v>
-      </c>
-      <c r="O55" t="s">
-        <v>0</v>
-      </c>
-      <c r="P55" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>0</v>
-      </c>
-      <c r="R55" t="s">
-        <v>0</v>
-      </c>
-      <c r="S55" t="s">
-        <v>0</v>
-      </c>
-      <c r="T55" t="s">
-        <v>0</v>
-      </c>
-      <c r="U55" t="s">
-        <v>0</v>
-      </c>
-      <c r="V55" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1">
+        <v>-2316.19</v>
+      </c>
+      <c r="J55" s="1">
+        <v>-0.82</v>
+      </c>
+      <c r="K55" s="1">
+        <v>34092.879999999997</v>
+      </c>
+      <c r="L55" s="1">
+        <v>34168.11</v>
+      </c>
+      <c r="M55" s="1">
+        <v>40472.550000000003</v>
+      </c>
+      <c r="N55" s="1">
+        <v>16.88</v>
+      </c>
+      <c r="O55" s="1">
+        <v>39943.71</v>
+      </c>
+      <c r="P55" s="1">
+        <v>16.62</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>280145.5</v>
+      </c>
+      <c r="R55" s="1">
+        <v>280145.5</v>
+      </c>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1">
+        <v>14.43</v>
+      </c>
+      <c r="V55" s="1">
         <v>0</v>
       </c>
       <c r="W55" t="s">
@@ -4009,10 +4541,10 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C56" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -4020,51 +4552,55 @@
       <c r="E56" t="s">
         <v>0</v>
       </c>
-      <c r="F56" s="1">
-        <v>41000</v>
-      </c>
-      <c r="G56" s="1">
-        <v>127.46</v>
+      <c r="F56" t="s">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>3</v>
-      </c>
-      <c r="I56" s="1">
-        <v>24.49</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K56" s="1">
-        <v>120.19</v>
-      </c>
-      <c r="L56" s="1">
-        <v>125.17</v>
-      </c>
-      <c r="M56" s="1">
-        <v>8962.42</v>
-      </c>
-      <c r="N56" s="1">
-        <v>6.05</v>
-      </c>
-      <c r="O56" s="1">
-        <v>2819.29</v>
-      </c>
-      <c r="P56" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>157037.09</v>
-      </c>
-      <c r="R56" s="1">
-        <v>52258.6</v>
-      </c>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1">
-        <v>7.76</v>
-      </c>
-      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>0</v>
+      </c>
+      <c r="P56" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>0</v>
+      </c>
+      <c r="R56" t="s">
+        <v>0</v>
+      </c>
+      <c r="S56" t="s">
+        <v>0</v>
+      </c>
+      <c r="T56" t="s">
+        <v>0</v>
+      </c>
+      <c r="U56" t="s">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
         <v>0</v>
       </c>
       <c r="W56" t="s">
@@ -4076,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D57" t="s">
         <v>0</v>
@@ -4087,51 +4623,55 @@
       <c r="E57" t="s">
         <v>0</v>
       </c>
-      <c r="F57" s="1">
-        <v>144000</v>
-      </c>
-      <c r="G57" s="1">
-        <v>106.24</v>
+      <c r="F57" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>2</v>
-      </c>
-      <c r="I57" s="1">
-        <v>14.38</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="K57" s="1">
-        <v>105.16</v>
-      </c>
-      <c r="L57" s="1">
-        <v>105.53</v>
-      </c>
-      <c r="M57" s="1">
-        <v>1549</v>
-      </c>
-      <c r="N57" s="1">
-        <v>1.02</v>
-      </c>
-      <c r="O57" s="1">
-        <v>1022.4</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0.67</v>
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>0</v>
+      </c>
+      <c r="K57" t="s">
+        <v>0</v>
+      </c>
+      <c r="L57" t="s">
+        <v>0</v>
+      </c>
+      <c r="M57" t="s">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>0</v>
+      </c>
+      <c r="P57" t="s">
+        <v>0</v>
       </c>
       <c r="Q57" s="1">
-        <v>152985.60000000001</v>
-      </c>
-      <c r="R57" s="1">
-        <v>152985.60000000001</v>
-      </c>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1">
-        <v>7.56</v>
-      </c>
-      <c r="V57" s="1">
+        <v>280145.5</v>
+      </c>
+      <c r="R57" t="s">
+        <v>0</v>
+      </c>
+      <c r="S57" t="s">
+        <v>0</v>
+      </c>
+      <c r="T57" t="s">
+        <v>0</v>
+      </c>
+      <c r="U57" t="s">
+        <v>0</v>
+      </c>
+      <c r="V57" t="s">
         <v>0</v>
       </c>
       <c r="W57" t="s">
@@ -4143,10 +4683,10 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D58" t="s">
         <v>0</v>
@@ -4154,51 +4694,55 @@
       <c r="E58" t="s">
         <v>0</v>
       </c>
-      <c r="F58" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G58" s="1">
-        <v>108.37</v>
+      <c r="F58" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>2</v>
-      </c>
-      <c r="I58" s="1">
-        <v>5.98</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K58" s="1">
-        <v>108.37</v>
-      </c>
-      <c r="L58" s="1">
-        <v>108.37</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>32511</v>
-      </c>
-      <c r="R58" s="1">
-        <v>32511</v>
-      </c>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" t="s">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
+        <v>0</v>
+      </c>
+      <c r="M58" t="s">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>0</v>
+      </c>
+      <c r="P58" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>0</v>
+      </c>
+      <c r="R58" t="s">
+        <v>0</v>
+      </c>
+      <c r="S58" t="s">
+        <v>0</v>
+      </c>
+      <c r="T58" t="s">
+        <v>0</v>
+      </c>
+      <c r="U58" t="s">
+        <v>0</v>
+      </c>
+      <c r="V58" t="s">
         <v>0</v>
       </c>
       <c r="W58" t="s">
@@ -4210,7 +4754,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
         <v>0</v>
@@ -4281,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
@@ -4325,8 +4869,8 @@
       <c r="P60" t="s">
         <v>0</v>
       </c>
-      <c r="Q60" s="1">
-        <v>342533.69</v>
+      <c r="Q60" t="s">
+        <v>0</v>
       </c>
       <c r="R60" t="s">
         <v>0</v>
@@ -4352,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C61" t="s">
         <v>0</v>
@@ -4423,66 +4967,62 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="D62" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s">
         <v>0</v>
       </c>
-      <c r="F62" t="s">
-        <v>0</v>
-      </c>
-      <c r="G62" t="s">
-        <v>0</v>
+      <c r="F62" s="1">
+        <v>700</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.3</v>
       </c>
       <c r="H62" t="s">
-        <v>0</v>
-      </c>
-      <c r="I62" t="s">
-        <v>0</v>
-      </c>
-      <c r="J62" t="s">
-        <v>0</v>
-      </c>
-      <c r="K62" t="s">
-        <v>0</v>
-      </c>
-      <c r="L62" t="s">
-        <v>0</v>
-      </c>
-      <c r="M62" t="s">
-        <v>0</v>
-      </c>
-      <c r="N62" t="s">
-        <v>0</v>
-      </c>
-      <c r="O62" t="s">
-        <v>0</v>
-      </c>
-      <c r="P62" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>0</v>
-      </c>
-      <c r="R62" t="s">
-        <v>0</v>
-      </c>
-      <c r="S62" t="s">
-        <v>0</v>
-      </c>
-      <c r="T62" t="s">
-        <v>0</v>
-      </c>
-      <c r="U62" t="s">
-        <v>0</v>
-      </c>
-      <c r="V62" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="1">
+        <v>-17.5</v>
+      </c>
+      <c r="J62" s="1">
+        <v>-2.7</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="M62" s="1">
+        <v>-627.69000000000005</v>
+      </c>
+      <c r="N62" s="1">
+        <v>-49.84</v>
+      </c>
+      <c r="O62" s="1">
+        <v>-636.23</v>
+      </c>
+      <c r="P62" s="1">
+        <v>-50.18</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>631.54</v>
+      </c>
+      <c r="R62" s="1">
+        <v>207.13</v>
+      </c>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="V62" s="1">
         <v>0</v>
       </c>
       <c r="W62" t="s">
@@ -4494,10 +5034,10 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D63" t="s">
         <v>0</v>
@@ -4505,51 +5045,55 @@
       <c r="E63" t="s">
         <v>0</v>
       </c>
-      <c r="F63" s="1">
-        <v>703</v>
-      </c>
-      <c r="G63" s="1">
-        <v>40860</v>
+      <c r="F63" t="s">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>2</v>
-      </c>
-      <c r="I63" s="1">
-        <v>2251.46</v>
-      </c>
-      <c r="J63" s="1">
-        <v>0.79</v>
-      </c>
-      <c r="K63" s="1">
-        <v>34092.879999999997</v>
-      </c>
-      <c r="L63" s="1">
-        <v>34168.11</v>
-      </c>
-      <c r="M63" s="1">
-        <v>47572.85</v>
-      </c>
-      <c r="N63" s="1">
-        <v>19.84</v>
-      </c>
-      <c r="O63" s="1">
-        <v>47044.01</v>
-      </c>
-      <c r="P63" s="1">
-        <v>19.579999999999998</v>
-      </c>
-      <c r="Q63" s="1">
-        <v>287245.8</v>
-      </c>
-      <c r="R63" s="1">
-        <v>287245.8</v>
-      </c>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="1">
-        <v>14.19</v>
-      </c>
-      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>0</v>
+      </c>
+      <c r="J63" t="s">
+        <v>0</v>
+      </c>
+      <c r="K63" t="s">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>0</v>
+      </c>
+      <c r="M63" t="s">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>0</v>
+      </c>
+      <c r="O63" t="s">
+        <v>0</v>
+      </c>
+      <c r="P63" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>0</v>
+      </c>
+      <c r="R63" t="s">
+        <v>0</v>
+      </c>
+      <c r="S63" t="s">
+        <v>0</v>
+      </c>
+      <c r="T63" t="s">
+        <v>0</v>
+      </c>
+      <c r="U63" t="s">
+        <v>0</v>
+      </c>
+      <c r="V63" t="s">
         <v>0</v>
       </c>
       <c r="W63" t="s">
@@ -4561,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
         <v>0</v>
@@ -4605,8 +5149,8 @@
       <c r="P64" t="s">
         <v>0</v>
       </c>
-      <c r="Q64" t="s">
-        <v>0</v>
+      <c r="Q64" s="1">
+        <v>631.54</v>
       </c>
       <c r="R64" t="s">
         <v>0</v>
@@ -4624,570 +5168,6 @@
         <v>0</v>
       </c>
       <c r="W64" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" t="s">
-        <v>107</v>
-      </c>
-      <c r="C65" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" t="s">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
-        <v>0</v>
-      </c>
-      <c r="F65" t="s">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
-        <v>0</v>
-      </c>
-      <c r="H65" t="s">
-        <v>0</v>
-      </c>
-      <c r="I65" t="s">
-        <v>0</v>
-      </c>
-      <c r="J65" t="s">
-        <v>0</v>
-      </c>
-      <c r="K65" t="s">
-        <v>0</v>
-      </c>
-      <c r="L65" t="s">
-        <v>0</v>
-      </c>
-      <c r="M65" t="s">
-        <v>0</v>
-      </c>
-      <c r="N65" t="s">
-        <v>0</v>
-      </c>
-      <c r="O65" t="s">
-        <v>0</v>
-      </c>
-      <c r="P65" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>287245.8</v>
-      </c>
-      <c r="R65" t="s">
-        <v>0</v>
-      </c>
-      <c r="S65" t="s">
-        <v>0</v>
-      </c>
-      <c r="T65" t="s">
-        <v>0</v>
-      </c>
-      <c r="U65" t="s">
-        <v>0</v>
-      </c>
-      <c r="V65" t="s">
-        <v>0</v>
-      </c>
-      <c r="W65" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" t="s">
-        <v>0</v>
-      </c>
-      <c r="C66" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" t="s">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>0</v>
-      </c>
-      <c r="F66" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" t="s">
-        <v>0</v>
-      </c>
-      <c r="H66" t="s">
-        <v>0</v>
-      </c>
-      <c r="I66" t="s">
-        <v>0</v>
-      </c>
-      <c r="J66" t="s">
-        <v>0</v>
-      </c>
-      <c r="K66" t="s">
-        <v>0</v>
-      </c>
-      <c r="L66" t="s">
-        <v>0</v>
-      </c>
-      <c r="M66" t="s">
-        <v>0</v>
-      </c>
-      <c r="N66" t="s">
-        <v>0</v>
-      </c>
-      <c r="O66" t="s">
-        <v>0</v>
-      </c>
-      <c r="P66" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>0</v>
-      </c>
-      <c r="R66" t="s">
-        <v>0</v>
-      </c>
-      <c r="S66" t="s">
-        <v>0</v>
-      </c>
-      <c r="T66" t="s">
-        <v>0</v>
-      </c>
-      <c r="U66" t="s">
-        <v>0</v>
-      </c>
-      <c r="V66" t="s">
-        <v>0</v>
-      </c>
-      <c r="W66" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" t="s">
-        <v>108</v>
-      </c>
-      <c r="C67" t="s">
-        <v>0</v>
-      </c>
-      <c r="D67" t="s">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>0</v>
-      </c>
-      <c r="F67" t="s">
-        <v>0</v>
-      </c>
-      <c r="G67" t="s">
-        <v>0</v>
-      </c>
-      <c r="H67" t="s">
-        <v>0</v>
-      </c>
-      <c r="I67" t="s">
-        <v>0</v>
-      </c>
-      <c r="J67" t="s">
-        <v>0</v>
-      </c>
-      <c r="K67" t="s">
-        <v>0</v>
-      </c>
-      <c r="L67" t="s">
-        <v>0</v>
-      </c>
-      <c r="M67" t="s">
-        <v>0</v>
-      </c>
-      <c r="N67" t="s">
-        <v>0</v>
-      </c>
-      <c r="O67" t="s">
-        <v>0</v>
-      </c>
-      <c r="P67" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>0</v>
-      </c>
-      <c r="R67" t="s">
-        <v>0</v>
-      </c>
-      <c r="S67" t="s">
-        <v>0</v>
-      </c>
-      <c r="T67" t="s">
-        <v>0</v>
-      </c>
-      <c r="U67" t="s">
-        <v>0</v>
-      </c>
-      <c r="V67" t="s">
-        <v>0</v>
-      </c>
-      <c r="W67" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B68" t="s">
-        <v>0</v>
-      </c>
-      <c r="C68" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" t="s">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>0</v>
-      </c>
-      <c r="F68" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>0</v>
-      </c>
-      <c r="I68" t="s">
-        <v>0</v>
-      </c>
-      <c r="J68" t="s">
-        <v>0</v>
-      </c>
-      <c r="K68" t="s">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
-        <v>0</v>
-      </c>
-      <c r="M68" t="s">
-        <v>0</v>
-      </c>
-      <c r="N68" t="s">
-        <v>0</v>
-      </c>
-      <c r="O68" t="s">
-        <v>0</v>
-      </c>
-      <c r="P68" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>0</v>
-      </c>
-      <c r="R68" t="s">
-        <v>0</v>
-      </c>
-      <c r="S68" t="s">
-        <v>0</v>
-      </c>
-      <c r="T68" t="s">
-        <v>0</v>
-      </c>
-      <c r="U68" t="s">
-        <v>0</v>
-      </c>
-      <c r="V68" t="s">
-        <v>0</v>
-      </c>
-      <c r="W68" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B69" t="s">
-        <v>26</v>
-      </c>
-      <c r="C69" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69" t="s">
-        <v>0</v>
-      </c>
-      <c r="E69" t="s">
-        <v>0</v>
-      </c>
-      <c r="F69" t="s">
-        <v>0</v>
-      </c>
-      <c r="G69" t="s">
-        <v>0</v>
-      </c>
-      <c r="H69" t="s">
-        <v>0</v>
-      </c>
-      <c r="I69" t="s">
-        <v>0</v>
-      </c>
-      <c r="J69" t="s">
-        <v>0</v>
-      </c>
-      <c r="K69" t="s">
-        <v>0</v>
-      </c>
-      <c r="L69" t="s">
-        <v>0</v>
-      </c>
-      <c r="M69" t="s">
-        <v>0</v>
-      </c>
-      <c r="N69" t="s">
-        <v>0</v>
-      </c>
-      <c r="O69" t="s">
-        <v>0</v>
-      </c>
-      <c r="P69" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>0</v>
-      </c>
-      <c r="R69" t="s">
-        <v>0</v>
-      </c>
-      <c r="S69" t="s">
-        <v>0</v>
-      </c>
-      <c r="T69" t="s">
-        <v>0</v>
-      </c>
-      <c r="U69" t="s">
-        <v>0</v>
-      </c>
-      <c r="V69" t="s">
-        <v>0</v>
-      </c>
-      <c r="W69" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B70" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70" t="s">
-        <v>110</v>
-      </c>
-      <c r="D70" t="s">
-        <v>111</v>
-      </c>
-      <c r="E70" t="s">
-        <v>0</v>
-      </c>
-      <c r="F70" s="1">
-        <v>700</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="H70" t="s">
-        <v>3</v>
-      </c>
-      <c r="I70" s="1">
-        <v>0</v>
-      </c>
-      <c r="J70" s="1">
-        <v>0</v>
-      </c>
-      <c r="K70" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="L70" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="M70" s="1">
-        <v>-555.74</v>
-      </c>
-      <c r="N70" s="1">
-        <v>-44.77</v>
-      </c>
-      <c r="O70" s="1">
-        <v>-564.15</v>
-      </c>
-      <c r="P70" s="1">
-        <v>-45.15</v>
-      </c>
-      <c r="Q70" s="1">
-        <v>685.32</v>
-      </c>
-      <c r="R70" s="1">
-        <v>228.06</v>
-      </c>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="V70" s="1">
-        <v>0</v>
-      </c>
-      <c r="W70" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H71" t="s">
-        <v>0</v>
-      </c>
-      <c r="I71" t="s">
-        <v>0</v>
-      </c>
-      <c r="J71" t="s">
-        <v>0</v>
-      </c>
-      <c r="K71" t="s">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
-        <v>0</v>
-      </c>
-      <c r="M71" t="s">
-        <v>0</v>
-      </c>
-      <c r="N71" t="s">
-        <v>0</v>
-      </c>
-      <c r="O71" t="s">
-        <v>0</v>
-      </c>
-      <c r="P71" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>0</v>
-      </c>
-      <c r="R71" t="s">
-        <v>0</v>
-      </c>
-      <c r="S71" t="s">
-        <v>0</v>
-      </c>
-      <c r="T71" t="s">
-        <v>0</v>
-      </c>
-      <c r="U71" t="s">
-        <v>0</v>
-      </c>
-      <c r="V71" t="s">
-        <v>0</v>
-      </c>
-      <c r="W71" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" t="s">
-        <v>59</v>
-      </c>
-      <c r="C72" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72" t="s">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
-        <v>0</v>
-      </c>
-      <c r="F72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I72" t="s">
-        <v>0</v>
-      </c>
-      <c r="J72" t="s">
-        <v>0</v>
-      </c>
-      <c r="K72" t="s">
-        <v>0</v>
-      </c>
-      <c r="L72" t="s">
-        <v>0</v>
-      </c>
-      <c r="M72" t="s">
-        <v>0</v>
-      </c>
-      <c r="N72" t="s">
-        <v>0</v>
-      </c>
-      <c r="O72" t="s">
-        <v>0</v>
-      </c>
-      <c r="P72" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="1">
-        <v>685.32</v>
-      </c>
-      <c r="R72" t="s">
-        <v>0</v>
-      </c>
-      <c r="S72" t="s">
-        <v>0</v>
-      </c>
-      <c r="T72" t="s">
-        <v>0</v>
-      </c>
-      <c r="U72" t="s">
-        <v>0</v>
-      </c>
-      <c r="V72" t="s">
-        <v>0</v>
-      </c>
-      <c r="W72" t="s">
         <v>0</v>
       </c>
     </row>

--- a/holdings.xlsx
+++ b/holdings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\tase-ytm-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB6845A-EE1E-4F3C-A46A-13344A0ADCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E644AA-AF32-46BA-A742-4A502D57EF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="114">
   <si>
     <t/>
   </si>
@@ -28,291 +28,291 @@
     <t>שינוי יומי באחוז</t>
   </si>
   <si>
+    <t>נייר</t>
+  </si>
+  <si>
+    <t>מספר נייר</t>
+  </si>
+  <si>
+    <t>סימבול</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
+    <t>כמות</t>
+  </si>
+  <si>
+    <t>שער אחרון</t>
+  </si>
+  <si>
+    <t>מטבע</t>
+  </si>
+  <si>
+    <t>שינוי יומי בסכום</t>
+  </si>
+  <si>
+    <t>שער עלות מותאם</t>
+  </si>
+  <si>
+    <t>שער עלות נומינלי</t>
+  </si>
+  <si>
+    <t>שינוי משער עלות מותאם בשח</t>
+  </si>
+  <si>
+    <t>שינוי משער עלות מותאם באחוז</t>
+  </si>
+  <si>
+    <t>שינוי משער עלות נומינלי בשח</t>
+  </si>
+  <si>
+    <t>שינוי משער עלות נומינלי באחוז</t>
+  </si>
+  <si>
+    <t>שווי אחזקה בשח</t>
+  </si>
+  <si>
+    <t>שווי אחזקה במטבע</t>
+  </si>
+  <si>
+    <t>הכנסה לקבל בשח</t>
+  </si>
+  <si>
+    <t>הכנסה לקבל במטבע</t>
+  </si>
+  <si>
+    <t>אחוז מהתיק</t>
+  </si>
+  <si>
+    <t>ריבית צבורה במטבע</t>
+  </si>
+  <si>
+    <t>ריבית צבורה בש"ח</t>
+  </si>
+  <si>
+    <t>ניע ישראלים</t>
+  </si>
+  <si>
+    <t>מניות</t>
+  </si>
+  <si>
+    <t>אטראו שוקי הון</t>
+  </si>
+  <si>
+    <t>1096106</t>
+  </si>
+  <si>
     <t>₪</t>
   </si>
   <si>
+    <t>אי.טי.ג'י.איי</t>
+  </si>
+  <si>
+    <t>1176114</t>
+  </si>
+  <si>
+    <t>אלטשולר שחם פנ</t>
+  </si>
+  <si>
+    <t>1184936</t>
+  </si>
+  <si>
+    <t>אפסלון ברנדס</t>
+  </si>
+  <si>
+    <t>456012</t>
+  </si>
+  <si>
+    <t>באבלס</t>
+  </si>
+  <si>
+    <t>1105139</t>
+  </si>
+  <si>
+    <t>גלוברנדס</t>
+  </si>
+  <si>
+    <t>1147487</t>
+  </si>
+  <si>
+    <t>ג'י סיטי</t>
+  </si>
+  <si>
+    <t>126011</t>
+  </si>
+  <si>
+    <t>ליברה</t>
+  </si>
+  <si>
+    <t>1176981</t>
+  </si>
+  <si>
+    <t>מיטרוניקס</t>
+  </si>
+  <si>
+    <t>1091065</t>
+  </si>
+  <si>
+    <t>מניף</t>
+  </si>
+  <si>
+    <t>1170893</t>
+  </si>
+  <si>
+    <t>נאוי</t>
+  </si>
+  <si>
+    <t>208017</t>
+  </si>
+  <si>
+    <t>נורסטאר</t>
+  </si>
+  <si>
+    <t>723007</t>
+  </si>
+  <si>
+    <t>פיקא אנטרפרייז</t>
+  </si>
+  <si>
+    <t>1174093</t>
+  </si>
+  <si>
+    <t>פליינג ספארק-ש</t>
+  </si>
+  <si>
+    <t>1173582</t>
+  </si>
+  <si>
+    <t>קונטיניואל-ש</t>
+  </si>
+  <si>
+    <t>1182260</t>
+  </si>
+  <si>
+    <t>ראלקו</t>
+  </si>
+  <si>
+    <t>393017</t>
+  </si>
+  <si>
+    <t>:סה"כ מניות</t>
+  </si>
+  <si>
+    <t>אג״ח</t>
+  </si>
+  <si>
+    <t>או פי סי אגח ב</t>
+  </si>
+  <si>
+    <t>1166057</t>
+  </si>
+  <si>
+    <t>אייסיאל אגח ז</t>
+  </si>
+  <si>
+    <t>2810372</t>
+  </si>
+  <si>
+    <t>אלומיי אגח ז</t>
+  </si>
+  <si>
+    <t>1217538</t>
+  </si>
+  <si>
+    <t>אלמוגים אגח יב</t>
+  </si>
+  <si>
+    <t>1217892</t>
+  </si>
+  <si>
+    <t>ביג אגח כ</t>
+  </si>
+  <si>
+    <t>1186188</t>
+  </si>
+  <si>
+    <t>23הכשרת ישוב אג</t>
+  </si>
+  <si>
+    <t>6120323</t>
+  </si>
+  <si>
+    <t>הראל הנפ אגח יח</t>
+  </si>
+  <si>
+    <t>1182666</t>
+  </si>
+  <si>
+    <t>יילוסטון אגח א</t>
+  </si>
+  <si>
+    <t>1242932</t>
+  </si>
+  <si>
+    <t>לוזון קב אג ט</t>
+  </si>
+  <si>
+    <t>4730180</t>
+  </si>
+  <si>
+    <t>מהדרין אגח ב</t>
+  </si>
+  <si>
+    <t>1236413</t>
+  </si>
+  <si>
+    <t>מודיעין אג ב</t>
+  </si>
+  <si>
+    <t>1210442</t>
+  </si>
+  <si>
+    <t>64 מז טפ הנ אגח</t>
+  </si>
+  <si>
+    <t>2310555</t>
+  </si>
+  <si>
+    <t>נמלי ישר אגחד</t>
+  </si>
+  <si>
+    <t>1175033</t>
+  </si>
+  <si>
+    <t>עזריאלי אגח ד</t>
+  </si>
+  <si>
+    <t>1138650</t>
+  </si>
+  <si>
+    <t>102 פועלים אגח</t>
+  </si>
+  <si>
+    <t>1223452</t>
+  </si>
+  <si>
+    <t>צור אגח י</t>
+  </si>
+  <si>
+    <t>7300171</t>
+  </si>
+  <si>
+    <t>:סה"כ אג״ח</t>
+  </si>
+  <si>
+    <t>קרנות נאמנות</t>
+  </si>
+  <si>
+    <t>$איביאי כספ נקב</t>
+  </si>
+  <si>
+    <t>5117429</t>
+  </si>
+  <si>
     <t>$</t>
   </si>
   <si>
-    <t>נייר</t>
-  </si>
-  <si>
-    <t>מספר נייר</t>
-  </si>
-  <si>
-    <t>סימבול</t>
-  </si>
-  <si>
-    <t>ISIN</t>
-  </si>
-  <si>
-    <t>כמות</t>
-  </si>
-  <si>
-    <t>שער אחרון</t>
-  </si>
-  <si>
-    <t>מטבע</t>
-  </si>
-  <si>
-    <t>שינוי יומי בסכום</t>
-  </si>
-  <si>
-    <t>שער עלות מותאם</t>
-  </si>
-  <si>
-    <t>שער עלות נומינלי</t>
-  </si>
-  <si>
-    <t>שינוי משער עלות מותאם בשח</t>
-  </si>
-  <si>
-    <t>שינוי משער עלות מותאם באחוז</t>
-  </si>
-  <si>
-    <t>שינוי משער עלות נומינלי בשח</t>
-  </si>
-  <si>
-    <t>שינוי משער עלות נומינלי באחוז</t>
-  </si>
-  <si>
-    <t>שווי אחזקה בשח</t>
-  </si>
-  <si>
-    <t>שווי אחזקה במטבע</t>
-  </si>
-  <si>
-    <t>הכנסה לקבל בשח</t>
-  </si>
-  <si>
-    <t>הכנסה לקבל במטבע</t>
-  </si>
-  <si>
-    <t>אחוז מהתיק</t>
-  </si>
-  <si>
-    <t>ריבית צבורה במטבע</t>
-  </si>
-  <si>
-    <t>ריבית צבורה בש"ח</t>
-  </si>
-  <si>
-    <t>ניע ישראלים</t>
-  </si>
-  <si>
-    <t>מניות</t>
-  </si>
-  <si>
-    <t>אטראו שוקי הון</t>
-  </si>
-  <si>
-    <t>1096106</t>
-  </si>
-  <si>
-    <t>אי.טי.ג'י.איי</t>
-  </si>
-  <si>
-    <t>1176114</t>
-  </si>
-  <si>
-    <t>אלטשולר שחם פנ</t>
-  </si>
-  <si>
-    <t>1184936</t>
-  </si>
-  <si>
-    <t>אפסלון ברנדס</t>
-  </si>
-  <si>
-    <t>456012</t>
-  </si>
-  <si>
-    <t>באבלס</t>
-  </si>
-  <si>
-    <t>1105139</t>
-  </si>
-  <si>
-    <t>גלוברנדס</t>
-  </si>
-  <si>
-    <t>1147487</t>
-  </si>
-  <si>
-    <t>ג'י סיטי</t>
-  </si>
-  <si>
-    <t>126011</t>
-  </si>
-  <si>
-    <t>טראקנט</t>
-  </si>
-  <si>
-    <t>1174093</t>
-  </si>
-  <si>
-    <t>ליברה</t>
-  </si>
-  <si>
-    <t>1176981</t>
-  </si>
-  <si>
-    <t>מיטרוניקס</t>
-  </si>
-  <si>
-    <t>1091065</t>
-  </si>
-  <si>
-    <t>מניף</t>
-  </si>
-  <si>
-    <t>1170893</t>
-  </si>
-  <si>
-    <t>נאוי</t>
-  </si>
-  <si>
-    <t>208017</t>
-  </si>
-  <si>
-    <t>נורסטאר</t>
-  </si>
-  <si>
-    <t>723007</t>
-  </si>
-  <si>
-    <t>פליינג ספארק-ש</t>
-  </si>
-  <si>
-    <t>1173582</t>
-  </si>
-  <si>
-    <t>קונטיניואל-ש</t>
-  </si>
-  <si>
-    <t>1182260</t>
-  </si>
-  <si>
-    <t>ראלקו</t>
-  </si>
-  <si>
-    <t>393017</t>
-  </si>
-  <si>
-    <t>:סה"כ מניות</t>
-  </si>
-  <si>
-    <t>אג״ח</t>
-  </si>
-  <si>
-    <t>או פי סי אגח ב</t>
-  </si>
-  <si>
-    <t>1166057</t>
-  </si>
-  <si>
-    <t>אייסיאל אגח ז</t>
-  </si>
-  <si>
-    <t>2810372</t>
-  </si>
-  <si>
-    <t>אלומיי אגח ז</t>
-  </si>
-  <si>
-    <t>1217538</t>
-  </si>
-  <si>
-    <t>אלמוגים אגח יב</t>
-  </si>
-  <si>
-    <t>1217892</t>
-  </si>
-  <si>
-    <t>ביג אגח כ</t>
-  </si>
-  <si>
-    <t>1186188</t>
-  </si>
-  <si>
-    <t>23הכשרת ישוב אג</t>
-  </si>
-  <si>
-    <t>6120323</t>
-  </si>
-  <si>
-    <t>הראל הנפ אגח יח</t>
-  </si>
-  <si>
-    <t>1182666</t>
-  </si>
-  <si>
-    <t>יילוסטון אגח א</t>
-  </si>
-  <si>
-    <t>1242932</t>
-  </si>
-  <si>
-    <t>לוזון קב אג ט</t>
-  </si>
-  <si>
-    <t>4730180</t>
-  </si>
-  <si>
-    <t>מהדרין אגח ב</t>
-  </si>
-  <si>
-    <t>1236413</t>
-  </si>
-  <si>
-    <t>מודיעין אג ב</t>
-  </si>
-  <si>
-    <t>1210442</t>
-  </si>
-  <si>
-    <t>64 מז טפ הנ אגח</t>
-  </si>
-  <si>
-    <t>2310555</t>
-  </si>
-  <si>
-    <t>נמלי ישר אגחד</t>
-  </si>
-  <si>
-    <t>1175033</t>
-  </si>
-  <si>
-    <t>עזריאלי אגח ד</t>
-  </si>
-  <si>
-    <t>1138650</t>
-  </si>
-  <si>
-    <t>102 פועלים אגח</t>
-  </si>
-  <si>
-    <t>1223452</t>
-  </si>
-  <si>
-    <t>צור אגח י</t>
-  </si>
-  <si>
-    <t>7300171</t>
-  </si>
-  <si>
-    <t>:סה"כ אג״ח</t>
-  </si>
-  <si>
-    <t>קרנות נאמנות</t>
-  </si>
-  <si>
-    <t>$איביאי כספ נקב</t>
-  </si>
-  <si>
-    <t>5117429</t>
-  </si>
-  <si>
     <t>אנלסט כספ חסכון</t>
   </si>
   <si>
@@ -338,6 +338,18 @@
   </si>
   <si>
     <t>:סה"כ מחקי מדד</t>
+  </si>
+  <si>
+    <t>נגזרים</t>
+  </si>
+  <si>
+    <t>2פלינג ספרק זכו</t>
+  </si>
+  <si>
+    <t>1247436</t>
+  </si>
+  <si>
+    <t>:סה"כ נגזרים</t>
   </si>
   <si>
     <t>ניע זרים</t>
@@ -744,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W64"/>
+  <dimension ref="A5:W75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -771,512 +783,31 @@
     <col min="23" max="23" width="24.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>0</v>
-      </c>
-      <c r="R1" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U1" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R2" t="s">
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
-        <v>0</v>
-      </c>
-      <c r="U2" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
-        <v>0</v>
-      </c>
-      <c r="W2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>0</v>
-      </c>
-      <c r="L4" t="s">
-        <v>0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>0</v>
-      </c>
-      <c r="P4" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>0</v>
-      </c>
-      <c r="R4" t="s">
-        <v>0</v>
-      </c>
-      <c r="S4" t="s">
-        <v>0</v>
-      </c>
-      <c r="T4" t="s">
-        <v>0</v>
-      </c>
-      <c r="U4" t="s">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>0</v>
-      </c>
-      <c r="W4" t="s">
-        <v>0</v>
-      </c>
-    </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>0</v>
-      </c>
-      <c r="M5" t="s">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P5" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>0</v>
-      </c>
-      <c r="R5" t="s">
-        <v>0</v>
-      </c>
-      <c r="S5" t="s">
-        <v>0</v>
-      </c>
-      <c r="T5" t="s">
-        <v>0</v>
-      </c>
-      <c r="U5" t="s">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
-        <v>0</v>
-      </c>
-      <c r="W5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>0</v>
-      </c>
-      <c r="P6" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>0</v>
-      </c>
-      <c r="R6" t="s">
-        <v>0</v>
-      </c>
-      <c r="S6" t="s">
-        <v>0</v>
-      </c>
-      <c r="T6" t="s">
-        <v>0</v>
-      </c>
-      <c r="U6" t="s">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
-        <v>0</v>
-      </c>
-      <c r="W6" t="s">
-        <v>0</v>
-      </c>
+      <c r="C5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="U5" s="1"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>0</v>
-      </c>
-      <c r="P7" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>0</v>
-      </c>
-      <c r="R7" t="s">
-        <v>0</v>
-      </c>
-      <c r="S7" t="s">
-        <v>0</v>
-      </c>
-      <c r="T7" t="s">
-        <v>0</v>
-      </c>
-      <c r="U7" t="s">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
-        <v>0</v>
-      </c>
-      <c r="W7" t="s">
-        <v>0</v>
-      </c>
+      <c r="C7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D8" t="s">
         <v>0</v>
@@ -1284,122 +815,130 @@
       <c r="E8" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="1">
-        <v>6433</v>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>0</v>
       </c>
       <c r="H8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T8" t="s">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
+        <v>0</v>
+      </c>
+      <c r="W8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="1">
-        <v>-3679.3</v>
-      </c>
-      <c r="J8" s="1">
-        <v>-5.41</v>
-      </c>
-      <c r="K8" s="1">
-        <v>6620.52</v>
-      </c>
-      <c r="L8" s="1">
-        <v>6725.05</v>
-      </c>
-      <c r="M8" s="1">
-        <v>-1875.18</v>
-      </c>
-      <c r="N8" s="1">
-        <v>-2.83</v>
-      </c>
-      <c r="O8" s="1">
-        <v>-2920.48</v>
-      </c>
-      <c r="P8" s="1">
-        <v>-4.34</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>64330</v>
-      </c>
-      <c r="R8" s="1">
-        <v>64330</v>
-      </c>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1">
-        <v>3.31</v>
-      </c>
-      <c r="V8" s="1">
-        <v>0</v>
-      </c>
-      <c r="W8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1500</v>
-      </c>
-      <c r="G9" s="1">
-        <v>2077</v>
-      </c>
-      <c r="H9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1">
-        <v>210.42</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1954.92</v>
-      </c>
-      <c r="L9" s="1">
-        <v>2001.82</v>
-      </c>
-      <c r="M9" s="1">
-        <v>1831.18</v>
-      </c>
-      <c r="N9" s="1">
-        <v>6.24</v>
-      </c>
-      <c r="O9" s="1">
-        <v>1127.71</v>
-      </c>
-      <c r="P9" s="1">
-        <v>3.75</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>31155</v>
-      </c>
-      <c r="R9" s="1">
-        <v>31155</v>
-      </c>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="V9" s="1">
-        <v>0</v>
-      </c>
-      <c r="W9" t="s">
-        <v>0</v>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
@@ -1407,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s">
         <v>0</v>
@@ -1418,55 +957,55 @@
       <c r="E10" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="1">
-        <v>9000</v>
-      </c>
-      <c r="G10" s="1">
-        <v>732</v>
+      <c r="F10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-1440.66</v>
-      </c>
-      <c r="J10" s="1">
-        <v>-2.14</v>
-      </c>
-      <c r="K10" s="1">
-        <v>629.78</v>
-      </c>
-      <c r="L10" s="1">
-        <v>673.72</v>
-      </c>
-      <c r="M10" s="1">
-        <v>9199.61</v>
-      </c>
-      <c r="N10" s="1">
-        <v>16.23</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5245.47</v>
-      </c>
-      <c r="P10" s="1">
-        <v>8.65</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>65880</v>
-      </c>
-      <c r="R10" s="1">
-        <v>65880</v>
-      </c>
-      <c r="S10" s="1">
-        <v>483.32</v>
-      </c>
-      <c r="T10" s="1">
-        <v>483.32</v>
-      </c>
-      <c r="U10" s="1">
-        <v>3.39</v>
-      </c>
-      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10" t="s">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>0</v>
       </c>
       <c r="W10" t="s">
@@ -1478,10 +1017,10 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
         <v>0</v>
@@ -1489,51 +1028,55 @@
       <c r="E11" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="1">
-        <v>85000</v>
-      </c>
-      <c r="G11" s="1">
-        <v>100.4</v>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1">
-        <v>508.99</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="K11" s="1">
-        <v>92.69</v>
-      </c>
-      <c r="L11" s="1">
-        <v>86</v>
-      </c>
-      <c r="M11" s="1">
-        <v>6551.28</v>
-      </c>
-      <c r="N11" s="1">
-        <v>8.31</v>
-      </c>
-      <c r="O11" s="1">
-        <v>12240.77</v>
-      </c>
-      <c r="P11" s="1">
-        <v>16.739999999999998</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>85340</v>
-      </c>
-      <c r="R11" s="1">
-        <v>85340</v>
-      </c>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
         <v>0</v>
       </c>
       <c r="W11" t="s">
@@ -1545,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D12" t="s">
         <v>0</v>
@@ -1556,51 +1099,55 @@
       <c r="E12" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="1">
-        <v>172500</v>
-      </c>
-      <c r="G12" s="1">
-        <v>12.9</v>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" s="1">
-        <v>-862.18</v>
-      </c>
-      <c r="J12" s="1">
-        <v>-3.73</v>
-      </c>
-      <c r="K12" s="1">
-        <v>18.760000000000002</v>
-      </c>
-      <c r="L12" s="1">
-        <v>18.78</v>
-      </c>
-      <c r="M12" s="1">
-        <v>-10101.42</v>
-      </c>
-      <c r="N12" s="1">
-        <v>-31.22</v>
-      </c>
-      <c r="O12" s="1">
-        <v>-10134.67</v>
-      </c>
-      <c r="P12" s="1">
-        <v>-31.29</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>22252.5</v>
-      </c>
-      <c r="R12" s="1">
-        <v>22252.5</v>
-      </c>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
+        <v>0</v>
+      </c>
+      <c r="U12" t="s">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
         <v>0</v>
       </c>
       <c r="W12" t="s">
@@ -1612,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D13" t="s">
         <v>0</v>
@@ -1623,51 +1170,55 @@
       <c r="E13" t="s">
         <v>0</v>
       </c>
-      <c r="F13" s="1">
-        <v>293</v>
-      </c>
-      <c r="G13" s="1">
-        <v>11120</v>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13" s="1">
-        <v>673.27</v>
-      </c>
-      <c r="J13" s="1">
-        <v>2.11</v>
-      </c>
-      <c r="K13" s="1">
-        <v>19220.14</v>
-      </c>
-      <c r="L13" s="1">
-        <v>19264.77</v>
-      </c>
-      <c r="M13" s="1">
-        <v>-23733.41</v>
-      </c>
-      <c r="N13" s="1">
-        <v>-42.14</v>
-      </c>
-      <c r="O13" s="1">
-        <v>-23864.16</v>
-      </c>
-      <c r="P13" s="1">
-        <v>-42.27</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>32581.599999999999</v>
-      </c>
-      <c r="R13" s="1">
-        <v>32581.599999999999</v>
-      </c>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>0</v>
+      </c>
+      <c r="P13" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>0</v>
+      </c>
+      <c r="T13" t="s">
+        <v>0</v>
+      </c>
+      <c r="U13" t="s">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
         <v>0</v>
       </c>
       <c r="W13" t="s">
@@ -1679,10 +1230,10 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
         <v>0</v>
@@ -1691,48 +1242,48 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="1">
-        <v>1118</v>
+        <v>6392</v>
       </c>
       <c r="H14" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I14" s="1">
-        <v>308.45</v>
+        <v>169.96</v>
       </c>
       <c r="J14" s="1">
-        <v>1.27</v>
+        <v>0.27</v>
       </c>
       <c r="K14" s="1">
-        <v>1374</v>
+        <v>6620.52</v>
       </c>
       <c r="L14" s="1">
-        <v>1375.24</v>
+        <v>6725.05</v>
       </c>
       <c r="M14" s="1">
-        <v>-5632</v>
+        <v>-2285.1799999999998</v>
       </c>
       <c r="N14" s="1">
-        <v>-18.63</v>
+        <v>-3.45</v>
       </c>
       <c r="O14" s="1">
-        <v>-5659.21</v>
+        <v>-3330.48</v>
       </c>
       <c r="P14" s="1">
-        <v>-18.7</v>
+        <v>-4.95</v>
       </c>
       <c r="Q14" s="1">
-        <v>24596</v>
+        <v>63920</v>
       </c>
       <c r="R14" s="1">
-        <v>24596</v>
+        <v>63920</v>
       </c>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="V14" s="1">
         <v>0</v>
@@ -1746,10 +1297,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
         <v>0</v>
@@ -1758,48 +1309,48 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="1">
-        <v>57.2</v>
+        <v>2242</v>
       </c>
       <c r="H15" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I15" s="1">
-        <v>32.99</v>
+        <v>449.99</v>
       </c>
       <c r="J15" s="1">
-        <v>6.12</v>
+        <v>1.36</v>
       </c>
       <c r="K15" s="1">
-        <v>55</v>
+        <v>1954.92</v>
       </c>
       <c r="L15" s="1">
-        <v>55.45</v>
+        <v>2001.82</v>
       </c>
       <c r="M15" s="1">
-        <v>22</v>
+        <v>4306.18</v>
       </c>
       <c r="N15" s="1">
-        <v>4</v>
+        <v>14.68</v>
       </c>
       <c r="O15" s="1">
-        <v>17.5</v>
+        <v>3602.71</v>
       </c>
       <c r="P15" s="1">
-        <v>3.15</v>
+        <v>11.99</v>
       </c>
       <c r="Q15" s="1">
-        <v>572</v>
+        <v>33630</v>
       </c>
       <c r="R15" s="1">
-        <v>572</v>
+        <v>33630</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1">
-        <v>0.03</v>
+        <v>1.73</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -1813,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
         <v>0</v>
@@ -1825,48 +1376,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="G16" s="1">
-        <v>3225</v>
+        <v>631</v>
       </c>
       <c r="H16" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I16" s="1">
-        <v>2191.2800000000002</v>
+        <v>-3483</v>
       </c>
       <c r="J16" s="1">
-        <v>7.29</v>
+        <v>-5.78</v>
       </c>
       <c r="K16" s="1">
-        <v>2472</v>
+        <v>624.41</v>
       </c>
       <c r="L16" s="1">
-        <v>2474.23</v>
+        <v>673.72</v>
       </c>
       <c r="M16" s="1">
-        <v>7529.99</v>
+        <v>592.92999999999995</v>
       </c>
       <c r="N16" s="1">
-        <v>30.46</v>
+        <v>1.05</v>
       </c>
       <c r="O16" s="1">
-        <v>7507.75</v>
+        <v>-3844.53</v>
       </c>
       <c r="P16" s="1">
-        <v>30.34</v>
+        <v>-6.34</v>
       </c>
       <c r="Q16" s="1">
-        <v>32250</v>
+        <v>56790</v>
       </c>
       <c r="R16" s="1">
-        <v>32250</v>
+        <v>56790</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1">
-        <v>1.66</v>
+        <v>2.92</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -1880,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
         <v>0</v>
@@ -1892,48 +1443,48 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>15000</v>
+        <v>85000</v>
       </c>
       <c r="G17" s="1">
-        <v>234.8</v>
+        <v>98.7</v>
       </c>
       <c r="H17" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I17" s="1">
-        <v>-781.23</v>
+        <v>-1614.94</v>
       </c>
       <c r="J17" s="1">
-        <v>-2.17</v>
+        <v>-1.89</v>
       </c>
       <c r="K17" s="1">
-        <v>317.23</v>
+        <v>92.69</v>
       </c>
       <c r="L17" s="1">
-        <v>318.69</v>
+        <v>86</v>
       </c>
       <c r="M17" s="1">
-        <v>-12364.89</v>
+        <v>5106.28</v>
       </c>
       <c r="N17" s="1">
-        <v>-25.98</v>
+        <v>6.48</v>
       </c>
       <c r="O17" s="1">
-        <v>-12582.98</v>
+        <v>10795.77</v>
       </c>
       <c r="P17" s="1">
-        <v>-26.32</v>
+        <v>14.76</v>
       </c>
       <c r="Q17" s="1">
-        <v>35220</v>
+        <v>83895</v>
       </c>
       <c r="R17" s="1">
-        <v>35220</v>
+        <v>83895</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1">
-        <v>1.81</v>
+        <v>4.32</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -1947,10 +1498,10 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
         <v>0</v>
@@ -1959,48 +1510,48 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>1350</v>
+        <v>172500</v>
       </c>
       <c r="G18" s="1">
-        <v>2231</v>
+        <v>12.1</v>
       </c>
       <c r="H18" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I18" s="1">
-        <v>-298.08</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2575.86</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="L18" s="1">
-        <v>2758.41</v>
+        <v>18.78</v>
       </c>
       <c r="M18" s="1">
-        <v>-4655.54</v>
+        <v>-11481.42</v>
       </c>
       <c r="N18" s="1">
-        <v>-13.38</v>
+        <v>-35.479999999999997</v>
       </c>
       <c r="O18" s="1">
-        <v>-7119.98</v>
+        <v>-11514.67</v>
       </c>
       <c r="P18" s="1">
-        <v>-19.11</v>
+        <v>-35.549999999999997</v>
       </c>
       <c r="Q18" s="1">
-        <v>30118.5</v>
+        <v>20872.5</v>
       </c>
       <c r="R18" s="1">
-        <v>30118.5</v>
+        <v>20872.5</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -2014,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
         <v>0</v>
@@ -2026,48 +1577,48 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>700</v>
+        <v>293</v>
       </c>
       <c r="G19" s="1">
-        <v>4780</v>
+        <v>10450</v>
       </c>
       <c r="H19" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I19" s="1">
-        <v>-561.35</v>
+        <v>-439.47</v>
       </c>
       <c r="J19" s="1">
-        <v>-1.65</v>
+        <v>-1.42</v>
       </c>
       <c r="K19" s="1">
-        <v>5547.95</v>
+        <v>19220.14</v>
       </c>
       <c r="L19" s="1">
-        <v>5657.95</v>
+        <v>19264.77</v>
       </c>
       <c r="M19" s="1">
-        <v>-5375.68</v>
+        <v>-25696.51</v>
       </c>
       <c r="N19" s="1">
-        <v>-13.84</v>
+        <v>-45.62</v>
       </c>
       <c r="O19" s="1">
-        <v>-6145.62</v>
+        <v>-25827.26</v>
       </c>
       <c r="P19" s="1">
-        <v>-15.51</v>
+        <v>-45.75</v>
       </c>
       <c r="Q19" s="1">
-        <v>33460</v>
+        <v>30618.5</v>
       </c>
       <c r="R19" s="1">
-        <v>33460</v>
+        <v>30618.5</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -2081,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
         <v>0</v>
@@ -2093,48 +1644,48 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="G20" s="1">
-        <v>727.2</v>
+        <v>1103</v>
       </c>
       <c r="H20" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I20" s="1">
-        <v>-152.94</v>
+        <v>-1715.98</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.72</v>
+        <v>-6.6</v>
       </c>
       <c r="K20" s="1">
-        <v>998</v>
+        <v>1354</v>
       </c>
       <c r="L20" s="1">
-        <v>998.9</v>
+        <v>1375.24</v>
       </c>
       <c r="M20" s="1">
-        <v>-7853.2</v>
+        <v>-5522</v>
       </c>
       <c r="N20" s="1">
-        <v>-27.13</v>
+        <v>-18.53</v>
       </c>
       <c r="O20" s="1">
-        <v>-7879.25</v>
+        <v>-5989.21</v>
       </c>
       <c r="P20" s="1">
-        <v>-27.19</v>
+        <v>-19.79</v>
       </c>
       <c r="Q20" s="1">
-        <v>21088.799999999999</v>
+        <v>24266</v>
       </c>
       <c r="R20" s="1">
-        <v>21088.799999999999</v>
+        <v>24266</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1">
-        <v>1.0900000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -2148,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
         <v>0</v>
@@ -2160,48 +1711,48 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>106391</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="1">
-        <v>30</v>
+        <v>3119</v>
       </c>
       <c r="H21" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I21" s="1">
-        <v>3191.44</v>
+        <v>-579.99</v>
       </c>
       <c r="J21" s="1">
-        <v>11.11</v>
+        <v>-1.83</v>
       </c>
       <c r="K21" s="1">
-        <v>39.97</v>
+        <v>2472</v>
       </c>
       <c r="L21" s="1">
-        <v>40.01</v>
+        <v>2474.23</v>
       </c>
       <c r="M21" s="1">
-        <v>-10601.86</v>
+        <v>6469.99</v>
       </c>
       <c r="N21" s="1">
-        <v>-24.93</v>
+        <v>26.17</v>
       </c>
       <c r="O21" s="1">
-        <v>-69497.63</v>
+        <v>6447.75</v>
       </c>
       <c r="P21" s="1">
-        <v>-25</v>
+        <v>26.05</v>
       </c>
       <c r="Q21" s="1">
-        <v>31917.3</v>
+        <v>31190</v>
       </c>
       <c r="R21" s="1">
-        <v>31917.3</v>
+        <v>31190</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -2215,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
         <v>0</v>
@@ -2227,48 +1778,48 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G22" s="1">
-        <v>94.8</v>
+        <v>210.4</v>
       </c>
       <c r="H22" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I22" s="1">
-        <v>0</v>
+        <v>-119.97</v>
       </c>
       <c r="J22" s="1">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="K22" s="1">
-        <v>109.9</v>
+        <v>317.23</v>
       </c>
       <c r="L22" s="1">
-        <v>110</v>
+        <v>318.69</v>
       </c>
       <c r="M22" s="1">
-        <v>-3020</v>
+        <v>-16024.89</v>
       </c>
       <c r="N22" s="1">
-        <v>-13.73</v>
+        <v>-33.67</v>
       </c>
       <c r="O22" s="1">
-        <v>-3039.78</v>
+        <v>-16242.98</v>
       </c>
       <c r="P22" s="1">
-        <v>-13.81</v>
+        <v>-33.97</v>
       </c>
       <c r="Q22" s="1">
-        <v>18960</v>
+        <v>31560</v>
       </c>
       <c r="R22" s="1">
-        <v>18960</v>
+        <v>31560</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1">
-        <v>0.98</v>
+        <v>1.62</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -2282,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
         <v>0</v>
@@ -2294,48 +1845,48 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>500</v>
+        <v>1350</v>
       </c>
       <c r="G23" s="1">
-        <v>4012</v>
+        <v>2184</v>
       </c>
       <c r="H23" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1">
-        <v>-64.400000000000006</v>
+        <v>-188.99</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.32</v>
+        <v>-0.64</v>
       </c>
       <c r="K23" s="1">
-        <v>4481.99</v>
+        <v>2575.86</v>
       </c>
       <c r="L23" s="1">
-        <v>4486.0200000000004</v>
+        <v>2758.41</v>
       </c>
       <c r="M23" s="1">
-        <v>-2349.9299999999998</v>
+        <v>-5290.04</v>
       </c>
       <c r="N23" s="1">
-        <v>-10.48</v>
+        <v>-15.21</v>
       </c>
       <c r="O23" s="1">
-        <v>-2370.09</v>
+        <v>-7754.48</v>
       </c>
       <c r="P23" s="1">
-        <v>-10.56</v>
+        <v>-20.82</v>
       </c>
       <c r="Q23" s="1">
-        <v>20060</v>
+        <v>29484</v>
       </c>
       <c r="R23" s="1">
-        <v>20060</v>
+        <v>29484</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -2349,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
         <v>0</v>
@@ -2360,55 +1911,51 @@
       <c r="E24" t="s">
         <v>0</v>
       </c>
-      <c r="F24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>0</v>
+      <c r="F24" s="1">
+        <v>700</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4562</v>
       </c>
       <c r="H24" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" t="s">
-        <v>0</v>
-      </c>
-      <c r="K24" t="s">
-        <v>0</v>
-      </c>
-      <c r="L24" t="s">
-        <v>0</v>
-      </c>
-      <c r="M24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>0</v>
-      </c>
-      <c r="P24" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>0</v>
-      </c>
-      <c r="R24" t="s">
-        <v>0</v>
-      </c>
-      <c r="S24" t="s">
-        <v>0</v>
-      </c>
-      <c r="T24" t="s">
-        <v>0</v>
-      </c>
-      <c r="U24" t="s">
-        <v>0</v>
-      </c>
-      <c r="V24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-258.99</v>
+      </c>
+      <c r="J24" s="1">
+        <v>-0.8</v>
+      </c>
+      <c r="K24" s="1">
+        <v>5547.95</v>
+      </c>
+      <c r="L24" s="1">
+        <v>5657.95</v>
+      </c>
+      <c r="M24" s="1">
+        <v>-6901.68</v>
+      </c>
+      <c r="N24" s="1">
+        <v>-17.77</v>
+      </c>
+      <c r="O24" s="1">
+        <v>-7671.62</v>
+      </c>
+      <c r="P24" s="1">
+        <v>-19.37</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>31934</v>
+      </c>
+      <c r="R24" s="1">
+        <v>31934</v>
+      </c>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="V24" s="1">
         <v>0</v>
       </c>
       <c r="W24" t="s">
@@ -2420,10 +1967,10 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
         <v>0</v>
@@ -2431,55 +1978,51 @@
       <c r="E25" t="s">
         <v>0</v>
       </c>
-      <c r="F25" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>0</v>
+      <c r="F25" s="1">
+        <v>2900</v>
+      </c>
+      <c r="G25" s="1">
+        <v>746.8</v>
       </c>
       <c r="H25" t="s">
-        <v>0</v>
-      </c>
-      <c r="I25" t="s">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>0</v>
-      </c>
-      <c r="K25" t="s">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>0</v>
-      </c>
-      <c r="M25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>0</v>
-      </c>
-      <c r="P25" t="s">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-211.69</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-0.97</v>
+      </c>
+      <c r="K25" s="1">
+        <v>998</v>
+      </c>
+      <c r="L25" s="1">
+        <v>998.9</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-7284.8</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-25.17</v>
+      </c>
+      <c r="O25" s="1">
+        <v>-7310.85</v>
+      </c>
+      <c r="P25" s="1">
+        <v>-25.23</v>
       </c>
       <c r="Q25" s="1">
-        <v>549781.69999999995</v>
-      </c>
-      <c r="R25" t="s">
-        <v>0</v>
-      </c>
-      <c r="S25" t="s">
-        <v>0</v>
-      </c>
-      <c r="T25" t="s">
-        <v>0</v>
-      </c>
-      <c r="U25" t="s">
-        <v>0</v>
-      </c>
-      <c r="V25" t="s">
+        <v>21657.200000000001</v>
+      </c>
+      <c r="R25" s="1">
+        <v>21657.200000000001</v>
+      </c>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="V25" s="1">
         <v>0</v>
       </c>
       <c r="W25" t="s">
@@ -2491,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
         <v>0</v>
@@ -2502,55 +2045,51 @@
       <c r="E26" t="s">
         <v>0</v>
       </c>
-      <c r="F26" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>0</v>
+      <c r="F26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G26" s="1">
+        <v>61.6</v>
       </c>
       <c r="H26" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" t="s">
-        <v>0</v>
-      </c>
-      <c r="J26" t="s">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s">
-        <v>0</v>
-      </c>
-      <c r="L26" t="s">
-        <v>0</v>
-      </c>
-      <c r="M26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>0</v>
-      </c>
-      <c r="P26" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>0</v>
-      </c>
-      <c r="R26" t="s">
-        <v>0</v>
-      </c>
-      <c r="S26" t="s">
-        <v>0</v>
-      </c>
-      <c r="T26" t="s">
-        <v>0</v>
-      </c>
-      <c r="U26" t="s">
-        <v>0</v>
-      </c>
-      <c r="V26" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="1">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="1">
+        <v>-2.5299999999999998</v>
+      </c>
+      <c r="K26" s="1">
+        <v>55</v>
+      </c>
+      <c r="L26" s="1">
+        <v>55.45</v>
+      </c>
+      <c r="M26" s="1">
+        <v>66</v>
+      </c>
+      <c r="N26" s="1">
+        <v>12</v>
+      </c>
+      <c r="O26" s="1">
+        <v>61.5</v>
+      </c>
+      <c r="P26" s="1">
+        <v>11.09</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>616</v>
+      </c>
+      <c r="R26" s="1">
+        <v>616</v>
+      </c>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="V26" s="1">
         <v>0</v>
       </c>
       <c r="W26" t="s">
@@ -2562,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
         <v>0</v>
@@ -2573,55 +2112,51 @@
       <c r="E27" t="s">
         <v>0</v>
       </c>
-      <c r="F27" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s">
-        <v>0</v>
+      <c r="F27" s="1">
+        <v>208356</v>
+      </c>
+      <c r="G27" s="1">
+        <v>26.4</v>
       </c>
       <c r="H27" t="s">
-        <v>0</v>
-      </c>
-      <c r="I27" t="s">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
-        <v>0</v>
-      </c>
-      <c r="K27" t="s">
-        <v>0</v>
-      </c>
-      <c r="L27" t="s">
-        <v>0</v>
-      </c>
-      <c r="M27" t="s">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>0</v>
-      </c>
-      <c r="P27" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>0</v>
-      </c>
-      <c r="R27" t="s">
-        <v>0</v>
-      </c>
-      <c r="S27" t="s">
-        <v>0</v>
-      </c>
-      <c r="T27" t="s">
-        <v>0</v>
-      </c>
-      <c r="U27" t="s">
-        <v>0</v>
-      </c>
-      <c r="V27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-1250.1199999999999</v>
+      </c>
+      <c r="J27" s="1">
+        <v>-2.2200000000000002</v>
+      </c>
+      <c r="K27" s="1">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="L27" s="1">
+        <v>33.14</v>
+      </c>
+      <c r="M27" s="1">
+        <v>-14024.02</v>
+      </c>
+      <c r="N27" s="1">
+        <v>-20.309999999999999</v>
+      </c>
+      <c r="O27" s="1">
+        <v>-14045.76</v>
+      </c>
+      <c r="P27" s="1">
+        <v>-20.34</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>55005.98</v>
+      </c>
+      <c r="R27" s="1">
+        <v>55005.98</v>
+      </c>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1">
+        <v>2.83</v>
+      </c>
+      <c r="V27" s="1">
         <v>0</v>
       </c>
       <c r="W27" t="s">
@@ -2633,10 +2168,10 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
         <v>0</v>
@@ -2645,48 +2180,48 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="G28" s="1">
-        <v>121.84</v>
+        <v>94.8</v>
       </c>
       <c r="H28" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I28" s="1">
-        <v>-7.31</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>120.64</v>
+        <v>109.9</v>
       </c>
       <c r="L28" s="1">
-        <v>120.76</v>
+        <v>110</v>
       </c>
       <c r="M28" s="1">
-        <v>360.11</v>
+        <v>-3020</v>
       </c>
       <c r="N28" s="1">
-        <v>0.99</v>
+        <v>-13.73</v>
       </c>
       <c r="O28" s="1">
-        <v>323.23</v>
+        <v>-3039.78</v>
       </c>
       <c r="P28" s="1">
-        <v>0.89</v>
+        <v>-13.81</v>
       </c>
       <c r="Q28" s="1">
-        <v>36552</v>
+        <v>18960</v>
       </c>
       <c r="R28" s="1">
-        <v>36552</v>
+        <v>18960</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1">
-        <v>1.88</v>
+        <v>0.98</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
@@ -2700,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
         <v>0</v>
@@ -2712,48 +2247,48 @@
         <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>75688.77</v>
+        <v>500</v>
       </c>
       <c r="G29" s="1">
-        <v>88.7</v>
+        <v>4306</v>
       </c>
       <c r="H29" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I29" s="1">
-        <v>0</v>
+        <v>29.99</v>
       </c>
       <c r="J29" s="1">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K29" s="1">
-        <v>74.53</v>
+        <v>4481.99</v>
       </c>
       <c r="L29" s="1">
-        <v>81.37</v>
+        <v>4486.0200000000004</v>
       </c>
       <c r="M29" s="1">
-        <v>10729.03</v>
+        <v>-879.93</v>
       </c>
       <c r="N29" s="1">
-        <v>19.02</v>
+        <v>-3.92</v>
       </c>
       <c r="O29" s="1">
-        <v>5548.02</v>
+        <v>-900.09</v>
       </c>
       <c r="P29" s="1">
-        <v>9</v>
+        <v>-4.01</v>
       </c>
       <c r="Q29" s="1">
-        <v>67135.94</v>
+        <v>21530</v>
       </c>
       <c r="R29" s="1">
-        <v>67135.94</v>
+        <v>21530</v>
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1">
-        <v>3.46</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
@@ -2767,10 +2302,10 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -2778,51 +2313,55 @@
       <c r="E30" t="s">
         <v>0</v>
       </c>
-      <c r="F30" s="1">
-        <v>50000</v>
-      </c>
-      <c r="G30" s="1">
-        <v>103.28</v>
+      <c r="F30" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>2</v>
-      </c>
-      <c r="I30" s="1">
-        <v>-463.72</v>
-      </c>
-      <c r="J30" s="1">
-        <v>-0.89</v>
-      </c>
-      <c r="K30" s="1">
-        <v>99.28</v>
-      </c>
-      <c r="L30" s="1">
-        <v>102.54</v>
-      </c>
-      <c r="M30" s="1">
-        <v>1998.69</v>
-      </c>
-      <c r="N30" s="1">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="O30" s="1">
-        <v>371.4</v>
-      </c>
-      <c r="P30" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>51640</v>
-      </c>
-      <c r="R30" s="1">
-        <v>51640</v>
-      </c>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1">
-        <v>2.66</v>
-      </c>
-      <c r="V30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>0</v>
+      </c>
+      <c r="P30" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>0</v>
+      </c>
+      <c r="R30" t="s">
+        <v>0</v>
+      </c>
+      <c r="S30" t="s">
+        <v>0</v>
+      </c>
+      <c r="T30" t="s">
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
+        <v>0</v>
+      </c>
+      <c r="V30" t="s">
         <v>0</v>
       </c>
       <c r="W30" t="s">
@@ -2834,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D31" t="s">
         <v>0</v>
@@ -2845,51 +2384,55 @@
       <c r="E31" t="s">
         <v>0</v>
       </c>
-      <c r="F31" s="1">
-        <v>25000</v>
-      </c>
-      <c r="G31" s="1">
-        <v>97.93</v>
+      <c r="F31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>2</v>
-      </c>
-      <c r="I31" s="1">
-        <v>-108.2</v>
-      </c>
-      <c r="J31" s="1">
-        <v>-0.44</v>
-      </c>
-      <c r="K31" s="1">
-        <v>97.53</v>
-      </c>
-      <c r="L31" s="1">
-        <v>100.91</v>
-      </c>
-      <c r="M31" s="1">
-        <v>100.97</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0.41</v>
-      </c>
-      <c r="O31" s="1">
-        <v>-745.47</v>
-      </c>
-      <c r="P31" s="1">
-        <v>-2.95</v>
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>0</v>
+      </c>
+      <c r="J31" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>0</v>
       </c>
       <c r="Q31" s="1">
-        <v>24482.5</v>
-      </c>
-      <c r="R31" s="1">
-        <v>24482.5</v>
-      </c>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1">
-        <v>1.26</v>
-      </c>
-      <c r="V31" s="1">
+        <v>555929.18000000005</v>
+      </c>
+      <c r="R31" t="s">
+        <v>0</v>
+      </c>
+      <c r="S31" t="s">
+        <v>0</v>
+      </c>
+      <c r="T31" t="s">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>0</v>
+      </c>
+      <c r="V31" t="s">
         <v>0</v>
       </c>
       <c r="W31" t="s">
@@ -2901,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D32" t="s">
         <v>0</v>
@@ -2912,51 +2455,55 @@
       <c r="E32" t="s">
         <v>0</v>
       </c>
-      <c r="F32" s="1">
-        <v>80257.09</v>
-      </c>
-      <c r="G32" s="1">
-        <v>112.84</v>
+      <c r="F32" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I32" s="1">
-        <v>-18.12</v>
-      </c>
-      <c r="J32" s="1">
-        <v>-0.02</v>
-      </c>
-      <c r="K32" s="1">
-        <v>94.06</v>
-      </c>
-      <c r="L32" s="1">
-        <v>99.76</v>
-      </c>
-      <c r="M32" s="1">
-        <v>15069.31</v>
-      </c>
-      <c r="N32" s="1">
-        <v>19.96</v>
-      </c>
-      <c r="O32" s="1">
-        <v>10500.75</v>
-      </c>
-      <c r="P32" s="1">
-        <v>13.11</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>90562.1</v>
-      </c>
-      <c r="R32" s="1">
-        <v>90562.1</v>
-      </c>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1">
-        <v>4.67</v>
-      </c>
-      <c r="V32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>0</v>
+      </c>
+      <c r="L32" t="s">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>0</v>
+      </c>
+      <c r="R32" t="s">
+        <v>0</v>
+      </c>
+      <c r="S32" t="s">
+        <v>0</v>
+      </c>
+      <c r="T32" t="s">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>0</v>
+      </c>
+      <c r="V32" t="s">
         <v>0</v>
       </c>
       <c r="W32" t="s">
@@ -2968,10 +2515,10 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D33" t="s">
         <v>0</v>
@@ -2979,51 +2526,55 @@
       <c r="E33" t="s">
         <v>0</v>
       </c>
-      <c r="F33" s="1">
-        <v>23000</v>
-      </c>
-      <c r="G33" s="1">
-        <v>121.62</v>
+      <c r="F33" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>2</v>
-      </c>
-      <c r="I33" s="1">
-        <v>-2.8</v>
-      </c>
-      <c r="J33" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="K33" s="1">
-        <v>120.19</v>
-      </c>
-      <c r="L33" s="1">
-        <v>120.3</v>
-      </c>
-      <c r="M33" s="1">
-        <v>328.89</v>
-      </c>
-      <c r="N33" s="1">
-        <v>1.18</v>
-      </c>
-      <c r="O33" s="1">
-        <v>304.02</v>
-      </c>
-      <c r="P33" s="1">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>27972.6</v>
-      </c>
-      <c r="R33" s="1">
-        <v>27972.6</v>
-      </c>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="V33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>0</v>
+      </c>
+      <c r="P33" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>0</v>
+      </c>
+      <c r="R33" t="s">
+        <v>0</v>
+      </c>
+      <c r="S33" t="s">
+        <v>0</v>
+      </c>
+      <c r="T33" t="s">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
+        <v>0</v>
+      </c>
+      <c r="V33" t="s">
         <v>0</v>
       </c>
       <c r="W33" t="s">
@@ -3035,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
         <v>0</v>
@@ -3047,48 +2598,48 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>100000</v>
+        <v>27794.12</v>
       </c>
       <c r="G34" s="1">
-        <v>91.32</v>
+        <v>120.43</v>
       </c>
       <c r="H34" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I34" s="1">
-        <v>-128.03</v>
+        <v>22.21</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.14000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K34" s="1">
-        <v>74.83</v>
+        <v>118.86</v>
       </c>
       <c r="L34" s="1">
-        <v>82.14</v>
+        <v>120.75</v>
       </c>
       <c r="M34" s="1">
-        <v>16492.490000000002</v>
+        <v>436.14</v>
       </c>
       <c r="N34" s="1">
-        <v>22.04</v>
+        <v>1.32</v>
       </c>
       <c r="O34" s="1">
-        <v>9177.93</v>
+        <v>-88.54</v>
       </c>
       <c r="P34" s="1">
-        <v>11.17</v>
+        <v>-0.26</v>
       </c>
       <c r="Q34" s="1">
-        <v>91320</v>
+        <v>33472.46</v>
       </c>
       <c r="R34" s="1">
-        <v>91320</v>
+        <v>33472.46</v>
       </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1">
-        <v>4.7</v>
+        <v>1.72</v>
       </c>
       <c r="V34" s="1">
         <v>0</v>
@@ -3102,10 +2653,10 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D35" t="s">
         <v>0</v>
@@ -3114,48 +2665,48 @@
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>45000</v>
+        <v>75688.77</v>
       </c>
       <c r="G35" s="1">
-        <v>100.17</v>
+        <v>88.16</v>
       </c>
       <c r="H35" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I35" s="1">
-        <v>-299.48</v>
+        <v>-121.06</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.66</v>
+        <v>-0.18</v>
       </c>
       <c r="K35" s="1">
-        <v>102.23</v>
+        <v>74.53</v>
       </c>
       <c r="L35" s="1">
-        <v>102.33</v>
+        <v>81.37</v>
       </c>
       <c r="M35" s="1">
-        <v>-928.48</v>
+        <v>10320.31</v>
       </c>
       <c r="N35" s="1">
-        <v>-2.0099999999999998</v>
+        <v>18.29</v>
       </c>
       <c r="O35" s="1">
-        <v>-969.9</v>
+        <v>5139.3</v>
       </c>
       <c r="P35" s="1">
-        <v>-2.1</v>
+        <v>8.34</v>
       </c>
       <c r="Q35" s="1">
-        <v>45076.5</v>
+        <v>66727.22</v>
       </c>
       <c r="R35" s="1">
-        <v>45076.5</v>
+        <v>66727.22</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1">
-        <v>2.3199999999999998</v>
+        <v>3.43</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -3169,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
         <v>0</v>
@@ -3181,48 +2732,48 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="G36" s="1">
-        <v>99.8</v>
+        <v>104</v>
       </c>
       <c r="H36" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I36" s="1">
-        <v>0</v>
+        <v>-99.98</v>
       </c>
       <c r="J36" s="1">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="K36" s="1">
-        <v>99</v>
+        <v>99.28</v>
       </c>
       <c r="L36" s="1">
-        <v>99.09</v>
+        <v>102.54</v>
       </c>
       <c r="M36" s="1">
-        <v>239.99</v>
+        <v>2358.69</v>
       </c>
       <c r="N36" s="1">
-        <v>0.8</v>
+        <v>4.75</v>
       </c>
       <c r="O36" s="1">
-        <v>213.27</v>
+        <v>731.4</v>
       </c>
       <c r="P36" s="1">
-        <v>0.71</v>
+        <v>1.42</v>
       </c>
       <c r="Q36" s="1">
-        <v>29940</v>
+        <v>52000</v>
       </c>
       <c r="R36" s="1">
-        <v>29940</v>
+        <v>52000</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1">
-        <v>1.54</v>
+        <v>2.68</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -3236,10 +2787,10 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
         <v>0</v>
@@ -3248,48 +2799,48 @@
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>25133</v>
+        <v>25000</v>
       </c>
       <c r="G37" s="1">
-        <v>100.42</v>
+        <v>98</v>
       </c>
       <c r="H37" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I37" s="1">
-        <v>-91.19</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.36</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K37" s="1">
         <v>97.53</v>
       </c>
       <c r="L37" s="1">
-        <v>99.56</v>
+        <v>100.91</v>
       </c>
       <c r="M37" s="1">
-        <v>726.79</v>
+        <v>118.47</v>
       </c>
       <c r="N37" s="1">
-        <v>2.96</v>
+        <v>0.48</v>
       </c>
       <c r="O37" s="1">
-        <v>216.26</v>
+        <v>-727.97</v>
       </c>
       <c r="P37" s="1">
-        <v>0.86</v>
+        <v>-2.88</v>
       </c>
       <c r="Q37" s="1">
-        <v>25238.560000000001</v>
+        <v>24500</v>
       </c>
       <c r="R37" s="1">
-        <v>25238.560000000001</v>
+        <v>24500</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
@@ -3303,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
         <v>0</v>
@@ -3315,48 +2866,48 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>40000</v>
+        <v>80257.09</v>
       </c>
       <c r="G38" s="1">
-        <v>98.1</v>
+        <v>112.44</v>
       </c>
       <c r="H38" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I38" s="1">
-        <v>78.319999999999993</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>84.49</v>
+        <v>94.06</v>
       </c>
       <c r="L38" s="1">
-        <v>94.72</v>
+        <v>99.76</v>
       </c>
       <c r="M38" s="1">
-        <v>5443.63</v>
+        <v>14748.28</v>
       </c>
       <c r="N38" s="1">
-        <v>16.100000000000001</v>
+        <v>19.53</v>
       </c>
       <c r="O38" s="1">
-        <v>1352.16</v>
+        <v>10179.719999999999</v>
       </c>
       <c r="P38" s="1">
-        <v>3.56</v>
+        <v>12.71</v>
       </c>
       <c r="Q38" s="1">
-        <v>39240</v>
+        <v>90241.07</v>
       </c>
       <c r="R38" s="1">
-        <v>39240</v>
+        <v>90241.07</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <v>2.02</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -3370,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D39" t="s">
         <v>0</v>
@@ -3382,48 +2933,48 @@
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>41667.919999999998</v>
+        <v>23000</v>
       </c>
       <c r="G39" s="1">
-        <v>110.16</v>
+        <v>121.74</v>
       </c>
       <c r="H39" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I39" s="1">
-        <v>13.77</v>
+        <v>-4.59</v>
       </c>
       <c r="J39" s="1">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="K39" s="1">
-        <v>107.93</v>
+        <v>120.19</v>
       </c>
       <c r="L39" s="1">
-        <v>108.14</v>
+        <v>120.3</v>
       </c>
       <c r="M39" s="1">
-        <v>931.02</v>
+        <v>356.49</v>
       </c>
       <c r="N39" s="1">
-        <v>2.0699999999999998</v>
+        <v>1.28</v>
       </c>
       <c r="O39" s="1">
-        <v>842.84</v>
+        <v>331.62</v>
       </c>
       <c r="P39" s="1">
-        <v>1.87</v>
+        <v>1.19</v>
       </c>
       <c r="Q39" s="1">
-        <v>45901.38</v>
+        <v>28000.2</v>
       </c>
       <c r="R39" s="1">
-        <v>45901.38</v>
+        <v>28000.2</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <v>2.36</v>
+        <v>1.44</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -3437,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
         <v>0</v>
@@ -3449,48 +3000,48 @@
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>61602</v>
+        <v>100000</v>
       </c>
       <c r="G40" s="1">
-        <v>95.42</v>
+        <v>91.08</v>
       </c>
       <c r="H40" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I40" s="1">
-        <v>70.45</v>
+        <v>-99.93</v>
       </c>
       <c r="J40" s="1">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="K40" s="1">
-        <v>86.1</v>
+        <v>74.83</v>
       </c>
       <c r="L40" s="1">
-        <v>88.3</v>
+        <v>82.14</v>
       </c>
       <c r="M40" s="1">
-        <v>5740.25</v>
+        <v>16252.49</v>
       </c>
       <c r="N40" s="1">
-        <v>10.82</v>
+        <v>21.71</v>
       </c>
       <c r="O40" s="1">
-        <v>4383.8599999999997</v>
+        <v>8937.93</v>
       </c>
       <c r="P40" s="1">
-        <v>8.0500000000000007</v>
+        <v>10.88</v>
       </c>
       <c r="Q40" s="1">
-        <v>58780.63</v>
+        <v>91080</v>
       </c>
       <c r="R40" s="1">
-        <v>58780.63</v>
+        <v>91080</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1">
-        <v>3.03</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
@@ -3504,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
         <v>0</v>
@@ -3516,48 +3067,48 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>57435.9</v>
+        <v>45000</v>
       </c>
       <c r="G41" s="1">
-        <v>119.63</v>
+        <v>100.75</v>
       </c>
       <c r="H41" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I41" s="1">
-        <v>0</v>
+        <v>-13.47</v>
       </c>
       <c r="J41" s="1">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="K41" s="1">
-        <v>106.92</v>
+        <v>102.23</v>
       </c>
       <c r="L41" s="1">
-        <v>110.63</v>
+        <v>102.33</v>
       </c>
       <c r="M41" s="1">
-        <v>7299.81</v>
+        <v>-667.48</v>
       </c>
       <c r="N41" s="1">
-        <v>11.88</v>
+        <v>-1.45</v>
       </c>
       <c r="O41" s="1">
-        <v>5166.88</v>
+        <v>-708.9</v>
       </c>
       <c r="P41" s="1">
-        <v>8.1300000000000008</v>
+        <v>-1.53</v>
       </c>
       <c r="Q41" s="1">
-        <v>68710.570000000007</v>
+        <v>45337.5</v>
       </c>
       <c r="R41" s="1">
-        <v>68710.570000000007</v>
+        <v>45337.5</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1">
-        <v>3.54</v>
+        <v>2.33</v>
       </c>
       <c r="V41" s="1">
         <v>0</v>
@@ -3571,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
         <v>0</v>
@@ -3583,48 +3134,48 @@
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="G42" s="1">
-        <v>103.67</v>
+        <v>99.8</v>
       </c>
       <c r="H42" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I42" s="1">
-        <v>-46.7</v>
+        <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>101.08</v>
+        <v>99</v>
       </c>
       <c r="L42" s="1">
-        <v>106.6</v>
+        <v>99.09</v>
       </c>
       <c r="M42" s="1">
-        <v>1166.48</v>
+        <v>239.99</v>
       </c>
       <c r="N42" s="1">
-        <v>2.56</v>
+        <v>0.8</v>
       </c>
       <c r="O42" s="1">
-        <v>-1316.62</v>
+        <v>213.27</v>
       </c>
       <c r="P42" s="1">
-        <v>-2.74</v>
+        <v>0.71</v>
       </c>
       <c r="Q42" s="1">
-        <v>46651.5</v>
+        <v>29940</v>
       </c>
       <c r="R42" s="1">
-        <v>46651.5</v>
+        <v>29940</v>
       </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -3638,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
         <v>0</v>
@@ -3650,48 +3201,48 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>24000</v>
+        <v>25133</v>
       </c>
       <c r="G43" s="1">
-        <v>121.85</v>
+        <v>99.93</v>
       </c>
       <c r="H43" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I43" s="1">
-        <v>35.049999999999997</v>
+        <v>-40.200000000000003</v>
       </c>
       <c r="J43" s="1">
-        <v>0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="K43" s="1">
-        <v>121</v>
+        <v>97.53</v>
       </c>
       <c r="L43" s="1">
-        <v>121.13</v>
+        <v>99.56</v>
       </c>
       <c r="M43" s="1">
-        <v>203.99</v>
+        <v>603.64</v>
       </c>
       <c r="N43" s="1">
-        <v>0.7</v>
+        <v>2.46</v>
       </c>
       <c r="O43" s="1">
-        <v>173.41</v>
+        <v>93.11</v>
       </c>
       <c r="P43" s="1">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="Q43" s="1">
-        <v>29244</v>
+        <v>25115.41</v>
       </c>
       <c r="R43" s="1">
-        <v>29244</v>
+        <v>25115.41</v>
       </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -3705,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C44" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
         <v>0</v>
@@ -3716,55 +3267,51 @@
       <c r="E44" t="s">
         <v>0</v>
       </c>
-      <c r="F44" t="s">
-        <v>0</v>
-      </c>
-      <c r="G44" t="s">
-        <v>0</v>
+      <c r="F44" s="1">
+        <v>40000</v>
+      </c>
+      <c r="G44" s="1">
+        <v>102.7</v>
       </c>
       <c r="H44" t="s">
-        <v>0</v>
-      </c>
-      <c r="I44" t="s">
-        <v>0</v>
-      </c>
-      <c r="J44" t="s">
-        <v>0</v>
-      </c>
-      <c r="K44" t="s">
-        <v>0</v>
-      </c>
-      <c r="L44" t="s">
-        <v>0</v>
-      </c>
-      <c r="M44" t="s">
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
-        <v>0</v>
-      </c>
-      <c r="P44" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>0</v>
-      </c>
-      <c r="R44" t="s">
-        <v>0</v>
-      </c>
-      <c r="S44" t="s">
-        <v>0</v>
-      </c>
-      <c r="T44" t="s">
-        <v>0</v>
-      </c>
-      <c r="U44" t="s">
-        <v>0</v>
-      </c>
-      <c r="V44" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" s="1">
+        <v>359.97</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="K44" s="1">
+        <v>81.650000000000006</v>
+      </c>
+      <c r="L44" s="1">
+        <v>94.72</v>
+      </c>
+      <c r="M44" s="1">
+        <v>8421.7099999999991</v>
+      </c>
+      <c r="N44" s="1">
+        <v>25.78</v>
+      </c>
+      <c r="O44" s="1">
+        <v>3192.16</v>
+      </c>
+      <c r="P44" s="1">
+        <v>8.42</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>41080</v>
+      </c>
+      <c r="R44" s="1">
+        <v>41080</v>
+      </c>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1">
+        <v>2.11</v>
+      </c>
+      <c r="V44" s="1">
         <v>0</v>
       </c>
       <c r="W44" t="s">
@@ -3776,10 +3323,10 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C45" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D45" t="s">
         <v>0</v>
@@ -3787,55 +3334,51 @@
       <c r="E45" t="s">
         <v>0</v>
       </c>
-      <c r="F45" t="s">
-        <v>0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>0</v>
+      <c r="F45" s="1">
+        <v>41667.919999999998</v>
+      </c>
+      <c r="G45" s="1">
+        <v>110.03</v>
       </c>
       <c r="H45" t="s">
-        <v>0</v>
-      </c>
-      <c r="I45" t="s">
-        <v>0</v>
-      </c>
-      <c r="J45" t="s">
-        <v>0</v>
-      </c>
-      <c r="K45" t="s">
-        <v>0</v>
-      </c>
-      <c r="L45" t="s">
-        <v>0</v>
-      </c>
-      <c r="M45" t="s">
-        <v>0</v>
-      </c>
-      <c r="N45" t="s">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>0</v>
-      </c>
-      <c r="P45" t="s">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="I45" s="1">
+        <v>-16.649999999999999</v>
+      </c>
+      <c r="J45" s="1">
+        <v>-0.04</v>
+      </c>
+      <c r="K45" s="1">
+        <v>107.93</v>
+      </c>
+      <c r="L45" s="1">
+        <v>108.14</v>
+      </c>
+      <c r="M45" s="1">
+        <v>876.85</v>
+      </c>
+      <c r="N45" s="1">
+        <v>1.94</v>
+      </c>
+      <c r="O45" s="1">
+        <v>788.67</v>
+      </c>
+      <c r="P45" s="1">
+        <v>1.75</v>
       </c>
       <c r="Q45" s="1">
-        <v>778448.28</v>
-      </c>
-      <c r="R45" t="s">
-        <v>0</v>
-      </c>
-      <c r="S45" t="s">
-        <v>0</v>
-      </c>
-      <c r="T45" t="s">
-        <v>0</v>
-      </c>
-      <c r="U45" t="s">
-        <v>0</v>
-      </c>
-      <c r="V45" t="s">
+        <v>45847.21</v>
+      </c>
+      <c r="R45" s="1">
+        <v>45847.21</v>
+      </c>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1">
+        <v>2.36</v>
+      </c>
+      <c r="V45" s="1">
         <v>0</v>
       </c>
       <c r="W45" t="s">
@@ -3847,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
         <v>0</v>
@@ -3858,55 +3401,51 @@
       <c r="E46" t="s">
         <v>0</v>
       </c>
-      <c r="F46" t="s">
-        <v>0</v>
-      </c>
-      <c r="G46" t="s">
-        <v>0</v>
+      <c r="F46" s="1">
+        <v>61602</v>
+      </c>
+      <c r="G46" s="1">
+        <v>95.67</v>
       </c>
       <c r="H46" t="s">
-        <v>0</v>
-      </c>
-      <c r="I46" t="s">
-        <v>0</v>
-      </c>
-      <c r="J46" t="s">
-        <v>0</v>
-      </c>
-      <c r="K46" t="s">
-        <v>0</v>
-      </c>
-      <c r="L46" t="s">
-        <v>0</v>
-      </c>
-      <c r="M46" t="s">
-        <v>0</v>
-      </c>
-      <c r="N46" t="s">
-        <v>0</v>
-      </c>
-      <c r="O46" t="s">
-        <v>0</v>
-      </c>
-      <c r="P46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>0</v>
-      </c>
-      <c r="R46" t="s">
-        <v>0</v>
-      </c>
-      <c r="S46" t="s">
-        <v>0</v>
-      </c>
-      <c r="T46" t="s">
-        <v>0</v>
-      </c>
-      <c r="U46" t="s">
-        <v>0</v>
-      </c>
-      <c r="V46" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" s="1">
+        <v>-197.09</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-0.33</v>
+      </c>
+      <c r="K46" s="1">
+        <v>86.1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>88.3</v>
+      </c>
+      <c r="M46" s="1">
+        <v>5894.26</v>
+      </c>
+      <c r="N46" s="1">
+        <v>11.11</v>
+      </c>
+      <c r="O46" s="1">
+        <v>4537.8599999999997</v>
+      </c>
+      <c r="P46" s="1">
+        <v>8.34</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>58934.63</v>
+      </c>
+      <c r="R46" s="1">
+        <v>58934.63</v>
+      </c>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1">
+        <v>3.03</v>
+      </c>
+      <c r="V46" s="1">
         <v>0</v>
       </c>
       <c r="W46" t="s">
@@ -3918,10 +3457,10 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="D47" t="s">
         <v>0</v>
@@ -3929,55 +3468,51 @@
       <c r="E47" t="s">
         <v>0</v>
       </c>
-      <c r="F47" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" t="s">
-        <v>0</v>
+      <c r="F47" s="1">
+        <v>57435.9</v>
+      </c>
+      <c r="G47" s="1">
+        <v>119.64</v>
       </c>
       <c r="H47" t="s">
-        <v>0</v>
-      </c>
-      <c r="I47" t="s">
-        <v>0</v>
-      </c>
-      <c r="J47" t="s">
-        <v>0</v>
-      </c>
-      <c r="K47" t="s">
-        <v>0</v>
-      </c>
-      <c r="L47" t="s">
-        <v>0</v>
-      </c>
-      <c r="M47" t="s">
-        <v>0</v>
-      </c>
-      <c r="N47" t="s">
-        <v>0</v>
-      </c>
-      <c r="O47" t="s">
-        <v>0</v>
-      </c>
-      <c r="P47" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>0</v>
-      </c>
-      <c r="R47" t="s">
-        <v>0</v>
-      </c>
-      <c r="S47" t="s">
-        <v>0</v>
-      </c>
-      <c r="T47" t="s">
-        <v>0</v>
-      </c>
-      <c r="U47" t="s">
-        <v>0</v>
-      </c>
-      <c r="V47" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="L47" s="1">
+        <v>110.63</v>
+      </c>
+      <c r="M47" s="1">
+        <v>7305.55</v>
+      </c>
+      <c r="N47" s="1">
+        <v>11.89</v>
+      </c>
+      <c r="O47" s="1">
+        <v>5172.62</v>
+      </c>
+      <c r="P47" s="1">
+        <v>8.14</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>68716.31</v>
+      </c>
+      <c r="R47" s="1">
+        <v>68716.31</v>
+      </c>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1">
+        <v>3.54</v>
+      </c>
+      <c r="V47" s="1">
         <v>0</v>
       </c>
       <c r="W47" t="s">
@@ -3989,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
         <v>0</v>
@@ -4001,48 +3536,48 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>41000</v>
+        <v>45000</v>
       </c>
       <c r="G48" s="1">
-        <v>127.55</v>
+        <v>103.53</v>
       </c>
       <c r="H48" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="I48" s="1">
-        <v>12.44</v>
+        <v>-8.99</v>
       </c>
       <c r="J48" s="1">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="K48" s="1">
-        <v>120.19</v>
+        <v>101.08</v>
       </c>
       <c r="L48" s="1">
-        <v>125.17</v>
+        <v>106.6</v>
       </c>
       <c r="M48" s="1">
-        <v>9206.16</v>
+        <v>1103.48</v>
       </c>
       <c r="N48" s="1">
-        <v>6.12</v>
+        <v>2.42</v>
       </c>
       <c r="O48" s="1">
-        <v>2973.08</v>
+        <v>-1379.62</v>
       </c>
       <c r="P48" s="1">
-        <v>1.9</v>
+        <v>-2.87</v>
       </c>
       <c r="Q48" s="1">
-        <v>159448.98000000001</v>
+        <v>46588.5</v>
       </c>
       <c r="R48" s="1">
-        <v>52295.5</v>
+        <v>46588.5</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1">
-        <v>8.2100000000000009</v>
+        <v>2.4</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
@@ -4056,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D49" t="s">
         <v>0</v>
@@ -4068,48 +3603,48 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>144000</v>
+        <v>24000</v>
       </c>
       <c r="G49" s="1">
-        <v>106.33</v>
+        <v>122.24</v>
       </c>
       <c r="H49" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I49" s="1">
-        <v>14.39</v>
+        <v>52.77</v>
       </c>
       <c r="J49" s="1">
-        <v>0.01</v>
+        <v>0.18</v>
       </c>
       <c r="K49" s="1">
-        <v>105.16</v>
+        <v>121</v>
       </c>
       <c r="L49" s="1">
-        <v>105.53</v>
+        <v>121.13</v>
       </c>
       <c r="M49" s="1">
-        <v>1678.6</v>
+        <v>297.58999999999997</v>
       </c>
       <c r="N49" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="O49" s="1">
-        <v>1152</v>
+        <v>267.01</v>
       </c>
       <c r="P49" s="1">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="Q49" s="1">
-        <v>153115.20000000001</v>
+        <v>29337.599999999999</v>
       </c>
       <c r="R49" s="1">
-        <v>153115.20000000001</v>
+        <v>29337.599999999999</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1">
-        <v>7.89</v>
+        <v>1.51</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -4123,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D50" t="s">
         <v>0</v>
@@ -4134,51 +3669,55 @@
       <c r="E50" t="s">
         <v>0</v>
       </c>
-      <c r="F50" s="1">
-        <v>18000</v>
-      </c>
-      <c r="G50" s="1">
-        <v>108.45</v>
+      <c r="F50" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>2</v>
-      </c>
-      <c r="I50" s="1">
-        <v>3.59</v>
-      </c>
-      <c r="J50" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K50" s="1">
-        <v>108.45</v>
-      </c>
-      <c r="L50" s="1">
-        <v>108.45</v>
-      </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1">
-        <v>0</v>
-      </c>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>19521</v>
-      </c>
-      <c r="R50" s="1">
-        <v>19521</v>
-      </c>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1">
-        <v>1.01</v>
-      </c>
-      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" t="s">
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>0</v>
+      </c>
+      <c r="M50" t="s">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>0</v>
+      </c>
+      <c r="P50" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>0</v>
+      </c>
+      <c r="R50" t="s">
+        <v>0</v>
+      </c>
+      <c r="S50" t="s">
+        <v>0</v>
+      </c>
+      <c r="T50" t="s">
+        <v>0</v>
+      </c>
+      <c r="U50" t="s">
+        <v>0</v>
+      </c>
+      <c r="V50" t="s">
         <v>0</v>
       </c>
       <c r="W50" t="s">
@@ -4190,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
         <v>0</v>
@@ -4234,8 +3773,8 @@
       <c r="P51" t="s">
         <v>0</v>
       </c>
-      <c r="Q51" t="s">
-        <v>0</v>
+      <c r="Q51" s="1">
+        <v>776918.11</v>
       </c>
       <c r="R51" t="s">
         <v>0</v>
@@ -4261,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -4305,8 +3844,8 @@
       <c r="P52" t="s">
         <v>0</v>
       </c>
-      <c r="Q52" s="1">
-        <v>332085.18</v>
+      <c r="Q52" t="s">
+        <v>0</v>
       </c>
       <c r="R52" t="s">
         <v>0</v>
@@ -4332,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
@@ -4403,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D54" t="s">
         <v>0</v>
@@ -4414,55 +3953,51 @@
       <c r="E54" t="s">
         <v>0</v>
       </c>
-      <c r="F54" t="s">
-        <v>0</v>
-      </c>
-      <c r="G54" t="s">
-        <v>0</v>
+      <c r="F54" s="1">
+        <v>41000</v>
+      </c>
+      <c r="G54" s="1">
+        <v>127.8</v>
       </c>
       <c r="H54" t="s">
-        <v>0</v>
-      </c>
-      <c r="I54" t="s">
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>0</v>
-      </c>
-      <c r="K54" t="s">
-        <v>0</v>
-      </c>
-      <c r="L54" t="s">
-        <v>0</v>
-      </c>
-      <c r="M54" t="s">
-        <v>0</v>
-      </c>
-      <c r="N54" t="s">
-        <v>0</v>
-      </c>
-      <c r="O54" t="s">
-        <v>0</v>
-      </c>
-      <c r="P54" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>0</v>
-      </c>
-      <c r="R54" t="s">
-        <v>0</v>
-      </c>
-      <c r="S54" t="s">
-        <v>0</v>
-      </c>
-      <c r="T54" t="s">
-        <v>0</v>
-      </c>
-      <c r="U54" t="s">
-        <v>0</v>
-      </c>
-      <c r="V54" t="s">
+        <v>96</v>
+      </c>
+      <c r="I54" s="1">
+        <v>25.01</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="K54" s="1">
+        <v>120.19</v>
+      </c>
+      <c r="L54" s="1">
+        <v>125.17</v>
+      </c>
+      <c r="M54" s="1">
+        <v>9553.02</v>
+      </c>
+      <c r="N54" s="1">
+        <v>6.33</v>
+      </c>
+      <c r="O54" s="1">
+        <v>3297.46</v>
+      </c>
+      <c r="P54" s="1">
+        <v>2.09</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>160337.88</v>
+      </c>
+      <c r="R54" s="1">
+        <v>52398</v>
+      </c>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1">
+        <v>8.25</v>
+      </c>
+      <c r="V54" s="1">
         <v>0</v>
       </c>
       <c r="W54" t="s">
@@ -4474,10 +4009,10 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D55" t="s">
         <v>0</v>
@@ -4486,48 +4021,48 @@
         <v>0</v>
       </c>
       <c r="F55" s="1">
-        <v>703</v>
+        <v>144000</v>
       </c>
       <c r="G55" s="1">
-        <v>39850</v>
+        <v>106.51</v>
       </c>
       <c r="H55" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I55" s="1">
-        <v>-2316.19</v>
+        <v>14.26</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.82</v>
+        <v>0.01</v>
       </c>
       <c r="K55" s="1">
-        <v>34092.879999999997</v>
+        <v>105.16</v>
       </c>
       <c r="L55" s="1">
-        <v>34168.11</v>
+        <v>105.53</v>
       </c>
       <c r="M55" s="1">
-        <v>40472.550000000003</v>
+        <v>1937.8</v>
       </c>
       <c r="N55" s="1">
-        <v>16.88</v>
+        <v>1.27</v>
       </c>
       <c r="O55" s="1">
-        <v>39943.71</v>
+        <v>1411.2</v>
       </c>
       <c r="P55" s="1">
-        <v>16.62</v>
+        <v>0.92</v>
       </c>
       <c r="Q55" s="1">
-        <v>280145.5</v>
+        <v>153374.39999999999</v>
       </c>
       <c r="R55" s="1">
-        <v>280145.5</v>
+        <v>153374.39999999999</v>
       </c>
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
       <c r="U55" s="1">
-        <v>14.43</v>
+        <v>7.89</v>
       </c>
       <c r="V55" s="1">
         <v>0</v>
@@ -4541,10 +4076,10 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C56" t="s">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -4552,55 +4087,51 @@
       <c r="E56" t="s">
         <v>0</v>
       </c>
-      <c r="F56" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" t="s">
-        <v>0</v>
+      <c r="F56" s="1">
+        <v>15000</v>
+      </c>
+      <c r="G56" s="1">
+        <v>108.62</v>
       </c>
       <c r="H56" t="s">
-        <v>0</v>
-      </c>
-      <c r="I56" t="s">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>0</v>
-      </c>
-      <c r="K56" t="s">
-        <v>0</v>
-      </c>
-      <c r="L56" t="s">
-        <v>0</v>
-      </c>
-      <c r="M56" t="s">
-        <v>0</v>
-      </c>
-      <c r="N56" t="s">
-        <v>0</v>
-      </c>
-      <c r="O56" t="s">
-        <v>0</v>
-      </c>
-      <c r="P56" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>0</v>
-      </c>
-      <c r="R56" t="s">
-        <v>0</v>
-      </c>
-      <c r="S56" t="s">
-        <v>0</v>
-      </c>
-      <c r="T56" t="s">
-        <v>0</v>
-      </c>
-      <c r="U56" t="s">
-        <v>0</v>
-      </c>
-      <c r="V56" t="s">
+        <v>27</v>
+      </c>
+      <c r="I56" s="1">
+        <v>3</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="K56" s="1">
+        <v>108.47</v>
+      </c>
+      <c r="L56" s="1">
+        <v>108.47</v>
+      </c>
+      <c r="M56" s="1">
+        <v>22.99</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O56" s="1">
+        <v>22.49</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>16293</v>
+      </c>
+      <c r="R56" s="1">
+        <v>16293</v>
+      </c>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="V56" s="1">
         <v>0</v>
       </c>
       <c r="W56" t="s">
@@ -4612,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="C57" t="s">
         <v>0</v>
@@ -4656,8 +4187,8 @@
       <c r="P57" t="s">
         <v>0</v>
       </c>
-      <c r="Q57" s="1">
-        <v>280145.5</v>
+      <c r="Q57" t="s">
+        <v>0</v>
       </c>
       <c r="R57" t="s">
         <v>0</v>
@@ -4683,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C58" t="s">
         <v>0</v>
@@ -4727,8 +4258,8 @@
       <c r="P58" t="s">
         <v>0</v>
       </c>
-      <c r="Q58" t="s">
-        <v>0</v>
+      <c r="Q58" s="1">
+        <v>330005.28000000003</v>
       </c>
       <c r="R58" t="s">
         <v>0</v>
@@ -4754,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="C59" t="s">
         <v>0</v>
@@ -4825,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
@@ -4896,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="C61" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
         <v>0</v>
@@ -4907,55 +4438,51 @@
       <c r="E61" t="s">
         <v>0</v>
       </c>
-      <c r="F61" t="s">
-        <v>0</v>
-      </c>
-      <c r="G61" t="s">
-        <v>0</v>
+      <c r="F61" s="1">
+        <v>703</v>
+      </c>
+      <c r="G61" s="1">
+        <v>39770</v>
       </c>
       <c r="H61" t="s">
-        <v>0</v>
-      </c>
-      <c r="I61" t="s">
-        <v>0</v>
-      </c>
-      <c r="J61" t="s">
-        <v>0</v>
-      </c>
-      <c r="K61" t="s">
-        <v>0</v>
-      </c>
-      <c r="L61" t="s">
-        <v>0</v>
-      </c>
-      <c r="M61" t="s">
-        <v>0</v>
-      </c>
-      <c r="N61" t="s">
-        <v>0</v>
-      </c>
-      <c r="O61" t="s">
-        <v>0</v>
-      </c>
-      <c r="P61" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>0</v>
-      </c>
-      <c r="R61" t="s">
-        <v>0</v>
-      </c>
-      <c r="S61" t="s">
-        <v>0</v>
-      </c>
-      <c r="T61" t="s">
-        <v>0</v>
-      </c>
-      <c r="U61" t="s">
-        <v>0</v>
-      </c>
-      <c r="V61" t="s">
+        <v>27</v>
+      </c>
+      <c r="I61" s="1">
+        <v>280.98</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K61" s="1">
+        <v>34092.879999999997</v>
+      </c>
+      <c r="L61" s="1">
+        <v>34168.11</v>
+      </c>
+      <c r="M61" s="1">
+        <v>39910.15</v>
+      </c>
+      <c r="N61" s="1">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="O61" s="1">
+        <v>39381.31</v>
+      </c>
+      <c r="P61" s="1">
+        <v>16.39</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>279583.09999999998</v>
+      </c>
+      <c r="R61" s="1">
+        <v>279583.09999999998</v>
+      </c>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1">
+        <v>14.39</v>
+      </c>
+      <c r="V61" s="1">
         <v>0</v>
       </c>
       <c r="W61" t="s">
@@ -4967,62 +4494,66 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="C62" t="s">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s">
         <v>0</v>
       </c>
-      <c r="F62" s="1">
-        <v>700</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0.3</v>
+      <c r="F62" t="s">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="1">
-        <v>-17.5</v>
-      </c>
-      <c r="J62" s="1">
-        <v>-2.7</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="L62" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="M62" s="1">
-        <v>-627.69000000000005</v>
-      </c>
-      <c r="N62" s="1">
-        <v>-49.84</v>
-      </c>
-      <c r="O62" s="1">
-        <v>-636.23</v>
-      </c>
-      <c r="P62" s="1">
-        <v>-50.18</v>
-      </c>
-      <c r="Q62" s="1">
-        <v>631.54</v>
-      </c>
-      <c r="R62" s="1">
-        <v>207.13</v>
-      </c>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
+        <v>0</v>
+      </c>
+      <c r="L62" t="s">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>0</v>
+      </c>
+      <c r="N62" t="s">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>0</v>
+      </c>
+      <c r="P62" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>0</v>
+      </c>
+      <c r="R62" t="s">
+        <v>0</v>
+      </c>
+      <c r="S62" t="s">
+        <v>0</v>
+      </c>
+      <c r="T62" t="s">
+        <v>0</v>
+      </c>
+      <c r="U62" t="s">
+        <v>0</v>
+      </c>
+      <c r="V62" t="s">
         <v>0</v>
       </c>
       <c r="W62" t="s">
@@ -5034,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C63" t="s">
         <v>0</v>
@@ -5078,8 +4609,8 @@
       <c r="P63" t="s">
         <v>0</v>
       </c>
-      <c r="Q63" t="s">
-        <v>0</v>
+      <c r="Q63" s="1">
+        <v>279583.09999999998</v>
       </c>
       <c r="R63" t="s">
         <v>0</v>
@@ -5105,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="C64" t="s">
         <v>0</v>
@@ -5149,8 +4680,8 @@
       <c r="P64" t="s">
         <v>0</v>
       </c>
-      <c r="Q64" s="1">
-        <v>631.54</v>
+      <c r="Q64" t="s">
+        <v>0</v>
       </c>
       <c r="R64" t="s">
         <v>0</v>
@@ -5168,6 +4699,779 @@
         <v>0</v>
       </c>
       <c r="W64" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" t="s">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F65" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>0</v>
+      </c>
+      <c r="J65" t="s">
+        <v>0</v>
+      </c>
+      <c r="K65" t="s">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>0</v>
+      </c>
+      <c r="M65" t="s">
+        <v>0</v>
+      </c>
+      <c r="N65" t="s">
+        <v>0</v>
+      </c>
+      <c r="O65" t="s">
+        <v>0</v>
+      </c>
+      <c r="P65" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>0</v>
+      </c>
+      <c r="R65" t="s">
+        <v>0</v>
+      </c>
+      <c r="S65" t="s">
+        <v>0</v>
+      </c>
+      <c r="T65" t="s">
+        <v>0</v>
+      </c>
+      <c r="U65" t="s">
+        <v>0</v>
+      </c>
+      <c r="V65" t="s">
+        <v>0</v>
+      </c>
+      <c r="W65" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" t="s">
+        <v>107</v>
+      </c>
+      <c r="C66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D66" t="s">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
+        <v>6649.44</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>66.489999999999995</v>
+      </c>
+      <c r="R66" s="1">
+        <v>66.489999999999995</v>
+      </c>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" t="s">
+        <v>0</v>
+      </c>
+      <c r="D67" t="s">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F67" t="s">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>0</v>
+      </c>
+      <c r="J67" t="s">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M67" t="s">
+        <v>0</v>
+      </c>
+      <c r="N67" t="s">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
+        <v>0</v>
+      </c>
+      <c r="P67" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>0</v>
+      </c>
+      <c r="R67" t="s">
+        <v>0</v>
+      </c>
+      <c r="S67" t="s">
+        <v>0</v>
+      </c>
+      <c r="T67" t="s">
+        <v>0</v>
+      </c>
+      <c r="U67" t="s">
+        <v>0</v>
+      </c>
+      <c r="V67" t="s">
+        <v>0</v>
+      </c>
+      <c r="W67" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" t="s">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>0</v>
+      </c>
+      <c r="F68" t="s">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>0</v>
+      </c>
+      <c r="J68" t="s">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>0</v>
+      </c>
+      <c r="M68" t="s">
+        <v>0</v>
+      </c>
+      <c r="N68" t="s">
+        <v>0</v>
+      </c>
+      <c r="O68" t="s">
+        <v>0</v>
+      </c>
+      <c r="P68" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>66.489999999999995</v>
+      </c>
+      <c r="R68" t="s">
+        <v>0</v>
+      </c>
+      <c r="S68" t="s">
+        <v>0</v>
+      </c>
+      <c r="T68" t="s">
+        <v>0</v>
+      </c>
+      <c r="U68" t="s">
+        <v>0</v>
+      </c>
+      <c r="V68" t="s">
+        <v>0</v>
+      </c>
+      <c r="W68" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" t="s">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>0</v>
+      </c>
+      <c r="I69" t="s">
+        <v>0</v>
+      </c>
+      <c r="J69" t="s">
+        <v>0</v>
+      </c>
+      <c r="K69" t="s">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>0</v>
+      </c>
+      <c r="M69" t="s">
+        <v>0</v>
+      </c>
+      <c r="N69" t="s">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
+        <v>0</v>
+      </c>
+      <c r="P69" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>0</v>
+      </c>
+      <c r="R69" t="s">
+        <v>0</v>
+      </c>
+      <c r="S69" t="s">
+        <v>0</v>
+      </c>
+      <c r="T69" t="s">
+        <v>0</v>
+      </c>
+      <c r="U69" t="s">
+        <v>0</v>
+      </c>
+      <c r="V69" t="s">
+        <v>0</v>
+      </c>
+      <c r="W69" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>0</v>
+      </c>
+      <c r="M70" t="s">
+        <v>0</v>
+      </c>
+      <c r="N70" t="s">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>0</v>
+      </c>
+      <c r="P70" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>0</v>
+      </c>
+      <c r="R70" t="s">
+        <v>0</v>
+      </c>
+      <c r="S70" t="s">
+        <v>0</v>
+      </c>
+      <c r="T70" t="s">
+        <v>0</v>
+      </c>
+      <c r="U70" t="s">
+        <v>0</v>
+      </c>
+      <c r="V70" t="s">
+        <v>0</v>
+      </c>
+      <c r="W70" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" t="s">
+        <v>0</v>
+      </c>
+      <c r="E71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>0</v>
+      </c>
+      <c r="K71" t="s">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>0</v>
+      </c>
+      <c r="M71" t="s">
+        <v>0</v>
+      </c>
+      <c r="N71" t="s">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>0</v>
+      </c>
+      <c r="P71" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>0</v>
+      </c>
+      <c r="R71" t="s">
+        <v>0</v>
+      </c>
+      <c r="S71" t="s">
+        <v>0</v>
+      </c>
+      <c r="T71" t="s">
+        <v>0</v>
+      </c>
+      <c r="U71" t="s">
+        <v>0</v>
+      </c>
+      <c r="V71" t="s">
+        <v>0</v>
+      </c>
+      <c r="W71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" t="s">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I72" t="s">
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>0</v>
+      </c>
+      <c r="K72" t="s">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>0</v>
+      </c>
+      <c r="M72" t="s">
+        <v>0</v>
+      </c>
+      <c r="N72" t="s">
+        <v>0</v>
+      </c>
+      <c r="O72" t="s">
+        <v>0</v>
+      </c>
+      <c r="P72" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>0</v>
+      </c>
+      <c r="R72" t="s">
+        <v>0</v>
+      </c>
+      <c r="S72" t="s">
+        <v>0</v>
+      </c>
+      <c r="T72" t="s">
+        <v>0</v>
+      </c>
+      <c r="U72" t="s">
+        <v>0</v>
+      </c>
+      <c r="V72" t="s">
+        <v>0</v>
+      </c>
+      <c r="W72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" t="s">
+        <v>111</v>
+      </c>
+      <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1">
+        <v>700</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="H73" t="s">
+        <v>96</v>
+      </c>
+      <c r="I73" s="1">
+        <v>-11.78</v>
+      </c>
+      <c r="J73" s="1">
+        <v>-1.51</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="M73" s="1">
+        <v>-497.58</v>
+      </c>
+      <c r="N73" s="1">
+        <v>-39.369999999999997</v>
+      </c>
+      <c r="O73" s="1">
+        <v>-506.15</v>
+      </c>
+      <c r="P73" s="1">
+        <v>-39.78</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>766.19</v>
+      </c>
+      <c r="R73" s="1">
+        <v>250.39</v>
+      </c>
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="V73" s="1">
+        <v>0</v>
+      </c>
+      <c r="W73" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>0</v>
+      </c>
+      <c r="I74" t="s">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>0</v>
+      </c>
+      <c r="M74" t="s">
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>0</v>
+      </c>
+      <c r="P74" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>0</v>
+      </c>
+      <c r="R74" t="s">
+        <v>0</v>
+      </c>
+      <c r="S74" t="s">
+        <v>0</v>
+      </c>
+      <c r="T74" t="s">
+        <v>0</v>
+      </c>
+      <c r="U74" t="s">
+        <v>0</v>
+      </c>
+      <c r="V74" t="s">
+        <v>0</v>
+      </c>
+      <c r="W74" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>0</v>
+      </c>
+      <c r="F75" t="s">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>0</v>
+      </c>
+      <c r="I75" t="s">
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>0</v>
+      </c>
+      <c r="M75" t="s">
+        <v>0</v>
+      </c>
+      <c r="N75" t="s">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
+        <v>0</v>
+      </c>
+      <c r="P75" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>766.19</v>
+      </c>
+      <c r="R75" t="s">
+        <v>0</v>
+      </c>
+      <c r="S75" t="s">
+        <v>0</v>
+      </c>
+      <c r="T75" t="s">
+        <v>0</v>
+      </c>
+      <c r="U75" t="s">
+        <v>0</v>
+      </c>
+      <c r="V75" t="s">
+        <v>0</v>
+      </c>
+      <c r="W75" t="s">
         <v>0</v>
       </c>
     </row>
